--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049602</v>
+        <v>127049592</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812043</v>
+        <v>812072</v>
       </c>
       <c r="R3" t="n">
-        <v>7389685</v>
+        <v>7389539</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049592</v>
+        <v>127049602</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812072</v>
+        <v>812043</v>
       </c>
       <c r="R4" t="n">
-        <v>7389539</v>
+        <v>7389685</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,6 +944,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,7 +1072,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049638</v>
+        <v>127049639</v>
       </c>
       <c r="B6" t="n">
         <v>92615</v>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811921</v>
+        <v>811937</v>
       </c>
       <c r="R6" t="n">
-        <v>7389590</v>
+        <v>7389558</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049639</v>
+        <v>127049638</v>
       </c>
       <c r="B7" t="n">
         <v>92615</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811937</v>
+        <v>811921</v>
       </c>
       <c r="R7" t="n">
-        <v>7389558</v>
+        <v>7389590</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127049595</v>
+        <v>127049621</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811948</v>
+        <v>812153</v>
       </c>
       <c r="R9" t="n">
-        <v>7389545</v>
+        <v>7389594</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127049621</v>
+        <v>127049595</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>812153</v>
+        <v>811948</v>
       </c>
       <c r="R10" t="n">
-        <v>7389594</v>
+        <v>7389545</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049620</v>
+        <v>127049628</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>812079</v>
+        <v>811980</v>
       </c>
       <c r="R12" t="n">
-        <v>7389510</v>
+        <v>7389540</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049596</v>
+        <v>127049620</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811955</v>
+        <v>812079</v>
       </c>
       <c r="R13" t="n">
-        <v>7389537</v>
+        <v>7389510</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049628</v>
+        <v>127049596</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811980</v>
+        <v>811955</v>
       </c>
       <c r="R14" t="n">
-        <v>7389540</v>
+        <v>7389537</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049630</v>
+        <v>127049631</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>812021</v>
+        <v>812026</v>
       </c>
       <c r="R18" t="n">
-        <v>7389474</v>
+        <v>7389461</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049631</v>
+        <v>127049630</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812026</v>
+        <v>812021</v>
       </c>
       <c r="R19" t="n">
-        <v>7389461</v>
+        <v>7389474</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049593</v>
+        <v>127049637</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R22" t="n">
-        <v>7389548</v>
+        <v>7389571</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,32 +2730,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049637</v>
+        <v>127049593</v>
       </c>
       <c r="B23" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R23" t="n">
-        <v>7389571</v>
+        <v>7389548</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3215,7 +3215,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049642</v>
+        <v>127049643</v>
       </c>
       <c r="B28" t="n">
         <v>92615</v>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811969</v>
+        <v>811987</v>
       </c>
       <c r="R28" t="n">
-        <v>7389545</v>
+        <v>7389527</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049643</v>
+        <v>127049642</v>
       </c>
       <c r="B29" t="n">
         <v>92615</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811987</v>
+        <v>811969</v>
       </c>
       <c r="R29" t="n">
-        <v>7389527</v>
+        <v>7389545</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049610</v>
+        <v>127049594</v>
       </c>
       <c r="B31" t="n">
-        <v>97326</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811967</v>
+        <v>811945</v>
       </c>
       <c r="R31" t="n">
-        <v>7389626</v>
+        <v>7389563</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049594</v>
+        <v>127049610</v>
       </c>
       <c r="B32" t="n">
-        <v>79632</v>
+        <v>97326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811945</v>
+        <v>811967</v>
       </c>
       <c r="R32" t="n">
-        <v>7389563</v>
+        <v>7389626</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049619</v>
+        <v>127049635</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>812060</v>
+        <v>812027</v>
       </c>
       <c r="R34" t="n">
-        <v>7389489</v>
+        <v>7389564</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3894,32 +3894,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127049635</v>
+        <v>127049619</v>
       </c>
       <c r="B35" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>812027</v>
+        <v>812060</v>
       </c>
       <c r="R35" t="n">
-        <v>7389564</v>
+        <v>7389489</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127049591</v>
+        <v>127049647</v>
       </c>
       <c r="B40" t="n">
-        <v>79632</v>
+        <v>77992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4391,21 +4391,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>812066</v>
+        <v>811948</v>
       </c>
       <c r="R40" t="n">
-        <v>7389504</v>
+        <v>7389545</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4477,10 +4477,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127049647</v>
+        <v>127049591</v>
       </c>
       <c r="B41" t="n">
-        <v>77992</v>
+        <v>79632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4488,21 +4488,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811948</v>
+        <v>812066</v>
       </c>
       <c r="R41" t="n">
-        <v>7389545</v>
+        <v>7389504</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4874,10 +4874,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049626</v>
+        <v>127049614</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>80989</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811984</v>
+        <v>812078</v>
       </c>
       <c r="R45" t="n">
-        <v>7389705</v>
+        <v>7389625</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049641</v>
+        <v>127049626</v>
       </c>
       <c r="B46" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811963</v>
+        <v>811984</v>
       </c>
       <c r="R46" t="n">
-        <v>7389548</v>
+        <v>7389705</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,32 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049614</v>
+        <v>127049641</v>
       </c>
       <c r="B47" t="n">
-        <v>80989</v>
+        <v>92615</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>812078</v>
+        <v>811963</v>
       </c>
       <c r="R47" t="n">
-        <v>7389625</v>
+        <v>7389548</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,34 +5567,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R52" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5627,6 +5631,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5653,10 +5662,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5664,38 +5673,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R53" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5728,11 +5733,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R54" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B55" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R55" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271847</v>
+        <v>127271925</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812034</v>
+        <v>812066</v>
       </c>
       <c r="R56" t="n">
-        <v>7389561</v>
+        <v>7389760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271925</v>
+        <v>127271847</v>
       </c>
       <c r="B57" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812066</v>
+        <v>812034</v>
       </c>
       <c r="R57" t="n">
-        <v>7389760</v>
+        <v>7389561</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6341,27 +6341,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271875</v>
+        <v>127271855</v>
       </c>
       <c r="B60" t="n">
-        <v>58027</v>
+        <v>57657</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6370,16 +6370,20 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812093</v>
+        <v>811859</v>
       </c>
       <c r="R60" t="n">
-        <v>7389656</v>
+        <v>7390026</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6412,6 +6416,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6438,32 +6447,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271883</v>
+        <v>127271911</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6473,10 +6482,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812004</v>
+        <v>812117</v>
       </c>
       <c r="R61" t="n">
-        <v>7389960</v>
+        <v>7389993</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6535,32 +6544,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271911</v>
+        <v>127271883</v>
       </c>
       <c r="B62" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6579,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812117</v>
+        <v>812004</v>
       </c>
       <c r="R62" t="n">
-        <v>7389993</v>
+        <v>7389960</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6632,27 +6641,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271855</v>
+        <v>127271875</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>58027</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6661,20 +6670,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811859</v>
+        <v>812093</v>
       </c>
       <c r="R63" t="n">
-        <v>7390026</v>
+        <v>7389656</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6707,11 +6712,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271858</v>
+        <v>127271888</v>
       </c>
       <c r="B64" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,38 +6749,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>812068</v>
+        <v>811957</v>
       </c>
       <c r="R64" t="n">
-        <v>7389929</v>
+        <v>7389943</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6813,11 +6809,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6844,10 +6835,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271888</v>
+        <v>127271858</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6855,34 +6846,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811957</v>
+        <v>812068</v>
       </c>
       <c r="R65" t="n">
-        <v>7389943</v>
+        <v>7389929</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6915,6 +6910,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6941,32 +6941,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271841</v>
+        <v>127271912</v>
       </c>
       <c r="B66" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812139</v>
+        <v>811981</v>
       </c>
       <c r="R66" t="n">
-        <v>7389967</v>
+        <v>7389988</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7038,32 +7038,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271842</v>
+        <v>127271921</v>
       </c>
       <c r="B67" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812161</v>
+        <v>812092</v>
       </c>
       <c r="R67" t="n">
-        <v>7389878</v>
+        <v>7389721</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7135,32 +7135,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271886</v>
+        <v>127271909</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811852</v>
+        <v>812175</v>
       </c>
       <c r="R68" t="n">
-        <v>7390093</v>
+        <v>7389748</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,32 +7232,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271912</v>
+        <v>127271841</v>
       </c>
       <c r="B69" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811981</v>
+        <v>812139</v>
       </c>
       <c r="R69" t="n">
-        <v>7389988</v>
+        <v>7389967</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,32 +7329,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271921</v>
+        <v>127271842</v>
       </c>
       <c r="B70" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812092</v>
+        <v>812161</v>
       </c>
       <c r="R70" t="n">
-        <v>7389721</v>
+        <v>7389878</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7426,32 +7426,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271909</v>
+        <v>127271886</v>
       </c>
       <c r="B71" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812175</v>
+        <v>811852</v>
       </c>
       <c r="R71" t="n">
-        <v>7389748</v>
+        <v>7390093</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7620,10 +7620,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271876</v>
+        <v>127271852</v>
       </c>
       <c r="B73" t="n">
-        <v>80989</v>
+        <v>57657</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7631,34 +7631,38 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812128</v>
+        <v>812054</v>
       </c>
       <c r="R73" t="n">
-        <v>7390038</v>
+        <v>7390009</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7693,13 +7697,17 @@
           <t>2025-08-05</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7718,10 +7726,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271852</v>
+        <v>127271876</v>
       </c>
       <c r="B74" t="n">
-        <v>57657</v>
+        <v>80989</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7729,38 +7737,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812054</v>
+        <v>812128</v>
       </c>
       <c r="R74" t="n">
-        <v>7390009</v>
+        <v>7390038</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7795,17 +7799,13 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8018,49 +8018,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271851</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>57657</v>
+        <v>92615</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812117</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389911</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8093,11 +8089,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8124,49 +8115,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271865</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
-        <v>57657</v>
+        <v>92615</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812024</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389558</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8199,11 +8186,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8230,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271917</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92615</v>
+        <v>91343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8265,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812088</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389936</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8327,45 +8309,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271908</v>
+        <v>127271851</v>
       </c>
       <c r="B80" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812128</v>
+        <v>812117</v>
       </c>
       <c r="R80" t="n">
-        <v>7389752</v>
+        <v>7389911</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8398,6 +8384,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8424,10 +8415,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271877</v>
+        <v>127271865</v>
       </c>
       <c r="B81" t="n">
-        <v>91343</v>
+        <v>57657</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8435,34 +8426,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812195</v>
+        <v>812024</v>
       </c>
       <c r="R81" t="n">
-        <v>7389776</v>
+        <v>7389558</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8495,6 +8490,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R84" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271843</v>
+        <v>127271890</v>
       </c>
       <c r="B85" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812074</v>
+        <v>812121</v>
       </c>
       <c r="R85" t="n">
-        <v>7389829</v>
+        <v>7389928</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,7 +8909,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271890</v>
+        <v>127271882</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812121</v>
+        <v>812120</v>
       </c>
       <c r="R86" t="n">
-        <v>7389928</v>
+        <v>7389917</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271849</v>
+        <v>127271891</v>
       </c>
       <c r="B89" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812114</v>
+        <v>812077</v>
       </c>
       <c r="R89" t="n">
-        <v>7389969</v>
+        <v>7389800</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9276,11 +9276,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9307,10 +9302,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271897</v>
+        <v>127271836</v>
       </c>
       <c r="B90" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9318,38 +9313,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>812122</v>
+        <v>811958</v>
       </c>
       <c r="R90" t="n">
-        <v>7389709</v>
+        <v>7389950</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9382,11 +9373,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9413,7 +9399,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271891</v>
+        <v>127271894</v>
       </c>
       <c r="B91" t="n">
         <v>79014</v>
@@ -9448,10 +9434,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>812077</v>
+        <v>811982</v>
       </c>
       <c r="R91" t="n">
-        <v>7389800</v>
+        <v>7389609</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9510,10 +9496,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271836</v>
+        <v>127271849</v>
       </c>
       <c r="B92" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9521,21 +9507,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9545,10 +9531,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811958</v>
+        <v>812114</v>
       </c>
       <c r="R92" t="n">
-        <v>7389950</v>
+        <v>7389969</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9581,6 +9567,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9607,10 +9598,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271894</v>
+        <v>127271897</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9618,34 +9609,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811982</v>
+        <v>812122</v>
       </c>
       <c r="R93" t="n">
-        <v>7389609</v>
+        <v>7389709</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9678,6 +9673,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271840</v>
+        <v>127271868</v>
       </c>
       <c r="B94" t="n">
-        <v>79632</v>
+        <v>57817</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812127</v>
+        <v>812092</v>
       </c>
       <c r="R94" t="n">
-        <v>7389936</v>
+        <v>7389656</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271857</v>
+        <v>127271840</v>
       </c>
       <c r="B95" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,21 +9812,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812050</v>
+        <v>812127</v>
       </c>
       <c r="R95" t="n">
-        <v>7389925</v>
+        <v>7389936</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271868</v>
+        <v>127271857</v>
       </c>
       <c r="B97" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812092</v>
+        <v>812050</v>
       </c>
       <c r="R97" t="n">
-        <v>7389656</v>
+        <v>7389925</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10392,32 +10392,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271893</v>
+        <v>127271916</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>812066</v>
+        <v>811958</v>
       </c>
       <c r="R101" t="n">
-        <v>7389634</v>
+        <v>7389946</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10489,32 +10489,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271916</v>
+        <v>127271893</v>
       </c>
       <c r="B102" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811958</v>
+        <v>812066</v>
       </c>
       <c r="R102" t="n">
-        <v>7389946</v>
+        <v>7389634</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10789,32 +10789,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271844</v>
+        <v>127271913</v>
       </c>
       <c r="B105" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>812114</v>
+        <v>811963</v>
       </c>
       <c r="R105" t="n">
-        <v>7389680</v>
+        <v>7390029</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10886,7 +10886,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271913</v>
+        <v>127271906</v>
       </c>
       <c r="B106" t="n">
         <v>92615</v>
@@ -10921,10 +10921,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811963</v>
+        <v>812166</v>
       </c>
       <c r="R106" t="n">
-        <v>7390029</v>
+        <v>7389625</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10983,10 +10983,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271892</v>
+        <v>127271844</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10994,21 +10994,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11018,10 +11018,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812106</v>
+        <v>812114</v>
       </c>
       <c r="R107" t="n">
-        <v>7389684</v>
+        <v>7389680</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11080,7 +11080,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271879</v>
+        <v>127271892</v>
       </c>
       <c r="B108" t="n">
         <v>79014</v>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812228</v>
+        <v>812106</v>
       </c>
       <c r="R108" t="n">
-        <v>7389839</v>
+        <v>7389684</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11177,32 +11177,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271906</v>
+        <v>127271879</v>
       </c>
       <c r="B109" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11212,10 +11212,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812166</v>
+        <v>812228</v>
       </c>
       <c r="R109" t="n">
-        <v>7389625</v>
+        <v>7389839</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11680,32 +11680,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271866</v>
+        <v>127271887</v>
       </c>
       <c r="B114" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811935</v>
+        <v>811866</v>
       </c>
       <c r="R114" t="n">
-        <v>7389957</v>
+        <v>7390052</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,32 +11777,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271887</v>
+        <v>127271919</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811866</v>
+        <v>812158</v>
       </c>
       <c r="R115" t="n">
-        <v>7390052</v>
+        <v>7389883</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,7 +11874,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271919</v>
+        <v>127271914</v>
       </c>
       <c r="B116" t="n">
         <v>92615</v>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>812158</v>
+        <v>811875</v>
       </c>
       <c r="R116" t="n">
-        <v>7389883</v>
+        <v>7389980</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11971,45 +11971,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271914</v>
+        <v>127271862</v>
       </c>
       <c r="B117" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811875</v>
+        <v>812079</v>
       </c>
       <c r="R117" t="n">
-        <v>7389980</v>
+        <v>7389800</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12042,6 +12046,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12068,49 +12077,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271862</v>
+        <v>127271866</v>
       </c>
       <c r="B118" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>812079</v>
+        <v>811935</v>
       </c>
       <c r="R118" t="n">
-        <v>7389800</v>
+        <v>7389957</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12143,11 +12148,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12271,7 +12271,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271850</v>
+        <v>127271861</v>
       </c>
       <c r="B120" t="n">
         <v>57657</v>
@@ -12310,10 +12310,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812124</v>
+        <v>812106</v>
       </c>
       <c r="R120" t="n">
-        <v>7389758</v>
+        <v>7389819</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Mellersta området</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12377,7 +12377,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271861</v>
+        <v>127271850</v>
       </c>
       <c r="B121" t="n">
         <v>57657</v>
@@ -12416,10 +12416,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812106</v>
+        <v>812124</v>
       </c>
       <c r="R121" t="n">
-        <v>7389819</v>
+        <v>7389758</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049594</v>
+        <v>127049610</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>97326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811945</v>
+        <v>811967</v>
       </c>
       <c r="R31" t="n">
-        <v>7389563</v>
+        <v>7389626</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049610</v>
+        <v>127049594</v>
       </c>
       <c r="B32" t="n">
-        <v>97326</v>
+        <v>79632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811967</v>
+        <v>811945</v>
       </c>
       <c r="R32" t="n">
-        <v>7389626</v>
+        <v>7389563</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4680,32 +4680,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127049634</v>
+        <v>127049615</v>
       </c>
       <c r="B43" t="n">
-        <v>92615</v>
+        <v>80989</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>812073</v>
+        <v>811948</v>
       </c>
       <c r="R43" t="n">
-        <v>7389533</v>
+        <v>7389545</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4777,32 +4777,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127049615</v>
+        <v>127049634</v>
       </c>
       <c r="B44" t="n">
-        <v>80989</v>
+        <v>92615</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811948</v>
+        <v>812073</v>
       </c>
       <c r="R44" t="n">
-        <v>7389545</v>
+        <v>7389533</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6341,27 +6341,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271855</v>
+        <v>127271875</v>
       </c>
       <c r="B60" t="n">
-        <v>57657</v>
+        <v>58027</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6370,20 +6370,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811859</v>
+        <v>812093</v>
       </c>
       <c r="R60" t="n">
-        <v>7390026</v>
+        <v>7389656</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6416,11 +6412,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6447,32 +6438,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271911</v>
+        <v>127271883</v>
       </c>
       <c r="B61" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6482,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812117</v>
+        <v>812004</v>
       </c>
       <c r="R61" t="n">
-        <v>7389993</v>
+        <v>7389960</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6544,32 +6535,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271883</v>
+        <v>127271911</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812004</v>
+        <v>812117</v>
       </c>
       <c r="R62" t="n">
-        <v>7389960</v>
+        <v>7389993</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6641,27 +6632,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271875</v>
+        <v>127271855</v>
       </c>
       <c r="B63" t="n">
-        <v>58027</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6670,16 +6661,20 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812093</v>
+        <v>811859</v>
       </c>
       <c r="R63" t="n">
-        <v>7389656</v>
+        <v>7390026</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6712,6 +6707,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B87" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R87" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,6 +9077,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9103,10 +9108,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B88" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9114,21 +9119,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R88" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9174,11 +9179,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271891</v>
+        <v>127271849</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812077</v>
+        <v>812114</v>
       </c>
       <c r="R89" t="n">
-        <v>7389800</v>
+        <v>7389969</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9276,6 +9276,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9302,10 +9307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271836</v>
+        <v>127271897</v>
       </c>
       <c r="B90" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,34 +9318,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811958</v>
+        <v>812122</v>
       </c>
       <c r="R90" t="n">
-        <v>7389950</v>
+        <v>7389709</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9373,6 +9382,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9399,7 +9413,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271894</v>
+        <v>127271891</v>
       </c>
       <c r="B91" t="n">
         <v>79014</v>
@@ -9434,10 +9448,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811982</v>
+        <v>812077</v>
       </c>
       <c r="R91" t="n">
-        <v>7389609</v>
+        <v>7389800</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9496,10 +9510,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271849</v>
+        <v>127271836</v>
       </c>
       <c r="B92" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9507,21 +9521,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9531,10 +9545,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>812114</v>
+        <v>811958</v>
       </c>
       <c r="R92" t="n">
-        <v>7389969</v>
+        <v>7389950</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9567,11 +9581,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9598,10 +9607,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271897</v>
+        <v>127271894</v>
       </c>
       <c r="B93" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9609,38 +9618,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>812122</v>
+        <v>811982</v>
       </c>
       <c r="R93" t="n">
-        <v>7389709</v>
+        <v>7389609</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9673,11 +9678,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271868</v>
+        <v>127271840</v>
       </c>
       <c r="B94" t="n">
-        <v>57817</v>
+        <v>79632</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812092</v>
+        <v>812127</v>
       </c>
       <c r="R94" t="n">
-        <v>7389656</v>
+        <v>7389936</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271840</v>
+        <v>127271856</v>
       </c>
       <c r="B95" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,34 +9812,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812127</v>
+        <v>811876</v>
       </c>
       <c r="R95" t="n">
-        <v>7389936</v>
+        <v>7389968</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9872,6 +9876,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9898,7 +9907,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271856</v>
+        <v>127271857</v>
       </c>
       <c r="B96" t="n">
         <v>57657</v>
@@ -9927,20 +9936,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811876</v>
+        <v>812050</v>
       </c>
       <c r="R96" t="n">
-        <v>7389968</v>
+        <v>7389925</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9973,11 +9978,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271857</v>
+        <v>127271868</v>
       </c>
       <c r="B97" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812050</v>
+        <v>812092</v>
       </c>
       <c r="R97" t="n">
-        <v>7389925</v>
+        <v>7389656</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049592</v>
+        <v>127049608</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812072</v>
+        <v>812055</v>
       </c>
       <c r="R3" t="n">
-        <v>7389539</v>
+        <v>7389491</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -975,32 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049608</v>
+        <v>127049592</v>
       </c>
       <c r="B5" t="n">
-        <v>97326</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812055</v>
+        <v>812072</v>
       </c>
       <c r="R5" t="n">
-        <v>7389491</v>
+        <v>7389539</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049639</v>
+        <v>127049638</v>
       </c>
       <c r="B6" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811937</v>
+        <v>811921</v>
       </c>
       <c r="R6" t="n">
-        <v>7389558</v>
+        <v>7389590</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049638</v>
+        <v>127049639</v>
       </c>
       <c r="B7" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811921</v>
+        <v>811937</v>
       </c>
       <c r="R7" t="n">
-        <v>7389590</v>
+        <v>7389558</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1269,7 +1269,7 @@
         <v>127049611</v>
       </c>
       <c r="B8" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049628</v>
+        <v>127049596</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811980</v>
+        <v>811955</v>
       </c>
       <c r="R12" t="n">
-        <v>7389540</v>
+        <v>7389537</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049620</v>
+        <v>127049618</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>812079</v>
+        <v>812047</v>
       </c>
       <c r="R13" t="n">
-        <v>7389510</v>
+        <v>7389473</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049596</v>
+        <v>127049620</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811955</v>
+        <v>812079</v>
       </c>
       <c r="R14" t="n">
-        <v>7389537</v>
+        <v>7389510</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049618</v>
+        <v>127049628</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>812047</v>
+        <v>811980</v>
       </c>
       <c r="R15" t="n">
-        <v>7389473</v>
+        <v>7389540</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2142,7 +2142,7 @@
         <v>127049645</v>
       </c>
       <c r="B17" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049631</v>
+        <v>127049630</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>812026</v>
+        <v>812021</v>
       </c>
       <c r="R18" t="n">
-        <v>7389461</v>
+        <v>7389474</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049630</v>
+        <v>127049631</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812021</v>
+        <v>812026</v>
       </c>
       <c r="R19" t="n">
-        <v>7389474</v>
+        <v>7389461</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049637</v>
+        <v>127049593</v>
       </c>
       <c r="B22" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R22" t="n">
-        <v>7389571</v>
+        <v>7389548</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,32 +2730,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049593</v>
+        <v>127049637</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R23" t="n">
-        <v>7389548</v>
+        <v>7389571</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2830,7 +2830,7 @@
         <v>127049640</v>
       </c>
       <c r="B24" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127049605</v>
       </c>
       <c r="B26" t="n">
-        <v>92643</v>
+        <v>92644</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049633</v>
+        <v>127049642</v>
       </c>
       <c r="B27" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811950</v>
+        <v>811969</v>
       </c>
       <c r="R27" t="n">
-        <v>7389574</v>
+        <v>7389545</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3218,7 +3218,7 @@
         <v>127049643</v>
       </c>
       <c r="B28" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,32 +3312,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049642</v>
+        <v>127049633</v>
       </c>
       <c r="B29" t="n">
-        <v>92615</v>
+        <v>78681</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811969</v>
+        <v>811950</v>
       </c>
       <c r="R29" t="n">
-        <v>7389545</v>
+        <v>7389574</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3412,7 +3412,7 @@
         <v>127049609</v>
       </c>
       <c r="B30" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049610</v>
+        <v>127049594</v>
       </c>
       <c r="B31" t="n">
-        <v>97326</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811967</v>
+        <v>811945</v>
       </c>
       <c r="R31" t="n">
-        <v>7389626</v>
+        <v>7389563</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049594</v>
+        <v>127049610</v>
       </c>
       <c r="B32" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811945</v>
+        <v>811967</v>
       </c>
       <c r="R32" t="n">
-        <v>7389563</v>
+        <v>7389626</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3700,32 +3700,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127049625</v>
+        <v>127049607</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811987</v>
+        <v>812105</v>
       </c>
       <c r="R33" t="n">
-        <v>7389722</v>
+        <v>7389559</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3800,7 +3800,7 @@
         <v>127049635</v>
       </c>
       <c r="B34" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127049619</v>
+        <v>127049625</v>
       </c>
       <c r="B35" t="n">
         <v>79014</v>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>812060</v>
+        <v>811987</v>
       </c>
       <c r="R35" t="n">
-        <v>7389489</v>
+        <v>7389722</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3991,32 +3991,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127049607</v>
+        <v>127049619</v>
       </c>
       <c r="B36" t="n">
-        <v>97326</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>812105</v>
+        <v>812060</v>
       </c>
       <c r="R36" t="n">
-        <v>7389559</v>
+        <v>7389489</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127049647</v>
+        <v>127049591</v>
       </c>
       <c r="B40" t="n">
-        <v>77992</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4391,21 +4391,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811948</v>
+        <v>812066</v>
       </c>
       <c r="R40" t="n">
-        <v>7389545</v>
+        <v>7389504</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4477,10 +4477,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127049591</v>
+        <v>127049647</v>
       </c>
       <c r="B41" t="n">
-        <v>79632</v>
+        <v>77992</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4488,21 +4488,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>812066</v>
+        <v>811948</v>
       </c>
       <c r="R41" t="n">
-        <v>7389504</v>
+        <v>7389545</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4680,32 +4680,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127049615</v>
+        <v>127049634</v>
       </c>
       <c r="B43" t="n">
-        <v>80989</v>
+        <v>92616</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811948</v>
+        <v>812073</v>
       </c>
       <c r="R43" t="n">
-        <v>7389545</v>
+        <v>7389533</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4777,32 +4777,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127049634</v>
+        <v>127049615</v>
       </c>
       <c r="B44" t="n">
-        <v>92615</v>
+        <v>80989</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>812073</v>
+        <v>811948</v>
       </c>
       <c r="R44" t="n">
-        <v>7389533</v>
+        <v>7389545</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049641</v>
+        <v>127049606</v>
       </c>
       <c r="B47" t="n">
-        <v>92615</v>
+        <v>97327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5079,21 +5079,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811963</v>
+        <v>812115</v>
       </c>
       <c r="R47" t="n">
-        <v>7389548</v>
+        <v>7389567</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5165,10 +5165,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127049606</v>
+        <v>127049641</v>
       </c>
       <c r="B48" t="n">
-        <v>97326</v>
+        <v>92616</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5176,21 +5176,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>812115</v>
+        <v>811963</v>
       </c>
       <c r="R48" t="n">
-        <v>7389567</v>
+        <v>7389548</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,38 +5567,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R52" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5631,11 +5627,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5662,10 +5653,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5673,34 +5664,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R53" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5733,6 +5728,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5762,7 +5762,7 @@
         <v>127271920</v>
       </c>
       <c r="B54" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B56" t="n">
-        <v>78420</v>
+        <v>92616</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R56" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B57" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R57" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B58" t="n">
-        <v>92615</v>
+        <v>78420</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R58" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B59" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R59" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,27 +6341,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271875</v>
+        <v>127271855</v>
       </c>
       <c r="B60" t="n">
-        <v>58027</v>
+        <v>57657</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6370,16 +6370,20 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812093</v>
+        <v>811859</v>
       </c>
       <c r="R60" t="n">
-        <v>7389656</v>
+        <v>7390026</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6412,6 +6416,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6538,7 +6547,7 @@
         <v>127271911</v>
       </c>
       <c r="B62" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6632,27 +6641,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271855</v>
+        <v>127271875</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>58027</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6661,20 +6670,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811859</v>
+        <v>812093</v>
       </c>
       <c r="R63" t="n">
-        <v>7390026</v>
+        <v>7389656</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6707,11 +6712,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271888</v>
+        <v>127271858</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,34 +6749,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811957</v>
+        <v>812068</v>
       </c>
       <c r="R64" t="n">
-        <v>7389943</v>
+        <v>7389929</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6809,6 +6813,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6835,10 +6844,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271858</v>
+        <v>127271888</v>
       </c>
       <c r="B65" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6846,38 +6855,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>812068</v>
+        <v>811957</v>
       </c>
       <c r="R65" t="n">
-        <v>7389929</v>
+        <v>7389943</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6910,11 +6915,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6941,32 +6941,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271912</v>
+        <v>127271876</v>
       </c>
       <c r="B66" t="n">
-        <v>92615</v>
+        <v>80989</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811981</v>
+        <v>812128</v>
       </c>
       <c r="R66" t="n">
-        <v>7389988</v>
+        <v>7390038</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7020,6 +7020,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7038,32 +7039,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271921</v>
+        <v>127271841</v>
       </c>
       <c r="B67" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7074,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812092</v>
+        <v>812139</v>
       </c>
       <c r="R67" t="n">
-        <v>7389721</v>
+        <v>7389967</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7135,32 +7136,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271909</v>
+        <v>127271842</v>
       </c>
       <c r="B68" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7170,10 +7171,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812175</v>
+        <v>812161</v>
       </c>
       <c r="R68" t="n">
-        <v>7389748</v>
+        <v>7389878</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,10 +7233,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271841</v>
+        <v>127271886</v>
       </c>
       <c r="B69" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7243,21 +7244,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7267,10 +7268,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812139</v>
+        <v>811852</v>
       </c>
       <c r="R69" t="n">
-        <v>7389967</v>
+        <v>7390093</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,10 +7330,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271842</v>
+        <v>127271852</v>
       </c>
       <c r="B70" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7340,34 +7341,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812161</v>
+        <v>812054</v>
       </c>
       <c r="R70" t="n">
-        <v>7389878</v>
+        <v>7390009</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7400,6 +7405,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7426,32 +7436,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271886</v>
+        <v>127271912</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7461,10 +7471,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811852</v>
+        <v>811981</v>
       </c>
       <c r="R71" t="n">
-        <v>7390093</v>
+        <v>7389988</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7523,32 +7533,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271881</v>
+        <v>127271921</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7558,10 +7568,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812133</v>
+        <v>812092</v>
       </c>
       <c r="R72" t="n">
-        <v>7389830</v>
+        <v>7389721</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7620,49 +7630,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271852</v>
+        <v>127271909</v>
       </c>
       <c r="B73" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812054</v>
+        <v>812175</v>
       </c>
       <c r="R73" t="n">
-        <v>7390009</v>
+        <v>7389748</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7695,11 +7701,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7726,10 +7727,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271876</v>
+        <v>127271881</v>
       </c>
       <c r="B74" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7737,21 +7738,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7761,10 +7762,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812128</v>
+        <v>812133</v>
       </c>
       <c r="R74" t="n">
-        <v>7390038</v>
+        <v>7389830</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7805,7 +7806,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>127271924</v>
       </c>
       <c r="B76" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,45 +8018,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127271851</v>
       </c>
       <c r="B77" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>812117</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389911</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8089,6 +8093,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8115,45 +8124,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127271865</v>
       </c>
       <c r="B78" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>812024</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389558</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8186,6 +8199,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8212,32 +8230,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271917</v>
       </c>
       <c r="B79" t="n">
-        <v>91343</v>
+        <v>92616</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8265,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>812088</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389936</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8309,49 +8327,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271851</v>
+        <v>127271908</v>
       </c>
       <c r="B80" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812117</v>
+        <v>812128</v>
       </c>
       <c r="R80" t="n">
-        <v>7389911</v>
+        <v>7389752</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8384,11 +8398,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8415,10 +8424,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271865</v>
+        <v>127271877</v>
       </c>
       <c r="B81" t="n">
-        <v>57657</v>
+        <v>91344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8426,38 +8435,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812024</v>
+        <v>812195</v>
       </c>
       <c r="R81" t="n">
-        <v>7389558</v>
+        <v>7389776</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8490,11 +8495,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8521,7 +8521,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127271895</v>
+        <v>127271878</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>812002</v>
+        <v>812112</v>
       </c>
       <c r="R82" t="n">
-        <v>7389603</v>
+        <v>7389762</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8618,7 +8618,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127271878</v>
+        <v>127271895</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>812112</v>
+        <v>812002</v>
       </c>
       <c r="R83" t="n">
-        <v>7389762</v>
+        <v>7389603</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271843</v>
+        <v>127271882</v>
       </c>
       <c r="B84" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812074</v>
+        <v>812120</v>
       </c>
       <c r="R84" t="n">
-        <v>7389829</v>
+        <v>7389917</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271890</v>
+        <v>127271843</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812121</v>
+        <v>812074</v>
       </c>
       <c r="R85" t="n">
-        <v>7389928</v>
+        <v>7389829</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,7 +8909,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271882</v>
+        <v>127271890</v>
       </c>
       <c r="B86" t="n">
         <v>79014</v>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812120</v>
+        <v>812121</v>
       </c>
       <c r="R86" t="n">
-        <v>7389917</v>
+        <v>7389928</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B87" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R87" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,11 +9077,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9108,10 +9103,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B88" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9119,21 +9114,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R88" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9179,6 +9174,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271849</v>
+        <v>127271891</v>
       </c>
       <c r="B89" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812114</v>
+        <v>812077</v>
       </c>
       <c r="R89" t="n">
-        <v>7389969</v>
+        <v>7389800</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9276,11 +9276,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9307,10 +9302,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271897</v>
+        <v>127271836</v>
       </c>
       <c r="B90" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9318,38 +9313,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>812122</v>
+        <v>811958</v>
       </c>
       <c r="R90" t="n">
-        <v>7389709</v>
+        <v>7389950</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9382,11 +9373,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9413,10 +9399,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271891</v>
+        <v>127271849</v>
       </c>
       <c r="B91" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9424,21 +9410,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9448,10 +9434,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>812077</v>
+        <v>812114</v>
       </c>
       <c r="R91" t="n">
-        <v>7389800</v>
+        <v>7389969</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9484,6 +9470,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9510,10 +9501,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271836</v>
+        <v>127271897</v>
       </c>
       <c r="B92" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9521,34 +9512,38 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811958</v>
+        <v>812122</v>
       </c>
       <c r="R92" t="n">
-        <v>7389950</v>
+        <v>7389709</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9581,6 +9576,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10201,7 +10201,7 @@
         <v>127271915</v>
       </c>
       <c r="B99" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10295,45 +10295,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271907</v>
+        <v>127271864</v>
       </c>
       <c r="B100" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812162</v>
+        <v>812087</v>
       </c>
       <c r="R100" t="n">
-        <v>7389625</v>
+        <v>7389653</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10366,6 +10370,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10392,10 +10401,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271916</v>
+        <v>127271907</v>
       </c>
       <c r="B101" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10427,10 +10436,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811958</v>
+        <v>812162</v>
       </c>
       <c r="R101" t="n">
-        <v>7389946</v>
+        <v>7389625</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10586,32 +10595,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271884</v>
+        <v>127271916</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10621,10 +10630,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811977</v>
+        <v>811958</v>
       </c>
       <c r="R103" t="n">
-        <v>7389985</v>
+        <v>7389946</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10683,10 +10692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271864</v>
+        <v>127271884</v>
       </c>
       <c r="B104" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10694,38 +10703,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>812087</v>
+        <v>811977</v>
       </c>
       <c r="R104" t="n">
-        <v>7389653</v>
+        <v>7389985</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10758,11 +10763,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,45 +10789,49 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271913</v>
+        <v>127271853</v>
       </c>
       <c r="B105" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811963</v>
+        <v>811970</v>
       </c>
       <c r="R105" t="n">
-        <v>7390029</v>
+        <v>7390085</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10860,6 +10864,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10886,10 +10895,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271906</v>
+        <v>127271913</v>
       </c>
       <c r="B106" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10921,10 +10930,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812166</v>
+        <v>811963</v>
       </c>
       <c r="R106" t="n">
-        <v>7389625</v>
+        <v>7390029</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10983,10 +10992,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271844</v>
+        <v>127271892</v>
       </c>
       <c r="B107" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10994,21 +11003,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11018,10 +11027,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812114</v>
+        <v>812106</v>
       </c>
       <c r="R107" t="n">
-        <v>7389680</v>
+        <v>7389684</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11080,7 +11089,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271892</v>
+        <v>127271879</v>
       </c>
       <c r="B108" t="n">
         <v>79014</v>
@@ -11115,10 +11124,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812106</v>
+        <v>812228</v>
       </c>
       <c r="R108" t="n">
-        <v>7389684</v>
+        <v>7389839</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11177,32 +11186,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271879</v>
+        <v>127271906</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11212,10 +11221,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812228</v>
+        <v>812166</v>
       </c>
       <c r="R109" t="n">
-        <v>7389839</v>
+        <v>7389625</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11274,10 +11283,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271853</v>
+        <v>127271844</v>
       </c>
       <c r="B110" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11285,38 +11294,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811970</v>
+        <v>812114</v>
       </c>
       <c r="R110" t="n">
-        <v>7390085</v>
+        <v>7389680</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11349,11 +11354,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11380,32 +11380,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271922</v>
+        <v>127271885</v>
       </c>
       <c r="B111" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>812120</v>
+        <v>811960</v>
       </c>
       <c r="R111" t="n">
-        <v>7389691</v>
+        <v>7390029</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11477,10 +11477,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271885</v>
+        <v>127271860</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11488,34 +11488,38 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811960</v>
+        <v>812080</v>
       </c>
       <c r="R112" t="n">
-        <v>7390029</v>
+        <v>7389823</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11548,6 +11552,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11574,49 +11583,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127271860</v>
+        <v>127271922</v>
       </c>
       <c r="B113" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>812080</v>
+        <v>812120</v>
       </c>
       <c r="R113" t="n">
-        <v>7389823</v>
+        <v>7389691</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11649,11 +11654,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11680,10 +11680,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271887</v>
+        <v>127271862</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11691,34 +11691,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811866</v>
+        <v>812079</v>
       </c>
       <c r="R114" t="n">
-        <v>7390052</v>
+        <v>7389800</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11751,6 +11755,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11777,32 +11786,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271919</v>
+        <v>127271887</v>
       </c>
       <c r="B115" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11812,10 +11821,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>812158</v>
+        <v>811866</v>
       </c>
       <c r="R115" t="n">
-        <v>7389883</v>
+        <v>7390052</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,10 +11883,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271914</v>
+        <v>127271919</v>
       </c>
       <c r="B116" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11909,10 +11918,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811875</v>
+        <v>812158</v>
       </c>
       <c r="R116" t="n">
-        <v>7389980</v>
+        <v>7389883</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11971,49 +11980,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271862</v>
+        <v>127271914</v>
       </c>
       <c r="B117" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>812079</v>
+        <v>811875</v>
       </c>
       <c r="R117" t="n">
-        <v>7389800</v>
+        <v>7389980</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12046,11 +12051,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12174,45 +12174,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271918</v>
+        <v>127271861</v>
       </c>
       <c r="B119" t="n">
-        <v>92615</v>
+        <v>57657</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812162</v>
+        <v>812106</v>
       </c>
       <c r="R119" t="n">
-        <v>7389925</v>
+        <v>7389819</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12245,6 +12249,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12271,7 +12280,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271861</v>
+        <v>127271850</v>
       </c>
       <c r="B120" t="n">
         <v>57657</v>
@@ -12310,10 +12319,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812106</v>
+        <v>812124</v>
       </c>
       <c r="R120" t="n">
-        <v>7389819</v>
+        <v>7389758</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12350,7 +12359,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12377,49 +12386,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271850</v>
+        <v>127271918</v>
       </c>
       <c r="B121" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812124</v>
+        <v>812162</v>
       </c>
       <c r="R121" t="n">
-        <v>7389758</v>
+        <v>7389925</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12454,11 +12459,6 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Mellersta området</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +12480,103 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>127388830</v>
+      </c>
+      <c r="B122" t="n">
+        <v>91487</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Skaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>812039</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7389582</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049596</v>
+        <v>127049620</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811955</v>
+        <v>812079</v>
       </c>
       <c r="R12" t="n">
-        <v>7389537</v>
+        <v>7389510</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049618</v>
+        <v>127049628</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>812047</v>
+        <v>811980</v>
       </c>
       <c r="R13" t="n">
-        <v>7389473</v>
+        <v>7389540</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049620</v>
+        <v>127049596</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>812079</v>
+        <v>811955</v>
       </c>
       <c r="R14" t="n">
-        <v>7389510</v>
+        <v>7389537</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049628</v>
+        <v>127049618</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811980</v>
+        <v>812047</v>
       </c>
       <c r="R15" t="n">
-        <v>7389540</v>
+        <v>7389473</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049593</v>
+        <v>127049637</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R22" t="n">
-        <v>7389548</v>
+        <v>7389571</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049637</v>
+        <v>127049640</v>
       </c>
       <c r="B23" t="n">
         <v>92616</v>
@@ -2768,7 +2768,7 @@
         <v>811936</v>
       </c>
       <c r="R23" t="n">
-        <v>7389571</v>
+        <v>7389556</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2827,32 +2827,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127049640</v>
+        <v>127049593</v>
       </c>
       <c r="B24" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R24" t="n">
-        <v>7389556</v>
+        <v>7389548</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049642</v>
+        <v>127049609</v>
       </c>
       <c r="B27" t="n">
-        <v>92616</v>
+        <v>97327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811969</v>
+        <v>811991</v>
       </c>
       <c r="R27" t="n">
-        <v>7389545</v>
+        <v>7389623</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049643</v>
+        <v>127049633</v>
       </c>
       <c r="B28" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811987</v>
+        <v>811950</v>
       </c>
       <c r="R28" t="n">
-        <v>7389527</v>
+        <v>7389574</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,32 +3312,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049633</v>
+        <v>127049642</v>
       </c>
       <c r="B29" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811950</v>
+        <v>811969</v>
       </c>
       <c r="R29" t="n">
-        <v>7389574</v>
+        <v>7389545</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049609</v>
+        <v>127049643</v>
       </c>
       <c r="B30" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811991</v>
+        <v>811987</v>
       </c>
       <c r="R30" t="n">
-        <v>7389623</v>
+        <v>7389527</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3700,10 +3700,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127049607</v>
+        <v>127049635</v>
       </c>
       <c r="B33" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3711,21 +3711,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>812105</v>
+        <v>812027</v>
       </c>
       <c r="R33" t="n">
-        <v>7389559</v>
+        <v>7389564</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049635</v>
+        <v>127049625</v>
       </c>
       <c r="B34" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>812027</v>
+        <v>811987</v>
       </c>
       <c r="R34" t="n">
-        <v>7389564</v>
+        <v>7389722</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127049625</v>
+        <v>127049619</v>
       </c>
       <c r="B35" t="n">
         <v>79014</v>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811987</v>
+        <v>812060</v>
       </c>
       <c r="R35" t="n">
-        <v>7389722</v>
+        <v>7389489</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3991,32 +3991,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127049619</v>
+        <v>127049607</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>812060</v>
+        <v>812105</v>
       </c>
       <c r="R36" t="n">
-        <v>7389489</v>
+        <v>7389559</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B54" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R54" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R55" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -8521,7 +8521,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127271878</v>
+        <v>127271895</v>
       </c>
       <c r="B82" t="n">
         <v>79014</v>
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>812112</v>
+        <v>812002</v>
       </c>
       <c r="R82" t="n">
-        <v>7389762</v>
+        <v>7389603</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8618,7 +8618,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127271895</v>
+        <v>127271878</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>812002</v>
+        <v>812112</v>
       </c>
       <c r="R83" t="n">
-        <v>7389603</v>
+        <v>7389762</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B87" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R87" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,6 +9077,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9103,10 +9108,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B88" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9114,21 +9119,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R88" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9174,11 +9179,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271856</v>
+        <v>127271868</v>
       </c>
       <c r="B95" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,38 +9812,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811876</v>
+        <v>812092</v>
       </c>
       <c r="R95" t="n">
-        <v>7389968</v>
+        <v>7389656</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9876,11 +9872,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9907,7 +9898,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271857</v>
+        <v>127271856</v>
       </c>
       <c r="B96" t="n">
         <v>57657</v>
@@ -9936,16 +9927,20 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812050</v>
+        <v>811876</v>
       </c>
       <c r="R96" t="n">
-        <v>7389925</v>
+        <v>7389968</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9978,6 +9973,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271868</v>
+        <v>127271857</v>
       </c>
       <c r="B97" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812092</v>
+        <v>812050</v>
       </c>
       <c r="R97" t="n">
-        <v>7389656</v>
+        <v>7389925</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049608</v>
+        <v>127049592</v>
       </c>
       <c r="B3" t="n">
-        <v>97327</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812055</v>
+        <v>812072</v>
       </c>
       <c r="R3" t="n">
-        <v>7389491</v>
+        <v>7389539</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -975,32 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049592</v>
+        <v>127049608</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812072</v>
+        <v>812055</v>
       </c>
       <c r="R5" t="n">
-        <v>7389539</v>
+        <v>7389491</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049620</v>
+        <v>127049596</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>812079</v>
+        <v>811955</v>
       </c>
       <c r="R12" t="n">
-        <v>7389510</v>
+        <v>7389537</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049628</v>
+        <v>127049618</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811980</v>
+        <v>812047</v>
       </c>
       <c r="R13" t="n">
-        <v>7389540</v>
+        <v>7389473</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049596</v>
+        <v>127049620</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811955</v>
+        <v>812079</v>
       </c>
       <c r="R14" t="n">
-        <v>7389537</v>
+        <v>7389510</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049618</v>
+        <v>127049628</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>812047</v>
+        <v>811980</v>
       </c>
       <c r="R15" t="n">
-        <v>7389473</v>
+        <v>7389540</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127049623</v>
+        <v>127049645</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>812077</v>
+        <v>812008</v>
       </c>
       <c r="R16" t="n">
-        <v>7389513</v>
+        <v>7389456</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127049645</v>
+        <v>127049623</v>
       </c>
       <c r="B17" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>812008</v>
+        <v>812077</v>
       </c>
       <c r="R17" t="n">
-        <v>7389456</v>
+        <v>7389513</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049630</v>
+        <v>127049601</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,34 +2247,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>812021</v>
+        <v>811940</v>
       </c>
       <c r="R18" t="n">
-        <v>7389474</v>
+        <v>7389556</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2307,6 +2311,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2333,7 +2342,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049631</v>
+        <v>127049630</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2368,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812026</v>
+        <v>812021</v>
       </c>
       <c r="R19" t="n">
-        <v>7389461</v>
+        <v>7389474</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2527,10 +2536,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127049601</v>
+        <v>127049631</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2538,38 +2547,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811940</v>
+        <v>812026</v>
       </c>
       <c r="R21" t="n">
-        <v>7389556</v>
+        <v>7389461</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2602,11 +2607,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049637</v>
+        <v>127049640</v>
       </c>
       <c r="B22" t="n">
         <v>92616</v>
@@ -2671,7 +2671,7 @@
         <v>811936</v>
       </c>
       <c r="R22" t="n">
-        <v>7389571</v>
+        <v>7389556</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049640</v>
+        <v>127049637</v>
       </c>
       <c r="B23" t="n">
         <v>92616</v>
@@ -2768,7 +2768,7 @@
         <v>811936</v>
       </c>
       <c r="R23" t="n">
-        <v>7389556</v>
+        <v>7389571</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049609</v>
+        <v>127049642</v>
       </c>
       <c r="B27" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811991</v>
+        <v>811969</v>
       </c>
       <c r="R27" t="n">
-        <v>7389623</v>
+        <v>7389545</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049633</v>
+        <v>127049609</v>
       </c>
       <c r="B28" t="n">
-        <v>78681</v>
+        <v>97327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811950</v>
+        <v>811991</v>
       </c>
       <c r="R28" t="n">
-        <v>7389574</v>
+        <v>7389623</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049642</v>
+        <v>127049643</v>
       </c>
       <c r="B29" t="n">
         <v>92616</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811969</v>
+        <v>811987</v>
       </c>
       <c r="R29" t="n">
-        <v>7389545</v>
+        <v>7389527</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,32 +3409,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049643</v>
+        <v>127049633</v>
       </c>
       <c r="B30" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811987</v>
+        <v>811950</v>
       </c>
       <c r="R30" t="n">
-        <v>7389527</v>
+        <v>7389574</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127049616</v>
+        <v>127049624</v>
       </c>
       <c r="B37" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811934</v>
+        <v>812000</v>
       </c>
       <c r="R37" t="n">
-        <v>7389548</v>
+        <v>7389736</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127049624</v>
+        <v>127049616</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>812000</v>
+        <v>811934</v>
       </c>
       <c r="R38" t="n">
-        <v>7389736</v>
+        <v>7389548</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4680,32 +4680,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127049634</v>
+        <v>127049615</v>
       </c>
       <c r="B43" t="n">
-        <v>92616</v>
+        <v>80989</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>812073</v>
+        <v>811948</v>
       </c>
       <c r="R43" t="n">
-        <v>7389533</v>
+        <v>7389545</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4777,32 +4777,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127049615</v>
+        <v>127049634</v>
       </c>
       <c r="B44" t="n">
-        <v>80989</v>
+        <v>92616</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811948</v>
+        <v>812073</v>
       </c>
       <c r="R44" t="n">
-        <v>7389545</v>
+        <v>7389533</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4874,32 +4874,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049614</v>
+        <v>127049641</v>
       </c>
       <c r="B45" t="n">
-        <v>80989</v>
+        <v>92616</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>812078</v>
+        <v>811963</v>
       </c>
       <c r="R45" t="n">
-        <v>7389625</v>
+        <v>7389548</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049626</v>
+        <v>127049606</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811984</v>
+        <v>812115</v>
       </c>
       <c r="R46" t="n">
-        <v>7389705</v>
+        <v>7389567</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,32 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049606</v>
+        <v>127049614</v>
       </c>
       <c r="B47" t="n">
-        <v>97327</v>
+        <v>80989</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>812115</v>
+        <v>812078</v>
       </c>
       <c r="R47" t="n">
-        <v>7389567</v>
+        <v>7389625</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5165,32 +5165,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127049641</v>
+        <v>127049626</v>
       </c>
       <c r="B48" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811963</v>
+        <v>811984</v>
       </c>
       <c r="R48" t="n">
-        <v>7389548</v>
+        <v>7389705</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B56" t="n">
-        <v>92616</v>
+        <v>78420</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R56" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,7 +6050,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271923</v>
+        <v>127271910</v>
       </c>
       <c r="B57" t="n">
         <v>92616</v>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811986</v>
+        <v>812192</v>
       </c>
       <c r="R57" t="n">
-        <v>7389610</v>
+        <v>7389757</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271925</v>
+        <v>127271923</v>
       </c>
       <c r="B58" t="n">
-        <v>78420</v>
+        <v>92616</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812066</v>
+        <v>811986</v>
       </c>
       <c r="R58" t="n">
-        <v>7389760</v>
+        <v>7389610</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271855</v>
+        <v>127271883</v>
       </c>
       <c r="B60" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6352,38 +6352,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811859</v>
+        <v>812004</v>
       </c>
       <c r="R60" t="n">
-        <v>7390026</v>
+        <v>7389960</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6416,11 +6412,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6447,32 +6438,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271883</v>
+        <v>127271911</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6482,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812004</v>
+        <v>812117</v>
       </c>
       <c r="R61" t="n">
-        <v>7389960</v>
+        <v>7389993</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6544,45 +6535,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271911</v>
+        <v>127271855</v>
       </c>
       <c r="B62" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812117</v>
+        <v>811859</v>
       </c>
       <c r="R62" t="n">
-        <v>7389993</v>
+        <v>7390026</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6615,6 +6610,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271876</v>
+        <v>127271886</v>
       </c>
       <c r="B66" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812128</v>
+        <v>811852</v>
       </c>
       <c r="R66" t="n">
-        <v>7390038</v>
+        <v>7390093</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7020,7 +7020,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7039,32 +7038,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271841</v>
+        <v>127271912</v>
       </c>
       <c r="B67" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7074,10 +7073,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812139</v>
+        <v>811981</v>
       </c>
       <c r="R67" t="n">
-        <v>7389967</v>
+        <v>7389988</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7136,32 +7135,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271842</v>
+        <v>127271921</v>
       </c>
       <c r="B68" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7171,10 +7170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812161</v>
+        <v>812092</v>
       </c>
       <c r="R68" t="n">
-        <v>7389878</v>
+        <v>7389721</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7233,32 +7232,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271886</v>
+        <v>127271909</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7268,10 +7267,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811852</v>
+        <v>812175</v>
       </c>
       <c r="R69" t="n">
-        <v>7390093</v>
+        <v>7389748</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7330,10 +7329,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271852</v>
+        <v>127271881</v>
       </c>
       <c r="B70" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7341,38 +7340,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812054</v>
+        <v>812133</v>
       </c>
       <c r="R70" t="n">
-        <v>7390009</v>
+        <v>7389830</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7405,11 +7400,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7436,32 +7426,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271912</v>
+        <v>127271876</v>
       </c>
       <c r="B71" t="n">
-        <v>92616</v>
+        <v>80989</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7471,10 +7461,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811981</v>
+        <v>812128</v>
       </c>
       <c r="R71" t="n">
-        <v>7389988</v>
+        <v>7390038</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7515,6 +7505,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7533,32 +7524,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271921</v>
+        <v>127271842</v>
       </c>
       <c r="B72" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7568,10 +7559,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812092</v>
+        <v>812161</v>
       </c>
       <c r="R72" t="n">
-        <v>7389721</v>
+        <v>7389878</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7630,32 +7621,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271909</v>
+        <v>127271841</v>
       </c>
       <c r="B73" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7665,10 +7656,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812175</v>
+        <v>812139</v>
       </c>
       <c r="R73" t="n">
-        <v>7389748</v>
+        <v>7389967</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7727,10 +7718,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271881</v>
+        <v>127271852</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7738,34 +7729,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812133</v>
+        <v>812054</v>
       </c>
       <c r="R74" t="n">
-        <v>7389830</v>
+        <v>7390009</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7798,6 +7793,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8018,49 +8018,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271851</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812117</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389911</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8093,11 +8089,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8124,49 +8115,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271865</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812024</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389558</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8199,11 +8186,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8230,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271917</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92616</v>
+        <v>91344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8265,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812088</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389936</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8327,45 +8309,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271908</v>
+        <v>127271851</v>
       </c>
       <c r="B80" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812128</v>
+        <v>812117</v>
       </c>
       <c r="R80" t="n">
-        <v>7389752</v>
+        <v>7389911</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8398,6 +8384,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8424,10 +8415,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271877</v>
+        <v>127271865</v>
       </c>
       <c r="B81" t="n">
-        <v>91344</v>
+        <v>57657</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8435,34 +8426,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812195</v>
+        <v>812024</v>
       </c>
       <c r="R81" t="n">
-        <v>7389776</v>
+        <v>7389558</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8495,6 +8490,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8812,10 +8812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271843</v>
+        <v>127271890</v>
       </c>
       <c r="B85" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812074</v>
+        <v>812121</v>
       </c>
       <c r="R85" t="n">
-        <v>7389829</v>
+        <v>7389928</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271890</v>
+        <v>127271843</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8920,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812121</v>
+        <v>812074</v>
       </c>
       <c r="R86" t="n">
-        <v>7389928</v>
+        <v>7389829</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271836</v>
+        <v>127271894</v>
       </c>
       <c r="B90" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,21 +9313,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811958</v>
+        <v>811982</v>
       </c>
       <c r="R90" t="n">
-        <v>7389950</v>
+        <v>7389609</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271849</v>
+        <v>127271836</v>
       </c>
       <c r="B91" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9410,21 +9410,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>812114</v>
+        <v>811958</v>
       </c>
       <c r="R91" t="n">
-        <v>7389969</v>
+        <v>7389950</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9470,11 +9470,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9607,10 +9602,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271894</v>
+        <v>127271849</v>
       </c>
       <c r="B93" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9618,21 +9613,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9642,10 +9637,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811982</v>
+        <v>812114</v>
       </c>
       <c r="R93" t="n">
-        <v>7389609</v>
+        <v>7389969</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9678,6 +9673,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271868</v>
+        <v>127271856</v>
       </c>
       <c r="B95" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,34 +9812,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812092</v>
+        <v>811876</v>
       </c>
       <c r="R95" t="n">
-        <v>7389656</v>
+        <v>7389968</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9872,6 +9876,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9898,7 +9907,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271856</v>
+        <v>127271857</v>
       </c>
       <c r="B96" t="n">
         <v>57657</v>
@@ -9927,20 +9936,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811876</v>
+        <v>812050</v>
       </c>
       <c r="R96" t="n">
-        <v>7389968</v>
+        <v>7389925</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9973,11 +9978,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271857</v>
+        <v>127271868</v>
       </c>
       <c r="B97" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812050</v>
+        <v>812092</v>
       </c>
       <c r="R97" t="n">
-        <v>7389925</v>
+        <v>7389656</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10295,49 +10295,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271864</v>
+        <v>127271907</v>
       </c>
       <c r="B100" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812087</v>
+        <v>812162</v>
       </c>
       <c r="R100" t="n">
-        <v>7389653</v>
+        <v>7389625</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10370,11 +10366,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10401,32 +10392,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271907</v>
+        <v>127271893</v>
       </c>
       <c r="B101" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10436,10 +10427,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>812162</v>
+        <v>812066</v>
       </c>
       <c r="R101" t="n">
-        <v>7389625</v>
+        <v>7389634</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10498,32 +10489,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271893</v>
+        <v>127271916</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10533,10 +10524,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>812066</v>
+        <v>811958</v>
       </c>
       <c r="R102" t="n">
-        <v>7389634</v>
+        <v>7389946</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10595,32 +10586,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271916</v>
+        <v>127271884</v>
       </c>
       <c r="B103" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10630,10 +10621,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811958</v>
+        <v>811977</v>
       </c>
       <c r="R103" t="n">
-        <v>7389946</v>
+        <v>7389985</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10692,10 +10683,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271884</v>
+        <v>127271864</v>
       </c>
       <c r="B104" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10703,34 +10694,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811977</v>
+        <v>812087</v>
       </c>
       <c r="R104" t="n">
-        <v>7389985</v>
+        <v>7389653</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10763,6 +10758,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,49 +10789,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271853</v>
+        <v>127271913</v>
       </c>
       <c r="B105" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811970</v>
+        <v>811963</v>
       </c>
       <c r="R105" t="n">
-        <v>7390085</v>
+        <v>7390029</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10864,11 +10860,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10895,32 +10886,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271913</v>
+        <v>127271892</v>
       </c>
       <c r="B106" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10930,10 +10921,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811963</v>
+        <v>812106</v>
       </c>
       <c r="R106" t="n">
-        <v>7390029</v>
+        <v>7389684</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10992,7 +10983,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271892</v>
+        <v>127271879</v>
       </c>
       <c r="B107" t="n">
         <v>79014</v>
@@ -11027,10 +11018,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812106</v>
+        <v>812228</v>
       </c>
       <c r="R107" t="n">
-        <v>7389684</v>
+        <v>7389839</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11089,32 +11080,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271879</v>
+        <v>127271906</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11124,10 +11115,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812228</v>
+        <v>812166</v>
       </c>
       <c r="R108" t="n">
-        <v>7389839</v>
+        <v>7389625</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11186,32 +11177,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271906</v>
+        <v>127271844</v>
       </c>
       <c r="B109" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11221,10 +11212,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812166</v>
+        <v>812114</v>
       </c>
       <c r="R109" t="n">
-        <v>7389625</v>
+        <v>7389680</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11283,10 +11274,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271844</v>
+        <v>127271853</v>
       </c>
       <c r="B110" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11294,34 +11285,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>812114</v>
+        <v>811970</v>
       </c>
       <c r="R110" t="n">
-        <v>7389680</v>
+        <v>7390085</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11354,6 +11349,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11380,32 +11380,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271885</v>
+        <v>127271922</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811960</v>
+        <v>812120</v>
       </c>
       <c r="R111" t="n">
-        <v>7390029</v>
+        <v>7389691</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11477,10 +11477,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271860</v>
+        <v>127271885</v>
       </c>
       <c r="B112" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11488,38 +11488,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>812080</v>
+        <v>811960</v>
       </c>
       <c r="R112" t="n">
-        <v>7389823</v>
+        <v>7390029</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11552,11 +11548,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11583,45 +11574,49 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127271922</v>
+        <v>127271860</v>
       </c>
       <c r="B113" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>812120</v>
+        <v>812080</v>
       </c>
       <c r="R113" t="n">
-        <v>7389691</v>
+        <v>7389823</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11654,6 +11649,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11680,10 +11680,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271862</v>
+        <v>127271887</v>
       </c>
       <c r="B114" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11691,38 +11691,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>812079</v>
+        <v>811866</v>
       </c>
       <c r="R114" t="n">
-        <v>7389800</v>
+        <v>7390052</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11755,11 +11751,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11786,32 +11777,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271887</v>
+        <v>127271919</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11821,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811866</v>
+        <v>812158</v>
       </c>
       <c r="R115" t="n">
-        <v>7390052</v>
+        <v>7389883</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11883,7 +11874,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271919</v>
+        <v>127271914</v>
       </c>
       <c r="B116" t="n">
         <v>92616</v>
@@ -11918,10 +11909,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>812158</v>
+        <v>811875</v>
       </c>
       <c r="R116" t="n">
-        <v>7389883</v>
+        <v>7389980</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11980,10 +11971,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271914</v>
+        <v>127271866</v>
       </c>
       <c r="B117" t="n">
-        <v>92616</v>
+        <v>56849</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11991,21 +11982,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12015,10 +12006,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811875</v>
+        <v>811935</v>
       </c>
       <c r="R117" t="n">
-        <v>7389980</v>
+        <v>7389957</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12077,45 +12068,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271866</v>
+        <v>127271862</v>
       </c>
       <c r="B118" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811935</v>
+        <v>812079</v>
       </c>
       <c r="R118" t="n">
-        <v>7389957</v>
+        <v>7389800</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12148,6 +12143,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12174,49 +12174,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271861</v>
+        <v>127271918</v>
       </c>
       <c r="B119" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812106</v>
+        <v>812162</v>
       </c>
       <c r="R119" t="n">
-        <v>7389819</v>
+        <v>7389925</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12249,11 +12245,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12280,7 +12271,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271850</v>
+        <v>127271861</v>
       </c>
       <c r="B120" t="n">
         <v>57657</v>
@@ -12319,10 +12310,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812124</v>
+        <v>812106</v>
       </c>
       <c r="R120" t="n">
-        <v>7389758</v>
+        <v>7389819</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12359,7 +12350,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Mellersta området</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12386,45 +12377,49 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271918</v>
+        <v>127271850</v>
       </c>
       <c r="B121" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812162</v>
+        <v>812124</v>
       </c>
       <c r="R121" t="n">
-        <v>7389925</v>
+        <v>7389758</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12457,6 +12452,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049601</v>
+        <v>127049630</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,38 +2247,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811940</v>
+        <v>812021</v>
       </c>
       <c r="R18" t="n">
-        <v>7389556</v>
+        <v>7389474</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2311,11 +2307,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2342,7 +2333,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049630</v>
+        <v>127049622</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2377,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812021</v>
+        <v>812088</v>
       </c>
       <c r="R19" t="n">
-        <v>7389474</v>
+        <v>7389588</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2439,7 +2430,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127049622</v>
+        <v>127049631</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2474,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>812088</v>
+        <v>812026</v>
       </c>
       <c r="R20" t="n">
-        <v>7389588</v>
+        <v>7389461</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,10 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127049631</v>
+        <v>127049601</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2547,34 +2538,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>812026</v>
+        <v>811940</v>
       </c>
       <c r="R21" t="n">
-        <v>7389461</v>
+        <v>7389556</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2607,6 +2602,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4874,10 +4874,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049641</v>
+        <v>127049606</v>
       </c>
       <c r="B45" t="n">
-        <v>92616</v>
+        <v>97327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811963</v>
+        <v>812115</v>
       </c>
       <c r="R45" t="n">
-        <v>7389548</v>
+        <v>7389567</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049606</v>
+        <v>127049614</v>
       </c>
       <c r="B46" t="n">
-        <v>97327</v>
+        <v>80989</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>812115</v>
+        <v>812078</v>
       </c>
       <c r="R46" t="n">
-        <v>7389567</v>
+        <v>7389625</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,32 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049614</v>
+        <v>127049641</v>
       </c>
       <c r="B47" t="n">
-        <v>80989</v>
+        <v>92616</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>812078</v>
+        <v>811963</v>
       </c>
       <c r="R47" t="n">
-        <v>7389625</v>
+        <v>7389548</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271886</v>
+        <v>127271842</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811852</v>
+        <v>812161</v>
       </c>
       <c r="R66" t="n">
-        <v>7390093</v>
+        <v>7389878</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7038,32 +7038,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271912</v>
+        <v>127271841</v>
       </c>
       <c r="B67" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811981</v>
+        <v>812139</v>
       </c>
       <c r="R67" t="n">
-        <v>7389988</v>
+        <v>7389967</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7135,32 +7135,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271921</v>
+        <v>127271886</v>
       </c>
       <c r="B68" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812092</v>
+        <v>811852</v>
       </c>
       <c r="R68" t="n">
-        <v>7389721</v>
+        <v>7390093</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271909</v>
+        <v>127271912</v>
       </c>
       <c r="B69" t="n">
         <v>92616</v>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812175</v>
+        <v>811981</v>
       </c>
       <c r="R69" t="n">
-        <v>7389748</v>
+        <v>7389988</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,32 +7329,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271881</v>
+        <v>127271921</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812133</v>
+        <v>812092</v>
       </c>
       <c r="R70" t="n">
-        <v>7389830</v>
+        <v>7389721</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7426,32 +7426,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271876</v>
+        <v>127271909</v>
       </c>
       <c r="B71" t="n">
-        <v>80989</v>
+        <v>92616</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812128</v>
+        <v>812175</v>
       </c>
       <c r="R71" t="n">
-        <v>7390038</v>
+        <v>7389748</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7505,7 +7505,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7524,10 +7523,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271842</v>
+        <v>127271881</v>
       </c>
       <c r="B72" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7535,21 +7534,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7559,10 +7558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812161</v>
+        <v>812133</v>
       </c>
       <c r="R72" t="n">
-        <v>7389878</v>
+        <v>7389830</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7621,10 +7620,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271841</v>
+        <v>127271876</v>
       </c>
       <c r="B73" t="n">
-        <v>79632</v>
+        <v>80989</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7632,21 +7631,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7656,10 +7655,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812139</v>
+        <v>812128</v>
       </c>
       <c r="R73" t="n">
-        <v>7389967</v>
+        <v>7390038</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7700,6 +7699,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271840</v>
+        <v>127271868</v>
       </c>
       <c r="B94" t="n">
-        <v>79632</v>
+        <v>57817</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812127</v>
+        <v>812092</v>
       </c>
       <c r="R94" t="n">
-        <v>7389936</v>
+        <v>7389656</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271856</v>
+        <v>127271840</v>
       </c>
       <c r="B95" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,38 +9812,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811876</v>
+        <v>812127</v>
       </c>
       <c r="R95" t="n">
-        <v>7389968</v>
+        <v>7389936</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9876,11 +9872,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9907,7 +9898,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271857</v>
+        <v>127271856</v>
       </c>
       <c r="B96" t="n">
         <v>57657</v>
@@ -9936,16 +9927,20 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812050</v>
+        <v>811876</v>
       </c>
       <c r="R96" t="n">
-        <v>7389925</v>
+        <v>7389968</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9978,6 +9973,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271868</v>
+        <v>127271857</v>
       </c>
       <c r="B97" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812092</v>
+        <v>812050</v>
       </c>
       <c r="R97" t="n">
-        <v>7389656</v>
+        <v>7389925</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049592</v>
+        <v>127049602</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812072</v>
+        <v>812043</v>
       </c>
       <c r="R3" t="n">
-        <v>7389539</v>
+        <v>7389685</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -843,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,49 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049602</v>
+        <v>127049608</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>97327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812043</v>
+        <v>812055</v>
       </c>
       <c r="R4" t="n">
-        <v>7389685</v>
+        <v>7389491</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -944,11 +949,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,32 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049608</v>
+        <v>127049592</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812055</v>
+        <v>812072</v>
       </c>
       <c r="R5" t="n">
-        <v>7389491</v>
+        <v>7389539</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049638</v>
+        <v>127049611</v>
       </c>
       <c r="B6" t="n">
-        <v>92616</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811921</v>
+        <v>812004</v>
       </c>
       <c r="R6" t="n">
-        <v>7389590</v>
+        <v>7389528</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049639</v>
+        <v>127049638</v>
       </c>
       <c r="B7" t="n">
         <v>92616</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811937</v>
+        <v>811921</v>
       </c>
       <c r="R7" t="n">
-        <v>7389558</v>
+        <v>7389590</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049611</v>
+        <v>127049639</v>
       </c>
       <c r="B8" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>812004</v>
+        <v>811937</v>
       </c>
       <c r="R8" t="n">
-        <v>7389528</v>
+        <v>7389558</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049596</v>
+        <v>127049618</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811955</v>
+        <v>812047</v>
       </c>
       <c r="R12" t="n">
-        <v>7389537</v>
+        <v>7389473</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049618</v>
+        <v>127049620</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>812047</v>
+        <v>812079</v>
       </c>
       <c r="R13" t="n">
-        <v>7389473</v>
+        <v>7389510</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049620</v>
+        <v>127049628</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>812079</v>
+        <v>811980</v>
       </c>
       <c r="R14" t="n">
-        <v>7389510</v>
+        <v>7389540</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049628</v>
+        <v>127049596</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811980</v>
+        <v>811955</v>
       </c>
       <c r="R15" t="n">
-        <v>7389540</v>
+        <v>7389537</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127049645</v>
+        <v>127049623</v>
       </c>
       <c r="B16" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>812008</v>
+        <v>812077</v>
       </c>
       <c r="R16" t="n">
-        <v>7389456</v>
+        <v>7389513</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127049623</v>
+        <v>127049645</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>812077</v>
+        <v>812008</v>
       </c>
       <c r="R17" t="n">
-        <v>7389513</v>
+        <v>7389456</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049642</v>
+        <v>127049643</v>
       </c>
       <c r="B27" t="n">
         <v>92616</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811969</v>
+        <v>811987</v>
       </c>
       <c r="R27" t="n">
-        <v>7389545</v>
+        <v>7389527</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049609</v>
+        <v>127049642</v>
       </c>
       <c r="B28" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3226,21 +3226,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811991</v>
+        <v>811969</v>
       </c>
       <c r="R28" t="n">
-        <v>7389623</v>
+        <v>7389545</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,32 +3312,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049643</v>
+        <v>127049633</v>
       </c>
       <c r="B29" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811987</v>
+        <v>811950</v>
       </c>
       <c r="R29" t="n">
-        <v>7389527</v>
+        <v>7389574</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,32 +3409,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049633</v>
+        <v>127049609</v>
       </c>
       <c r="B30" t="n">
-        <v>78681</v>
+        <v>97327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811950</v>
+        <v>811991</v>
       </c>
       <c r="R30" t="n">
-        <v>7389574</v>
+        <v>7389623</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049594</v>
+        <v>127049610</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811945</v>
+        <v>811967</v>
       </c>
       <c r="R31" t="n">
-        <v>7389563</v>
+        <v>7389626</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049610</v>
+        <v>127049594</v>
       </c>
       <c r="B32" t="n">
-        <v>97327</v>
+        <v>79632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811967</v>
+        <v>811945</v>
       </c>
       <c r="R32" t="n">
-        <v>7389626</v>
+        <v>7389563</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4874,10 +4874,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049606</v>
+        <v>127049641</v>
       </c>
       <c r="B45" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>812115</v>
+        <v>811963</v>
       </c>
       <c r="R45" t="n">
-        <v>7389567</v>
+        <v>7389548</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049614</v>
+        <v>127049606</v>
       </c>
       <c r="B46" t="n">
-        <v>80989</v>
+        <v>97327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>221941</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>812078</v>
+        <v>812115</v>
       </c>
       <c r="R46" t="n">
-        <v>7389625</v>
+        <v>7389567</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,32 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049641</v>
+        <v>127049614</v>
       </c>
       <c r="B47" t="n">
-        <v>92616</v>
+        <v>80989</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811963</v>
+        <v>812078</v>
       </c>
       <c r="R47" t="n">
-        <v>7389548</v>
+        <v>7389625</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271925</v>
+        <v>127271847</v>
       </c>
       <c r="B56" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812066</v>
+        <v>812034</v>
       </c>
       <c r="R56" t="n">
-        <v>7389760</v>
+        <v>7389561</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B57" t="n">
-        <v>92616</v>
+        <v>78420</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R57" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,7 +6147,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271923</v>
+        <v>127271910</v>
       </c>
       <c r="B58" t="n">
         <v>92616</v>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811986</v>
+        <v>812192</v>
       </c>
       <c r="R58" t="n">
-        <v>7389610</v>
+        <v>7389757</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B59" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R59" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,32 +6341,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271883</v>
+        <v>127271875</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812004</v>
+        <v>812093</v>
       </c>
       <c r="R60" t="n">
-        <v>7389960</v>
+        <v>7389656</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6438,32 +6438,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271911</v>
+        <v>127271883</v>
       </c>
       <c r="B61" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812117</v>
+        <v>812004</v>
       </c>
       <c r="R61" t="n">
-        <v>7389993</v>
+        <v>7389960</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6535,49 +6535,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271855</v>
+        <v>127271911</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811859</v>
+        <v>812117</v>
       </c>
       <c r="R62" t="n">
-        <v>7390026</v>
+        <v>7389993</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6610,11 +6606,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6641,27 +6632,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271875</v>
+        <v>127271855</v>
       </c>
       <c r="B63" t="n">
-        <v>58027</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6670,16 +6661,20 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812093</v>
+        <v>811859</v>
       </c>
       <c r="R63" t="n">
-        <v>7389656</v>
+        <v>7390026</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6712,6 +6707,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271842</v>
+        <v>127271886</v>
       </c>
       <c r="B66" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812161</v>
+        <v>811852</v>
       </c>
       <c r="R66" t="n">
-        <v>7389878</v>
+        <v>7390093</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7038,32 +7038,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271841</v>
+        <v>127271912</v>
       </c>
       <c r="B67" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812139</v>
+        <v>811981</v>
       </c>
       <c r="R67" t="n">
-        <v>7389967</v>
+        <v>7389988</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7135,32 +7135,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271886</v>
+        <v>127271921</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811852</v>
+        <v>812092</v>
       </c>
       <c r="R68" t="n">
-        <v>7390093</v>
+        <v>7389721</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271912</v>
+        <v>127271909</v>
       </c>
       <c r="B69" t="n">
         <v>92616</v>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811981</v>
+        <v>812175</v>
       </c>
       <c r="R69" t="n">
-        <v>7389988</v>
+        <v>7389748</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,32 +7329,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271921</v>
+        <v>127271881</v>
       </c>
       <c r="B70" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812092</v>
+        <v>812133</v>
       </c>
       <c r="R70" t="n">
-        <v>7389721</v>
+        <v>7389830</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7426,32 +7426,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271909</v>
+        <v>127271876</v>
       </c>
       <c r="B71" t="n">
-        <v>92616</v>
+        <v>80989</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812175</v>
+        <v>812128</v>
       </c>
       <c r="R71" t="n">
-        <v>7389748</v>
+        <v>7390038</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7505,6 +7505,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7523,10 +7524,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271881</v>
+        <v>127271842</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7534,21 +7535,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7558,10 +7559,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812133</v>
+        <v>812161</v>
       </c>
       <c r="R72" t="n">
-        <v>7389830</v>
+        <v>7389878</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7620,10 +7621,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271876</v>
+        <v>127271841</v>
       </c>
       <c r="B73" t="n">
-        <v>80989</v>
+        <v>79632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7631,21 +7632,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7655,10 +7656,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812128</v>
+        <v>812139</v>
       </c>
       <c r="R73" t="n">
-        <v>7390038</v>
+        <v>7389967</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7699,7 +7700,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8018,45 +8018,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127271851</v>
       </c>
       <c r="B77" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>812117</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389911</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8089,6 +8093,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8115,45 +8124,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127271865</v>
       </c>
       <c r="B78" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>812024</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389558</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8186,6 +8199,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8212,32 +8230,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271917</v>
       </c>
       <c r="B79" t="n">
-        <v>91344</v>
+        <v>92616</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8265,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>812088</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389936</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8309,49 +8327,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271851</v>
+        <v>127271908</v>
       </c>
       <c r="B80" t="n">
-        <v>57657</v>
+        <v>92616</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812117</v>
+        <v>812128</v>
       </c>
       <c r="R80" t="n">
-        <v>7389911</v>
+        <v>7389752</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8384,11 +8398,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8415,10 +8424,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271865</v>
+        <v>127271877</v>
       </c>
       <c r="B81" t="n">
-        <v>57657</v>
+        <v>91344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8426,38 +8435,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812024</v>
+        <v>812195</v>
       </c>
       <c r="R81" t="n">
-        <v>7389558</v>
+        <v>7389776</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8490,11 +8495,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127271874</v>
+        <v>127271915</v>
       </c>
       <c r="B98" t="n">
-        <v>57761</v>
+        <v>92616</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10112,21 +10112,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>812168</v>
+        <v>811935</v>
       </c>
       <c r="R98" t="n">
-        <v>7389829</v>
+        <v>7389943</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10198,10 +10198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127271915</v>
+        <v>127271874</v>
       </c>
       <c r="B99" t="n">
-        <v>92616</v>
+        <v>57761</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10209,21 +10209,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811935</v>
+        <v>812168</v>
       </c>
       <c r="R99" t="n">
-        <v>7389943</v>
+        <v>7389829</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11177,10 +11177,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271844</v>
+        <v>127271853</v>
       </c>
       <c r="B109" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11188,34 +11188,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812114</v>
+        <v>811970</v>
       </c>
       <c r="R109" t="n">
-        <v>7389680</v>
+        <v>7390085</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11248,6 +11252,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11274,10 +11283,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271853</v>
+        <v>127271844</v>
       </c>
       <c r="B110" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11285,38 +11294,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811970</v>
+        <v>812114</v>
       </c>
       <c r="R110" t="n">
-        <v>7390085</v>
+        <v>7389680</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11349,11 +11354,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11971,45 +11971,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271866</v>
+        <v>127271862</v>
       </c>
       <c r="B117" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811935</v>
+        <v>812079</v>
       </c>
       <c r="R117" t="n">
-        <v>7389957</v>
+        <v>7389800</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12042,6 +12046,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12068,49 +12077,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271862</v>
+        <v>127271866</v>
       </c>
       <c r="B118" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>812079</v>
+        <v>811935</v>
       </c>
       <c r="R118" t="n">
-        <v>7389800</v>
+        <v>7389957</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12143,11 +12148,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127049629</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049602</v>
+        <v>127049592</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812043</v>
+        <v>812072</v>
       </c>
       <c r="R3" t="n">
-        <v>7389685</v>
+        <v>7389539</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +872,7 @@
         <v>127049608</v>
       </c>
       <c r="B4" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049592</v>
+        <v>127049602</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812072</v>
+        <v>812043</v>
       </c>
       <c r="R5" t="n">
-        <v>7389539</v>
+        <v>7389685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1046,6 +1041,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1075,7 +1075,7 @@
         <v>127049611</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127049638</v>
       </c>
       <c r="B7" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127049639</v>
       </c>
       <c r="B8" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127049621</v>
+        <v>127049595</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>812153</v>
+        <v>811948</v>
       </c>
       <c r="R9" t="n">
-        <v>7389594</v>
+        <v>7389545</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127049595</v>
+        <v>127049621</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811948</v>
+        <v>812153</v>
       </c>
       <c r="R10" t="n">
-        <v>7389545</v>
+        <v>7389594</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1560,7 +1560,7 @@
         <v>127049612</v>
       </c>
       <c r="B11" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>127049618</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>127049620</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>127049628</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127049596</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127049623</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127049645</v>
       </c>
       <c r="B17" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>127049630</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>127049622</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>127049631</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>127049601</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049640</v>
+        <v>127049593</v>
       </c>
       <c r="B22" t="n">
-        <v>92616</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R22" t="n">
-        <v>7389556</v>
+        <v>7389548</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2733,7 +2733,7 @@
         <v>127049637</v>
       </c>
       <c r="B23" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2827,32 +2827,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127049593</v>
+        <v>127049640</v>
       </c>
       <c r="B24" t="n">
-        <v>79632</v>
+        <v>92620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R24" t="n">
-        <v>7389548</v>
+        <v>7389556</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2927,7 +2927,7 @@
         <v>127049613</v>
       </c>
       <c r="B25" t="n">
-        <v>80989</v>
+        <v>80993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127049605</v>
       </c>
       <c r="B26" t="n">
-        <v>92644</v>
+        <v>92648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049643</v>
+        <v>127049609</v>
       </c>
       <c r="B27" t="n">
-        <v>92616</v>
+        <v>97331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811987</v>
+        <v>811991</v>
       </c>
       <c r="R27" t="n">
-        <v>7389527</v>
+        <v>7389623</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049642</v>
+        <v>127049633</v>
       </c>
       <c r="B28" t="n">
-        <v>92616</v>
+        <v>78685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811969</v>
+        <v>811950</v>
       </c>
       <c r="R28" t="n">
-        <v>7389545</v>
+        <v>7389574</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,32 +3312,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049633</v>
+        <v>127049642</v>
       </c>
       <c r="B29" t="n">
-        <v>78681</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811950</v>
+        <v>811969</v>
       </c>
       <c r="R29" t="n">
-        <v>7389574</v>
+        <v>7389545</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049609</v>
+        <v>127049643</v>
       </c>
       <c r="B30" t="n">
-        <v>97327</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811991</v>
+        <v>811987</v>
       </c>
       <c r="R30" t="n">
-        <v>7389623</v>
+        <v>7389527</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049610</v>
+        <v>127049594</v>
       </c>
       <c r="B31" t="n">
-        <v>97327</v>
+        <v>79636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811967</v>
+        <v>811945</v>
       </c>
       <c r="R31" t="n">
-        <v>7389626</v>
+        <v>7389563</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049594</v>
+        <v>127049610</v>
       </c>
       <c r="B32" t="n">
-        <v>79632</v>
+        <v>97331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811945</v>
+        <v>811967</v>
       </c>
       <c r="R32" t="n">
-        <v>7389563</v>
+        <v>7389626</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3700,32 +3700,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127049635</v>
+        <v>127049625</v>
       </c>
       <c r="B33" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>812027</v>
+        <v>811987</v>
       </c>
       <c r="R33" t="n">
-        <v>7389564</v>
+        <v>7389722</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049625</v>
+        <v>127049635</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811987</v>
+        <v>812027</v>
       </c>
       <c r="R34" t="n">
-        <v>7389722</v>
+        <v>7389564</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3897,7 +3897,7 @@
         <v>127049619</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127049607</v>
       </c>
       <c r="B36" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>127049624</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127049616</v>
       </c>
       <c r="B38" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127049648</v>
       </c>
       <c r="B39" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>127049591</v>
       </c>
       <c r="B40" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>127049647</v>
       </c>
       <c r="B41" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>127049632</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>127049615</v>
       </c>
       <c r="B43" t="n">
-        <v>80989</v>
+        <v>80993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>127049634</v>
       </c>
       <c r="B44" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4874,32 +4874,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049641</v>
+        <v>127049614</v>
       </c>
       <c r="B45" t="n">
-        <v>92616</v>
+        <v>80993</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811963</v>
+        <v>812078</v>
       </c>
       <c r="R45" t="n">
-        <v>7389548</v>
+        <v>7389625</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049606</v>
+        <v>127049626</v>
       </c>
       <c r="B46" t="n">
-        <v>97327</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>812115</v>
+        <v>811984</v>
       </c>
       <c r="R46" t="n">
-        <v>7389567</v>
+        <v>7389705</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,32 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049614</v>
+        <v>127049641</v>
       </c>
       <c r="B47" t="n">
-        <v>80989</v>
+        <v>92620</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>812078</v>
+        <v>811963</v>
       </c>
       <c r="R47" t="n">
-        <v>7389625</v>
+        <v>7389548</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5165,32 +5165,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127049626</v>
+        <v>127049606</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>97331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811984</v>
+        <v>812115</v>
       </c>
       <c r="R48" t="n">
-        <v>7389705</v>
+        <v>7389567</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5265,7 +5265,7 @@
         <v>127049600</v>
       </c>
       <c r="B49" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>127049598</v>
       </c>
       <c r="B50" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>127049599</v>
       </c>
       <c r="B51" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>127271845</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>127271854</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>127271889</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127271920</v>
       </c>
       <c r="B55" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271847</v>
+        <v>127271925</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>78424</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5964,21 +5964,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812034</v>
+        <v>812066</v>
       </c>
       <c r="R56" t="n">
-        <v>7389561</v>
+        <v>7389760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271925</v>
+        <v>127271847</v>
       </c>
       <c r="B57" t="n">
-        <v>78420</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812066</v>
+        <v>812034</v>
       </c>
       <c r="R57" t="n">
-        <v>7389760</v>
+        <v>7389561</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6150,7 +6150,7 @@
         <v>127271910</v>
       </c>
       <c r="B58" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>127271923</v>
       </c>
       <c r="B59" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271875</v>
+        <v>127271911</v>
       </c>
       <c r="B60" t="n">
-        <v>58027</v>
+        <v>92620</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6352,21 +6352,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812093</v>
+        <v>812117</v>
       </c>
       <c r="R60" t="n">
-        <v>7389656</v>
+        <v>7389993</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271883</v>
+        <v>127271855</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,34 +6449,38 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812004</v>
+        <v>811859</v>
       </c>
       <c r="R61" t="n">
-        <v>7389960</v>
+        <v>7390026</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6509,6 +6513,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6535,10 +6544,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271911</v>
+        <v>127271875</v>
       </c>
       <c r="B62" t="n">
-        <v>92616</v>
+        <v>58031</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,21 +6555,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6579,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812117</v>
+        <v>812093</v>
       </c>
       <c r="R62" t="n">
-        <v>7389993</v>
+        <v>7389656</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6632,10 +6641,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271855</v>
+        <v>127271883</v>
       </c>
       <c r="B63" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6643,38 +6652,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811859</v>
+        <v>812004</v>
       </c>
       <c r="R63" t="n">
-        <v>7390026</v>
+        <v>7389960</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6707,11 +6712,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271858</v>
+        <v>127271888</v>
       </c>
       <c r="B64" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,38 +6749,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>812068</v>
+        <v>811957</v>
       </c>
       <c r="R64" t="n">
-        <v>7389929</v>
+        <v>7389943</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6813,11 +6809,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6844,10 +6835,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271888</v>
+        <v>127271858</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6855,34 +6846,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811957</v>
+        <v>812068</v>
       </c>
       <c r="R65" t="n">
-        <v>7389943</v>
+        <v>7389929</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6915,6 +6910,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271886</v>
+        <v>127271852</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,34 +6952,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811852</v>
+        <v>812054</v>
       </c>
       <c r="R66" t="n">
-        <v>7390093</v>
+        <v>7390009</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7012,6 +7016,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7038,32 +7047,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271912</v>
+        <v>127271876</v>
       </c>
       <c r="B67" t="n">
-        <v>92616</v>
+        <v>80993</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811981</v>
+        <v>812128</v>
       </c>
       <c r="R67" t="n">
-        <v>7389988</v>
+        <v>7390038</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7117,6 +7126,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7135,32 +7145,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271921</v>
+        <v>127271841</v>
       </c>
       <c r="B68" t="n">
-        <v>92616</v>
+        <v>79636</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7170,10 +7180,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812092</v>
+        <v>812139</v>
       </c>
       <c r="R68" t="n">
-        <v>7389721</v>
+        <v>7389967</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,32 +7242,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271909</v>
+        <v>127271842</v>
       </c>
       <c r="B69" t="n">
-        <v>92616</v>
+        <v>79636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7267,10 +7277,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812175</v>
+        <v>812161</v>
       </c>
       <c r="R69" t="n">
-        <v>7389748</v>
+        <v>7389878</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,10 +7339,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271881</v>
+        <v>127271886</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7364,10 +7374,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812133</v>
+        <v>811852</v>
       </c>
       <c r="R70" t="n">
-        <v>7389830</v>
+        <v>7390093</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7426,10 +7436,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271876</v>
+        <v>127271881</v>
       </c>
       <c r="B71" t="n">
-        <v>80989</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7437,21 +7447,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7461,10 +7471,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812128</v>
+        <v>812133</v>
       </c>
       <c r="R71" t="n">
-        <v>7390038</v>
+        <v>7389830</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7505,7 +7515,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7524,32 +7533,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271842</v>
+        <v>127271912</v>
       </c>
       <c r="B72" t="n">
-        <v>79632</v>
+        <v>92620</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7559,10 +7568,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812161</v>
+        <v>811981</v>
       </c>
       <c r="R72" t="n">
-        <v>7389878</v>
+        <v>7389988</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7621,32 +7630,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271841</v>
+        <v>127271921</v>
       </c>
       <c r="B73" t="n">
-        <v>79632</v>
+        <v>92620</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7656,10 +7665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812139</v>
+        <v>812092</v>
       </c>
       <c r="R73" t="n">
-        <v>7389967</v>
+        <v>7389721</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7718,49 +7727,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271852</v>
+        <v>127271909</v>
       </c>
       <c r="B74" t="n">
-        <v>57657</v>
+        <v>92620</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812054</v>
+        <v>812175</v>
       </c>
       <c r="R74" t="n">
-        <v>7390009</v>
+        <v>7389748</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7793,11 +7798,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7827,7 +7827,7 @@
         <v>127271880</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>127271924</v>
       </c>
       <c r="B76" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,49 +8018,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271851</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>57657</v>
+        <v>92620</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812117</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389911</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8093,11 +8089,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8124,49 +8115,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271865</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
-        <v>57657</v>
+        <v>92620</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812024</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389558</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8199,11 +8186,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8230,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271917</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92616</v>
+        <v>91348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8265,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812088</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389936</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8327,45 +8309,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271908</v>
+        <v>127271851</v>
       </c>
       <c r="B80" t="n">
-        <v>92616</v>
+        <v>57661</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812128</v>
+        <v>812117</v>
       </c>
       <c r="R80" t="n">
-        <v>7389752</v>
+        <v>7389911</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8398,6 +8384,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8424,10 +8415,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271877</v>
+        <v>127271865</v>
       </c>
       <c r="B81" t="n">
-        <v>91344</v>
+        <v>57661</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8435,34 +8426,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812195</v>
+        <v>812024</v>
       </c>
       <c r="R81" t="n">
-        <v>7389776</v>
+        <v>7389558</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8495,6 +8490,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8524,7 +8524,7 @@
         <v>127271895</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>127271878</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>127271882</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271890</v>
+        <v>127271843</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812121</v>
+        <v>812074</v>
       </c>
       <c r="R85" t="n">
-        <v>7389928</v>
+        <v>7389829</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271843</v>
+        <v>127271890</v>
       </c>
       <c r="B86" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8920,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812074</v>
+        <v>812121</v>
       </c>
       <c r="R86" t="n">
-        <v>7389829</v>
+        <v>7389928</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B87" t="n">
-        <v>57654</v>
+        <v>79636</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R87" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,11 +9077,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9108,10 +9103,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B88" t="n">
-        <v>79632</v>
+        <v>57658</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9119,21 +9114,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R88" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9179,6 +9174,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9208,7 +9208,7 @@
         <v>127271891</v>
       </c>
       <c r="B89" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271894</v>
+        <v>127271836</v>
       </c>
       <c r="B90" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,21 +9313,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811982</v>
+        <v>811958</v>
       </c>
       <c r="R90" t="n">
-        <v>7389609</v>
+        <v>7389950</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271836</v>
+        <v>127271894</v>
       </c>
       <c r="B91" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9410,21 +9410,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811958</v>
+        <v>811982</v>
       </c>
       <c r="R91" t="n">
-        <v>7389950</v>
+        <v>7389609</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9496,10 +9496,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271897</v>
+        <v>127271849</v>
       </c>
       <c r="B92" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9524,21 +9524,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>812122</v>
+        <v>812114</v>
       </c>
       <c r="R92" t="n">
-        <v>7389709</v>
+        <v>7389969</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9575,7 +9571,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Observerad och filmad under födosök.</t>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9602,10 +9598,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271849</v>
+        <v>127271897</v>
       </c>
       <c r="B93" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9630,17 +9626,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>812114</v>
+        <v>812122</v>
       </c>
       <c r="R93" t="n">
-        <v>7389969</v>
+        <v>7389709</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271868</v>
+        <v>127271840</v>
       </c>
       <c r="B94" t="n">
-        <v>57817</v>
+        <v>79636</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812092</v>
+        <v>812127</v>
       </c>
       <c r="R94" t="n">
-        <v>7389656</v>
+        <v>7389936</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271840</v>
+        <v>127271856</v>
       </c>
       <c r="B95" t="n">
-        <v>79632</v>
+        <v>57661</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,34 +9812,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812127</v>
+        <v>811876</v>
       </c>
       <c r="R95" t="n">
-        <v>7389936</v>
+        <v>7389968</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9872,6 +9876,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9898,10 +9907,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271856</v>
+        <v>127271857</v>
       </c>
       <c r="B96" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9927,20 +9936,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811876</v>
+        <v>812050</v>
       </c>
       <c r="R96" t="n">
-        <v>7389968</v>
+        <v>7389925</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9973,11 +9978,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271857</v>
+        <v>127271868</v>
       </c>
       <c r="B97" t="n">
-        <v>57657</v>
+        <v>57821</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812050</v>
+        <v>812092</v>
       </c>
       <c r="R97" t="n">
-        <v>7389925</v>
+        <v>7389656</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127271915</v>
+        <v>127271874</v>
       </c>
       <c r="B98" t="n">
-        <v>92616</v>
+        <v>57765</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10112,21 +10112,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811935</v>
+        <v>812168</v>
       </c>
       <c r="R98" t="n">
-        <v>7389943</v>
+        <v>7389829</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10198,10 +10198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127271874</v>
+        <v>127271915</v>
       </c>
       <c r="B99" t="n">
-        <v>57761</v>
+        <v>92620</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10209,21 +10209,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>812168</v>
+        <v>811935</v>
       </c>
       <c r="R99" t="n">
-        <v>7389829</v>
+        <v>7389943</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10295,32 +10295,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271907</v>
+        <v>127271893</v>
       </c>
       <c r="B100" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812162</v>
+        <v>812066</v>
       </c>
       <c r="R100" t="n">
-        <v>7389625</v>
+        <v>7389634</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271893</v>
+        <v>127271884</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>812066</v>
+        <v>811977</v>
       </c>
       <c r="R101" t="n">
-        <v>7389634</v>
+        <v>7389985</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271916</v>
+        <v>127271907</v>
       </c>
       <c r="B102" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811958</v>
+        <v>812162</v>
       </c>
       <c r="R102" t="n">
-        <v>7389946</v>
+        <v>7389625</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10586,32 +10586,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271884</v>
+        <v>127271916</v>
       </c>
       <c r="B103" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10621,10 +10621,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811977</v>
+        <v>811958</v>
       </c>
       <c r="R103" t="n">
-        <v>7389985</v>
+        <v>7389946</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10686,7 +10686,7 @@
         <v>127271864</v>
       </c>
       <c r="B104" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10789,32 +10789,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271913</v>
+        <v>127271892</v>
       </c>
       <c r="B105" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811963</v>
+        <v>812106</v>
       </c>
       <c r="R105" t="n">
-        <v>7390029</v>
+        <v>7389684</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10886,10 +10886,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271892</v>
+        <v>127271879</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10921,10 +10921,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812106</v>
+        <v>812228</v>
       </c>
       <c r="R106" t="n">
-        <v>7389684</v>
+        <v>7389839</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10983,10 +10983,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271879</v>
+        <v>127271844</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10994,21 +10994,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11018,10 +11018,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812228</v>
+        <v>812114</v>
       </c>
       <c r="R107" t="n">
-        <v>7389839</v>
+        <v>7389680</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11080,10 +11080,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271906</v>
+        <v>127271913</v>
       </c>
       <c r="B108" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812166</v>
+        <v>811963</v>
       </c>
       <c r="R108" t="n">
-        <v>7389625</v>
+        <v>7390029</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11177,49 +11177,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271853</v>
+        <v>127271906</v>
       </c>
       <c r="B109" t="n">
-        <v>57657</v>
+        <v>92620</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811970</v>
+        <v>812166</v>
       </c>
       <c r="R109" t="n">
-        <v>7390085</v>
+        <v>7389625</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11252,11 +11248,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11283,10 +11274,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271844</v>
+        <v>127271853</v>
       </c>
       <c r="B110" t="n">
-        <v>79632</v>
+        <v>57661</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11294,34 +11285,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>812114</v>
+        <v>811970</v>
       </c>
       <c r="R110" t="n">
-        <v>7389680</v>
+        <v>7390085</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11354,6 +11349,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11380,32 +11380,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271922</v>
+        <v>127271885</v>
       </c>
       <c r="B111" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>812120</v>
+        <v>811960</v>
       </c>
       <c r="R111" t="n">
-        <v>7389691</v>
+        <v>7390029</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11477,32 +11477,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271885</v>
+        <v>127271922</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811960</v>
+        <v>812120</v>
       </c>
       <c r="R112" t="n">
-        <v>7390029</v>
+        <v>7389691</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11577,7 +11577,7 @@
         <v>127271860</v>
       </c>
       <c r="B113" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11680,32 +11680,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271887</v>
+        <v>127271866</v>
       </c>
       <c r="B114" t="n">
-        <v>79014</v>
+        <v>56853</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811866</v>
+        <v>811935</v>
       </c>
       <c r="R114" t="n">
-        <v>7390052</v>
+        <v>7389957</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,32 +11777,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271919</v>
+        <v>127271887</v>
       </c>
       <c r="B115" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>812158</v>
+        <v>811866</v>
       </c>
       <c r="R115" t="n">
-        <v>7389883</v>
+        <v>7390052</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271914</v>
+        <v>127271919</v>
       </c>
       <c r="B116" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811875</v>
+        <v>812158</v>
       </c>
       <c r="R116" t="n">
-        <v>7389980</v>
+        <v>7389883</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11971,49 +11971,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271862</v>
+        <v>127271914</v>
       </c>
       <c r="B117" t="n">
-        <v>57657</v>
+        <v>92620</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>812079</v>
+        <v>811875</v>
       </c>
       <c r="R117" t="n">
-        <v>7389800</v>
+        <v>7389980</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12046,11 +12042,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12077,45 +12068,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271866</v>
+        <v>127271862</v>
       </c>
       <c r="B118" t="n">
-        <v>56849</v>
+        <v>57661</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811935</v>
+        <v>812079</v>
       </c>
       <c r="R118" t="n">
-        <v>7389957</v>
+        <v>7389800</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12148,6 +12143,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12177,7 +12177,7 @@
         <v>127271918</v>
       </c>
       <c r="B119" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>127271861</v>
       </c>
       <c r="B120" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>127271850</v>
       </c>
       <c r="B121" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>127388830</v>
       </c>
       <c r="B122" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049592</v>
+        <v>127049608</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>97331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812072</v>
+        <v>812055</v>
       </c>
       <c r="R3" t="n">
-        <v>7389539</v>
+        <v>7389491</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049608</v>
+        <v>127049592</v>
       </c>
       <c r="B4" t="n">
-        <v>97331</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812055</v>
+        <v>812072</v>
       </c>
       <c r="R4" t="n">
-        <v>7389491</v>
+        <v>7389539</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049611</v>
+        <v>127049638</v>
       </c>
       <c r="B6" t="n">
-        <v>97331</v>
+        <v>92620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>812004</v>
+        <v>811921</v>
       </c>
       <c r="R6" t="n">
-        <v>7389528</v>
+        <v>7389590</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049638</v>
+        <v>127049639</v>
       </c>
       <c r="B7" t="n">
         <v>92620</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811921</v>
+        <v>811937</v>
       </c>
       <c r="R7" t="n">
-        <v>7389590</v>
+        <v>7389558</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049639</v>
+        <v>127049611</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>97331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811937</v>
+        <v>812004</v>
       </c>
       <c r="R8" t="n">
-        <v>7389558</v>
+        <v>7389528</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049618</v>
+        <v>127049596</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>812047</v>
+        <v>811955</v>
       </c>
       <c r="R12" t="n">
-        <v>7389473</v>
+        <v>7389537</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049596</v>
+        <v>127049618</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811955</v>
+        <v>812047</v>
       </c>
       <c r="R15" t="n">
-        <v>7389537</v>
+        <v>7389473</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049622</v>
+        <v>127049631</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812088</v>
+        <v>812026</v>
       </c>
       <c r="R19" t="n">
-        <v>7389588</v>
+        <v>7389461</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127049631</v>
+        <v>127049622</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>812026</v>
+        <v>812088</v>
       </c>
       <c r="R20" t="n">
-        <v>7389461</v>
+        <v>7389588</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3700,32 +3700,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127049625</v>
+        <v>127049635</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811987</v>
+        <v>812027</v>
       </c>
       <c r="R33" t="n">
-        <v>7389722</v>
+        <v>7389564</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049635</v>
+        <v>127049625</v>
       </c>
       <c r="B34" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>812027</v>
+        <v>811987</v>
       </c>
       <c r="R34" t="n">
-        <v>7389564</v>
+        <v>7389722</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127049624</v>
+        <v>127049616</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>812000</v>
+        <v>811934</v>
       </c>
       <c r="R37" t="n">
-        <v>7389736</v>
+        <v>7389548</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127049616</v>
+        <v>127049624</v>
       </c>
       <c r="B38" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811934</v>
+        <v>812000</v>
       </c>
       <c r="R38" t="n">
-        <v>7389548</v>
+        <v>7389736</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4680,32 +4680,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127049615</v>
+        <v>127049634</v>
       </c>
       <c r="B43" t="n">
-        <v>80993</v>
+        <v>92620</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811948</v>
+        <v>812073</v>
       </c>
       <c r="R43" t="n">
-        <v>7389545</v>
+        <v>7389533</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4777,32 +4777,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127049634</v>
+        <v>127049615</v>
       </c>
       <c r="B44" t="n">
-        <v>92620</v>
+        <v>80993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>812073</v>
+        <v>811948</v>
       </c>
       <c r="R44" t="n">
-        <v>7389533</v>
+        <v>7389545</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4874,10 +4874,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049614</v>
+        <v>127049626</v>
       </c>
       <c r="B45" t="n">
-        <v>80993</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>812078</v>
+        <v>811984</v>
       </c>
       <c r="R45" t="n">
-        <v>7389625</v>
+        <v>7389705</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049626</v>
+        <v>127049641</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811984</v>
+        <v>811963</v>
       </c>
       <c r="R46" t="n">
-        <v>7389705</v>
+        <v>7389548</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,32 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049641</v>
+        <v>127049614</v>
       </c>
       <c r="B47" t="n">
-        <v>92620</v>
+        <v>80993</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811963</v>
+        <v>812078</v>
       </c>
       <c r="R47" t="n">
-        <v>7389548</v>
+        <v>7389625</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6341,32 +6341,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271911</v>
+        <v>127271883</v>
       </c>
       <c r="B60" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812117</v>
+        <v>812004</v>
       </c>
       <c r="R60" t="n">
-        <v>7389993</v>
+        <v>7389960</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271875</v>
+        <v>127271911</v>
       </c>
       <c r="B62" t="n">
-        <v>58031</v>
+        <v>92620</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6555,21 +6555,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812093</v>
+        <v>812117</v>
       </c>
       <c r="R62" t="n">
-        <v>7389656</v>
+        <v>7389993</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6641,32 +6641,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271883</v>
+        <v>127271875</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812004</v>
+        <v>812093</v>
       </c>
       <c r="R63" t="n">
-        <v>7389960</v>
+        <v>7389656</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271852</v>
+        <v>127271876</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>80993</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,38 +6952,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812054</v>
+        <v>812128</v>
       </c>
       <c r="R66" t="n">
-        <v>7390009</v>
+        <v>7390038</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7018,17 +7014,13 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7047,10 +7039,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271876</v>
+        <v>127271841</v>
       </c>
       <c r="B67" t="n">
-        <v>80993</v>
+        <v>79636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7050,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7074,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812128</v>
+        <v>812139</v>
       </c>
       <c r="R67" t="n">
-        <v>7390038</v>
+        <v>7389967</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7126,7 +7118,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7145,7 +7136,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271841</v>
+        <v>127271842</v>
       </c>
       <c r="B68" t="n">
         <v>79636</v>
@@ -7180,10 +7171,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812139</v>
+        <v>812161</v>
       </c>
       <c r="R68" t="n">
-        <v>7389967</v>
+        <v>7389878</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7242,10 +7233,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271842</v>
+        <v>127271886</v>
       </c>
       <c r="B69" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7253,21 +7244,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7277,10 +7268,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812161</v>
+        <v>811852</v>
       </c>
       <c r="R69" t="n">
-        <v>7389878</v>
+        <v>7390093</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7339,7 +7330,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271886</v>
+        <v>127271881</v>
       </c>
       <c r="B70" t="n">
         <v>79018</v>
@@ -7374,10 +7365,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811852</v>
+        <v>812133</v>
       </c>
       <c r="R70" t="n">
-        <v>7390093</v>
+        <v>7389830</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7436,32 +7427,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271881</v>
+        <v>127271912</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7471,10 +7462,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812133</v>
+        <v>811981</v>
       </c>
       <c r="R71" t="n">
-        <v>7389830</v>
+        <v>7389988</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7533,7 +7524,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271912</v>
+        <v>127271921</v>
       </c>
       <c r="B72" t="n">
         <v>92620</v>
@@ -7568,10 +7559,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811981</v>
+        <v>812092</v>
       </c>
       <c r="R72" t="n">
-        <v>7389988</v>
+        <v>7389721</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7630,7 +7621,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271921</v>
+        <v>127271909</v>
       </c>
       <c r="B73" t="n">
         <v>92620</v>
@@ -7665,10 +7656,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812092</v>
+        <v>812175</v>
       </c>
       <c r="R73" t="n">
-        <v>7389721</v>
+        <v>7389748</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7727,45 +7718,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271909</v>
+        <v>127271852</v>
       </c>
       <c r="B74" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812175</v>
+        <v>812054</v>
       </c>
       <c r="R74" t="n">
-        <v>7389748</v>
+        <v>7390009</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7798,6 +7793,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8018,45 +8018,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127271851</v>
       </c>
       <c r="B77" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>812117</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389911</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8089,6 +8093,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8115,7 +8124,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127271917</v>
       </c>
       <c r="B78" t="n">
         <v>92620</v>
@@ -8150,10 +8159,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>812088</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389936</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8212,32 +8221,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271908</v>
       </c>
       <c r="B79" t="n">
-        <v>91348</v>
+        <v>92620</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8256,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>812128</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389752</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8309,10 +8318,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271851</v>
+        <v>127271877</v>
       </c>
       <c r="B80" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8320,38 +8329,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812117</v>
+        <v>812195</v>
       </c>
       <c r="R80" t="n">
-        <v>7389911</v>
+        <v>7389776</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8384,11 +8389,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R84" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271843</v>
+        <v>127271890</v>
       </c>
       <c r="B85" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812074</v>
+        <v>812121</v>
       </c>
       <c r="R85" t="n">
-        <v>7389829</v>
+        <v>7389928</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,7 +8909,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271890</v>
+        <v>127271882</v>
       </c>
       <c r="B86" t="n">
         <v>79018</v>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812121</v>
+        <v>812120</v>
       </c>
       <c r="R86" t="n">
-        <v>7389928</v>
+        <v>7389917</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9801,7 +9801,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271856</v>
+        <v>127271857</v>
       </c>
       <c r="B95" t="n">
         <v>57661</v>
@@ -9830,20 +9830,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811876</v>
+        <v>812050</v>
       </c>
       <c r="R95" t="n">
-        <v>7389968</v>
+        <v>7389925</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9876,11 +9872,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9907,7 +9898,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271857</v>
+        <v>127271856</v>
       </c>
       <c r="B96" t="n">
         <v>57661</v>
@@ -9936,16 +9927,20 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812050</v>
+        <v>811876</v>
       </c>
       <c r="R96" t="n">
-        <v>7389925</v>
+        <v>7389968</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9978,6 +9973,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127271874</v>
+        <v>127271915</v>
       </c>
       <c r="B98" t="n">
-        <v>57765</v>
+        <v>92620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10112,21 +10112,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>812168</v>
+        <v>811935</v>
       </c>
       <c r="R98" t="n">
-        <v>7389829</v>
+        <v>7389943</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10198,10 +10198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127271915</v>
+        <v>127271874</v>
       </c>
       <c r="B99" t="n">
-        <v>92620</v>
+        <v>57765</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10209,21 +10209,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811935</v>
+        <v>812168</v>
       </c>
       <c r="R99" t="n">
-        <v>7389943</v>
+        <v>7389829</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10789,32 +10789,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271892</v>
+        <v>127271906</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>812106</v>
+        <v>812166</v>
       </c>
       <c r="R105" t="n">
-        <v>7389684</v>
+        <v>7389625</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10886,7 +10886,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271879</v>
+        <v>127271892</v>
       </c>
       <c r="B106" t="n">
         <v>79018</v>
@@ -10921,10 +10921,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812228</v>
+        <v>812106</v>
       </c>
       <c r="R106" t="n">
-        <v>7389839</v>
+        <v>7389684</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11080,32 +11080,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271913</v>
+        <v>127271879</v>
       </c>
       <c r="B108" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811963</v>
+        <v>812228</v>
       </c>
       <c r="R108" t="n">
-        <v>7390029</v>
+        <v>7389839</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11177,7 +11177,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271906</v>
+        <v>127271913</v>
       </c>
       <c r="B109" t="n">
         <v>92620</v>
@@ -11212,10 +11212,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812166</v>
+        <v>811963</v>
       </c>
       <c r="R109" t="n">
-        <v>7389625</v>
+        <v>7390029</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11380,32 +11380,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271885</v>
+        <v>127271922</v>
       </c>
       <c r="B111" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811960</v>
+        <v>812120</v>
       </c>
       <c r="R111" t="n">
-        <v>7390029</v>
+        <v>7389691</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11477,45 +11477,49 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271922</v>
+        <v>127271860</v>
       </c>
       <c r="B112" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>812120</v>
+        <v>812080</v>
       </c>
       <c r="R112" t="n">
-        <v>7389691</v>
+        <v>7389823</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11548,6 +11552,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11574,10 +11583,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127271860</v>
+        <v>127271885</v>
       </c>
       <c r="B113" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11585,38 +11594,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>812080</v>
+        <v>811960</v>
       </c>
       <c r="R113" t="n">
-        <v>7389823</v>
+        <v>7390029</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11649,11 +11654,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11680,32 +11680,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271866</v>
+        <v>127271887</v>
       </c>
       <c r="B114" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811935</v>
+        <v>811866</v>
       </c>
       <c r="R114" t="n">
-        <v>7389957</v>
+        <v>7390052</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,32 +11777,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271887</v>
+        <v>127271919</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811866</v>
+        <v>812158</v>
       </c>
       <c r="R115" t="n">
-        <v>7390052</v>
+        <v>7389883</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,7 +11874,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271919</v>
+        <v>127271914</v>
       </c>
       <c r="B116" t="n">
         <v>92620</v>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>812158</v>
+        <v>811875</v>
       </c>
       <c r="R116" t="n">
-        <v>7389883</v>
+        <v>7389980</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11971,45 +11971,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271914</v>
+        <v>127271862</v>
       </c>
       <c r="B117" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811875</v>
+        <v>812079</v>
       </c>
       <c r="R117" t="n">
-        <v>7389980</v>
+        <v>7389800</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12042,6 +12046,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12068,49 +12077,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271862</v>
+        <v>127271866</v>
       </c>
       <c r="B118" t="n">
-        <v>57661</v>
+        <v>56853</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>812079</v>
+        <v>811935</v>
       </c>
       <c r="R118" t="n">
-        <v>7389800</v>
+        <v>7389957</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12143,11 +12148,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12174,45 +12174,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271918</v>
+        <v>127271861</v>
       </c>
       <c r="B119" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812162</v>
+        <v>812106</v>
       </c>
       <c r="R119" t="n">
-        <v>7389925</v>
+        <v>7389819</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12245,6 +12249,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12271,49 +12280,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271861</v>
+        <v>127271918</v>
       </c>
       <c r="B120" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812106</v>
+        <v>812162</v>
       </c>
       <c r="R120" t="n">
-        <v>7389819</v>
+        <v>7389925</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12346,11 +12351,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD120" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049638</v>
+        <v>127049611</v>
       </c>
       <c r="B6" t="n">
-        <v>92620</v>
+        <v>97331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811921</v>
+        <v>812004</v>
       </c>
       <c r="R6" t="n">
-        <v>7389590</v>
+        <v>7389528</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049639</v>
+        <v>127049638</v>
       </c>
       <c r="B7" t="n">
         <v>92620</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811937</v>
+        <v>811921</v>
       </c>
       <c r="R7" t="n">
-        <v>7389558</v>
+        <v>7389590</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049611</v>
+        <v>127049639</v>
       </c>
       <c r="B8" t="n">
-        <v>97331</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>812004</v>
+        <v>811937</v>
       </c>
       <c r="R8" t="n">
-        <v>7389528</v>
+        <v>7389558</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049609</v>
+        <v>127049633</v>
       </c>
       <c r="B27" t="n">
-        <v>97331</v>
+        <v>78685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811991</v>
+        <v>811950</v>
       </c>
       <c r="R27" t="n">
-        <v>7389623</v>
+        <v>7389574</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049633</v>
+        <v>127049642</v>
       </c>
       <c r="B28" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811950</v>
+        <v>811969</v>
       </c>
       <c r="R28" t="n">
-        <v>7389574</v>
+        <v>7389545</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049642</v>
+        <v>127049643</v>
       </c>
       <c r="B29" t="n">
         <v>92620</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811969</v>
+        <v>811987</v>
       </c>
       <c r="R29" t="n">
-        <v>7389545</v>
+        <v>7389527</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049643</v>
+        <v>127049609</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>97331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811987</v>
+        <v>811991</v>
       </c>
       <c r="R30" t="n">
-        <v>7389527</v>
+        <v>7389623</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B56" t="n">
-        <v>78424</v>
+        <v>92620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R56" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R57" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B58" t="n">
-        <v>92620</v>
+        <v>78424</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R58" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B59" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R59" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -8018,49 +8018,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271851</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812117</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389911</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8093,11 +8089,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8124,7 +8115,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271917</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
         <v>92620</v>
@@ -8159,10 +8150,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812088</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389936</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8221,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271908</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92620</v>
+        <v>91348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8256,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812128</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389752</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8318,10 +8309,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271877</v>
+        <v>127271851</v>
       </c>
       <c r="B80" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8329,34 +8320,38 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812195</v>
+        <v>812117</v>
       </c>
       <c r="R80" t="n">
-        <v>7389776</v>
+        <v>7389911</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8389,6 +8384,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10789,45 +10789,49 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271906</v>
+        <v>127271853</v>
       </c>
       <c r="B105" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>812166</v>
+        <v>811970</v>
       </c>
       <c r="R105" t="n">
-        <v>7389625</v>
+        <v>7390085</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10860,6 +10864,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10886,32 +10895,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271892</v>
+        <v>127271906</v>
       </c>
       <c r="B106" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10921,10 +10930,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812106</v>
+        <v>812166</v>
       </c>
       <c r="R106" t="n">
-        <v>7389684</v>
+        <v>7389625</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10983,10 +10992,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271844</v>
+        <v>127271892</v>
       </c>
       <c r="B107" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10994,21 +11003,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11018,10 +11027,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812114</v>
+        <v>812106</v>
       </c>
       <c r="R107" t="n">
-        <v>7389680</v>
+        <v>7389684</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11080,10 +11089,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271879</v>
+        <v>127271844</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11091,21 +11100,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11115,10 +11124,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812228</v>
+        <v>812114</v>
       </c>
       <c r="R108" t="n">
-        <v>7389839</v>
+        <v>7389680</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11274,10 +11283,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271853</v>
+        <v>127271879</v>
       </c>
       <c r="B110" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11285,38 +11294,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811970</v>
+        <v>812228</v>
       </c>
       <c r="R110" t="n">
-        <v>7390085</v>
+        <v>7389839</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11349,11 +11354,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11380,32 +11380,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271922</v>
+        <v>127271885</v>
       </c>
       <c r="B111" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>812120</v>
+        <v>811960</v>
       </c>
       <c r="R111" t="n">
-        <v>7389691</v>
+        <v>7390029</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11477,49 +11477,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271860</v>
+        <v>127271922</v>
       </c>
       <c r="B112" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>812080</v>
+        <v>812120</v>
       </c>
       <c r="R112" t="n">
-        <v>7389823</v>
+        <v>7389691</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11552,11 +11548,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11583,10 +11574,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127271885</v>
+        <v>127271860</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11594,34 +11585,38 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811960</v>
+        <v>812080</v>
       </c>
       <c r="R113" t="n">
-        <v>7390029</v>
+        <v>7389823</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11654,6 +11649,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049608</v>
+        <v>127049602</v>
       </c>
       <c r="B3" t="n">
-        <v>97331</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812055</v>
+        <v>812043</v>
       </c>
       <c r="R3" t="n">
-        <v>7389491</v>
+        <v>7389685</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -843,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049592</v>
+        <v>127049608</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>97331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812072</v>
+        <v>812055</v>
       </c>
       <c r="R4" t="n">
-        <v>7389539</v>
+        <v>7389491</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049602</v>
+        <v>127049592</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,38 +986,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812043</v>
+        <v>812072</v>
       </c>
       <c r="R5" t="n">
-        <v>7389685</v>
+        <v>7389539</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1041,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049611</v>
+        <v>127049639</v>
       </c>
       <c r="B6" t="n">
-        <v>97331</v>
+        <v>92620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>812004</v>
+        <v>811937</v>
       </c>
       <c r="R6" t="n">
-        <v>7389528</v>
+        <v>7389558</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049638</v>
+        <v>127049611</v>
       </c>
       <c r="B7" t="n">
-        <v>92620</v>
+        <v>97331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811921</v>
+        <v>812004</v>
       </c>
       <c r="R7" t="n">
-        <v>7389590</v>
+        <v>7389528</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049639</v>
+        <v>127049638</v>
       </c>
       <c r="B8" t="n">
         <v>92620</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811937</v>
+        <v>811921</v>
       </c>
       <c r="R8" t="n">
-        <v>7389558</v>
+        <v>7389590</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049596</v>
+        <v>127049620</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811955</v>
+        <v>812079</v>
       </c>
       <c r="R12" t="n">
-        <v>7389537</v>
+        <v>7389510</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049620</v>
+        <v>127049628</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>812079</v>
+        <v>811980</v>
       </c>
       <c r="R13" t="n">
-        <v>7389510</v>
+        <v>7389540</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049628</v>
+        <v>127049618</v>
       </c>
       <c r="B14" t="n">
         <v>79018</v>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811980</v>
+        <v>812047</v>
       </c>
       <c r="R14" t="n">
-        <v>7389540</v>
+        <v>7389473</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049618</v>
+        <v>127049596</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>812047</v>
+        <v>811955</v>
       </c>
       <c r="R15" t="n">
-        <v>7389473</v>
+        <v>7389537</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049633</v>
+        <v>127049609</v>
       </c>
       <c r="B27" t="n">
-        <v>78685</v>
+        <v>97331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811950</v>
+        <v>811991</v>
       </c>
       <c r="R27" t="n">
-        <v>7389574</v>
+        <v>7389623</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049642</v>
+        <v>127049633</v>
       </c>
       <c r="B28" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811969</v>
+        <v>811950</v>
       </c>
       <c r="R28" t="n">
-        <v>7389545</v>
+        <v>7389574</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049643</v>
+        <v>127049642</v>
       </c>
       <c r="B29" t="n">
         <v>92620</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811987</v>
+        <v>811969</v>
       </c>
       <c r="R29" t="n">
-        <v>7389527</v>
+        <v>7389545</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049609</v>
+        <v>127049643</v>
       </c>
       <c r="B30" t="n">
-        <v>97331</v>
+        <v>92620</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811991</v>
+        <v>811987</v>
       </c>
       <c r="R30" t="n">
-        <v>7389623</v>
+        <v>7389527</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -8018,45 +8018,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127271851</v>
       </c>
       <c r="B77" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>812117</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389911</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8089,6 +8093,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8115,7 +8124,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127271917</v>
       </c>
       <c r="B78" t="n">
         <v>92620</v>
@@ -8150,10 +8159,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>812088</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389936</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8212,32 +8221,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271908</v>
       </c>
       <c r="B79" t="n">
-        <v>91348</v>
+        <v>92620</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8256,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>812128</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389752</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8309,10 +8318,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271851</v>
+        <v>127271877</v>
       </c>
       <c r="B80" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8320,38 +8329,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812117</v>
+        <v>812195</v>
       </c>
       <c r="R80" t="n">
-        <v>7389911</v>
+        <v>7389776</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8384,11 +8389,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11680,32 +11680,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271887</v>
+        <v>127271866</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811866</v>
+        <v>811935</v>
       </c>
       <c r="R114" t="n">
-        <v>7390052</v>
+        <v>7389957</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,32 +11777,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271919</v>
+        <v>127271887</v>
       </c>
       <c r="B115" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>812158</v>
+        <v>811866</v>
       </c>
       <c r="R115" t="n">
-        <v>7389883</v>
+        <v>7390052</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,7 +11874,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271914</v>
+        <v>127271919</v>
       </c>
       <c r="B116" t="n">
         <v>92620</v>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811875</v>
+        <v>812158</v>
       </c>
       <c r="R116" t="n">
-        <v>7389980</v>
+        <v>7389883</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11971,49 +11971,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271862</v>
+        <v>127271914</v>
       </c>
       <c r="B117" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>812079</v>
+        <v>811875</v>
       </c>
       <c r="R117" t="n">
-        <v>7389800</v>
+        <v>7389980</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12046,11 +12042,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12077,45 +12068,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271866</v>
+        <v>127271862</v>
       </c>
       <c r="B118" t="n">
-        <v>56853</v>
+        <v>57661</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811935</v>
+        <v>812079</v>
       </c>
       <c r="R118" t="n">
-        <v>7389957</v>
+        <v>7389800</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12148,6 +12143,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049602</v>
+        <v>127049608</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>97331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812043</v>
+        <v>812055</v>
       </c>
       <c r="R3" t="n">
-        <v>7389685</v>
+        <v>7389491</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049608</v>
+        <v>127049592</v>
       </c>
       <c r="B4" t="n">
-        <v>97331</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812055</v>
+        <v>812072</v>
       </c>
       <c r="R4" t="n">
-        <v>7389491</v>
+        <v>7389539</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049592</v>
+        <v>127049602</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,34 +977,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812072</v>
+        <v>812043</v>
       </c>
       <c r="R5" t="n">
-        <v>7389539</v>
+        <v>7389685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1046,6 +1041,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049639</v>
+        <v>127049611</v>
       </c>
       <c r="B6" t="n">
-        <v>92620</v>
+        <v>97331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811937</v>
+        <v>812004</v>
       </c>
       <c r="R6" t="n">
-        <v>7389558</v>
+        <v>7389528</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049611</v>
+        <v>127049638</v>
       </c>
       <c r="B7" t="n">
-        <v>97331</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1180,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>812004</v>
+        <v>811921</v>
       </c>
       <c r="R7" t="n">
-        <v>7389528</v>
+        <v>7389590</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049638</v>
+        <v>127049639</v>
       </c>
       <c r="B8" t="n">
         <v>92620</v>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811921</v>
+        <v>811937</v>
       </c>
       <c r="R8" t="n">
-        <v>7389590</v>
+        <v>7389558</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049620</v>
+        <v>127049628</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>812079</v>
+        <v>811980</v>
       </c>
       <c r="R12" t="n">
-        <v>7389510</v>
+        <v>7389540</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049628</v>
+        <v>127049618</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811980</v>
+        <v>812047</v>
       </c>
       <c r="R13" t="n">
-        <v>7389540</v>
+        <v>7389473</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049618</v>
+        <v>127049596</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>812047</v>
+        <v>811955</v>
       </c>
       <c r="R14" t="n">
-        <v>7389473</v>
+        <v>7389537</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049596</v>
+        <v>127049620</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811955</v>
+        <v>812079</v>
       </c>
       <c r="R15" t="n">
-        <v>7389537</v>
+        <v>7389510</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049593</v>
+        <v>127049637</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R22" t="n">
-        <v>7389548</v>
+        <v>7389571</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049637</v>
+        <v>127049640</v>
       </c>
       <c r="B23" t="n">
         <v>92620</v>
@@ -2768,7 +2768,7 @@
         <v>811936</v>
       </c>
       <c r="R23" t="n">
-        <v>7389571</v>
+        <v>7389556</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2827,32 +2827,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127049640</v>
+        <v>127049593</v>
       </c>
       <c r="B24" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R24" t="n">
-        <v>7389556</v>
+        <v>7389548</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049609</v>
+        <v>127049642</v>
       </c>
       <c r="B27" t="n">
-        <v>97331</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811991</v>
+        <v>811969</v>
       </c>
       <c r="R27" t="n">
-        <v>7389623</v>
+        <v>7389545</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049633</v>
+        <v>127049643</v>
       </c>
       <c r="B28" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811950</v>
+        <v>811987</v>
       </c>
       <c r="R28" t="n">
-        <v>7389574</v>
+        <v>7389527</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049642</v>
+        <v>127049609</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>97331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3323,21 +3323,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811969</v>
+        <v>811991</v>
       </c>
       <c r="R29" t="n">
-        <v>7389545</v>
+        <v>7389623</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,32 +3409,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049643</v>
+        <v>127049633</v>
       </c>
       <c r="B30" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811987</v>
+        <v>811950</v>
       </c>
       <c r="R30" t="n">
-        <v>7389527</v>
+        <v>7389574</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,34 +5567,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R52" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5627,6 +5631,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5653,10 +5662,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B53" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5664,38 +5673,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R53" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5728,11 +5733,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>78424</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R56" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B57" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R57" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B58" t="n">
-        <v>78424</v>
+        <v>92620</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R58" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R59" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,32 +6341,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271883</v>
+        <v>127271875</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812004</v>
+        <v>812093</v>
       </c>
       <c r="R60" t="n">
-        <v>7389960</v>
+        <v>7389656</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6544,32 +6544,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271911</v>
+        <v>127271883</v>
       </c>
       <c r="B62" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812117</v>
+        <v>812004</v>
       </c>
       <c r="R62" t="n">
-        <v>7389993</v>
+        <v>7389960</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271875</v>
+        <v>127271911</v>
       </c>
       <c r="B63" t="n">
-        <v>58031</v>
+        <v>92620</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6652,21 +6652,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812093</v>
+        <v>812117</v>
       </c>
       <c r="R63" t="n">
-        <v>7389656</v>
+        <v>7389993</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271876</v>
+        <v>127271886</v>
       </c>
       <c r="B66" t="n">
-        <v>80993</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812128</v>
+        <v>811852</v>
       </c>
       <c r="R66" t="n">
-        <v>7390038</v>
+        <v>7390093</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7020,7 +7020,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7039,32 +7038,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271841</v>
+        <v>127271912</v>
       </c>
       <c r="B67" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7074,10 +7073,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812139</v>
+        <v>811981</v>
       </c>
       <c r="R67" t="n">
-        <v>7389967</v>
+        <v>7389988</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7136,32 +7135,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271842</v>
+        <v>127271921</v>
       </c>
       <c r="B68" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7171,10 +7170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812161</v>
+        <v>812092</v>
       </c>
       <c r="R68" t="n">
-        <v>7389878</v>
+        <v>7389721</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7233,32 +7232,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271886</v>
+        <v>127271909</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7268,10 +7267,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811852</v>
+        <v>812175</v>
       </c>
       <c r="R69" t="n">
-        <v>7390093</v>
+        <v>7389748</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7427,45 +7426,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271912</v>
+        <v>127271852</v>
       </c>
       <c r="B71" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811981</v>
+        <v>812054</v>
       </c>
       <c r="R71" t="n">
-        <v>7389988</v>
+        <v>7390009</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7498,6 +7501,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7524,32 +7532,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271921</v>
+        <v>127271876</v>
       </c>
       <c r="B72" t="n">
-        <v>92620</v>
+        <v>80993</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7559,10 +7567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812092</v>
+        <v>812128</v>
       </c>
       <c r="R72" t="n">
-        <v>7389721</v>
+        <v>7390038</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7603,6 +7611,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7621,32 +7630,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271909</v>
+        <v>127271841</v>
       </c>
       <c r="B73" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7656,10 +7665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812175</v>
+        <v>812139</v>
       </c>
       <c r="R73" t="n">
-        <v>7389748</v>
+        <v>7389967</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7718,10 +7727,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271852</v>
+        <v>127271842</v>
       </c>
       <c r="B74" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7729,38 +7738,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812054</v>
+        <v>812161</v>
       </c>
       <c r="R74" t="n">
-        <v>7390009</v>
+        <v>7389878</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7793,11 +7798,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8018,49 +8018,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271851</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812117</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389911</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8093,11 +8089,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8124,7 +8115,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271917</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
         <v>92620</v>
@@ -8159,10 +8150,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812088</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389936</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8221,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271908</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92620</v>
+        <v>91348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8256,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812128</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389752</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8318,10 +8309,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271877</v>
+        <v>127271851</v>
       </c>
       <c r="B80" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8329,34 +8320,38 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812195</v>
+        <v>812117</v>
       </c>
       <c r="R80" t="n">
-        <v>7389776</v>
+        <v>7389911</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8389,6 +8384,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271843</v>
+        <v>127271882</v>
       </c>
       <c r="B84" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812074</v>
+        <v>812120</v>
       </c>
       <c r="R84" t="n">
-        <v>7389829</v>
+        <v>7389917</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8920,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R86" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B87" t="n">
-        <v>79636</v>
+        <v>57658</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R87" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,6 +9077,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9103,10 +9108,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B88" t="n">
-        <v>57658</v>
+        <v>79636</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9114,21 +9119,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R88" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9174,11 +9179,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9302,10 +9302,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271836</v>
+        <v>127271894</v>
       </c>
       <c r="B90" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,21 +9313,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811958</v>
+        <v>811982</v>
       </c>
       <c r="R90" t="n">
-        <v>7389950</v>
+        <v>7389609</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271894</v>
+        <v>127271836</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9410,21 +9410,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811982</v>
+        <v>811958</v>
       </c>
       <c r="R91" t="n">
-        <v>7389609</v>
+        <v>7389950</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9801,7 +9801,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271857</v>
+        <v>127271856</v>
       </c>
       <c r="B95" t="n">
         <v>57661</v>
@@ -9830,16 +9830,20 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812050</v>
+        <v>811876</v>
       </c>
       <c r="R95" t="n">
-        <v>7389925</v>
+        <v>7389968</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9872,6 +9876,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9898,7 +9907,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271856</v>
+        <v>127271857</v>
       </c>
       <c r="B96" t="n">
         <v>57661</v>
@@ -9927,20 +9936,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811876</v>
+        <v>812050</v>
       </c>
       <c r="R96" t="n">
-        <v>7389968</v>
+        <v>7389925</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9973,11 +9978,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10295,10 +10295,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271893</v>
+        <v>127271864</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10306,34 +10306,38 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812066</v>
+        <v>812087</v>
       </c>
       <c r="R100" t="n">
-        <v>7389634</v>
+        <v>7389653</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10366,6 +10370,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10392,32 +10401,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271884</v>
+        <v>127271907</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10427,10 +10436,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811977</v>
+        <v>812162</v>
       </c>
       <c r="R101" t="n">
-        <v>7389985</v>
+        <v>7389625</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10489,32 +10498,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271907</v>
+        <v>127271893</v>
       </c>
       <c r="B102" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10524,10 +10533,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>812162</v>
+        <v>812066</v>
       </c>
       <c r="R102" t="n">
-        <v>7389625</v>
+        <v>7389634</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10683,10 +10692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271864</v>
+        <v>127271884</v>
       </c>
       <c r="B104" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10694,38 +10703,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>812087</v>
+        <v>811977</v>
       </c>
       <c r="R104" t="n">
-        <v>7389653</v>
+        <v>7389985</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10758,11 +10763,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,49 +10789,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271853</v>
+        <v>127271913</v>
       </c>
       <c r="B105" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811970</v>
+        <v>811963</v>
       </c>
       <c r="R105" t="n">
-        <v>7390085</v>
+        <v>7390029</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10864,11 +10860,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10895,32 +10886,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271906</v>
+        <v>127271892</v>
       </c>
       <c r="B106" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10930,10 +10921,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812166</v>
+        <v>812106</v>
       </c>
       <c r="R106" t="n">
-        <v>7389625</v>
+        <v>7389684</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10992,7 +10983,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271892</v>
+        <v>127271879</v>
       </c>
       <c r="B107" t="n">
         <v>79018</v>
@@ -11027,10 +11018,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812106</v>
+        <v>812228</v>
       </c>
       <c r="R107" t="n">
-        <v>7389684</v>
+        <v>7389839</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11089,32 +11080,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271844</v>
+        <v>127271906</v>
       </c>
       <c r="B108" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11124,10 +11115,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812114</v>
+        <v>812166</v>
       </c>
       <c r="R108" t="n">
-        <v>7389680</v>
+        <v>7389625</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11186,45 +11177,49 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271913</v>
+        <v>127271853</v>
       </c>
       <c r="B109" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811963</v>
+        <v>811970</v>
       </c>
       <c r="R109" t="n">
-        <v>7390029</v>
+        <v>7390085</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11257,6 +11252,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11283,10 +11283,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271879</v>
+        <v>127271844</v>
       </c>
       <c r="B110" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11294,21 +11294,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>812228</v>
+        <v>812114</v>
       </c>
       <c r="R110" t="n">
-        <v>7389839</v>
+        <v>7389680</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11380,32 +11380,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271885</v>
+        <v>127271922</v>
       </c>
       <c r="B111" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811960</v>
+        <v>812120</v>
       </c>
       <c r="R111" t="n">
-        <v>7390029</v>
+        <v>7389691</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11477,32 +11477,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271922</v>
+        <v>127271885</v>
       </c>
       <c r="B112" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>812120</v>
+        <v>811960</v>
       </c>
       <c r="R112" t="n">
-        <v>7389691</v>
+        <v>7390029</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11680,32 +11680,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271866</v>
+        <v>127271887</v>
       </c>
       <c r="B114" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811935</v>
+        <v>811866</v>
       </c>
       <c r="R114" t="n">
-        <v>7389957</v>
+        <v>7390052</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,32 +11777,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271887</v>
+        <v>127271919</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811866</v>
+        <v>812158</v>
       </c>
       <c r="R115" t="n">
-        <v>7390052</v>
+        <v>7389883</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,7 +11874,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271919</v>
+        <v>127271914</v>
       </c>
       <c r="B116" t="n">
         <v>92620</v>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>812158</v>
+        <v>811875</v>
       </c>
       <c r="R116" t="n">
-        <v>7389883</v>
+        <v>7389980</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11971,45 +11971,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271914</v>
+        <v>127271862</v>
       </c>
       <c r="B117" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811875</v>
+        <v>812079</v>
       </c>
       <c r="R117" t="n">
-        <v>7389980</v>
+        <v>7389800</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12042,6 +12046,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12068,49 +12077,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271862</v>
+        <v>127271866</v>
       </c>
       <c r="B118" t="n">
-        <v>57661</v>
+        <v>56853</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>812079</v>
+        <v>811935</v>
       </c>
       <c r="R118" t="n">
-        <v>7389800</v>
+        <v>7389957</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12143,11 +12148,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12280,45 +12280,49 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271918</v>
+        <v>127271850</v>
       </c>
       <c r="B120" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812162</v>
+        <v>812124</v>
       </c>
       <c r="R120" t="n">
-        <v>7389925</v>
+        <v>7389758</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12351,6 +12355,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12377,49 +12386,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271850</v>
+        <v>127271918</v>
       </c>
       <c r="B121" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812124</v>
+        <v>812162</v>
       </c>
       <c r="R121" t="n">
-        <v>7389758</v>
+        <v>7389925</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12452,11 +12457,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049608</v>
+        <v>127049592</v>
       </c>
       <c r="B3" t="n">
-        <v>97331</v>
+        <v>79636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812055</v>
+        <v>812072</v>
       </c>
       <c r="R3" t="n">
-        <v>7389491</v>
+        <v>7389539</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049592</v>
+        <v>127049602</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812072</v>
+        <v>812043</v>
       </c>
       <c r="R4" t="n">
-        <v>7389539</v>
+        <v>7389685</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -940,6 +944,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,49 +975,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049602</v>
+        <v>127049608</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>97331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812043</v>
+        <v>812055</v>
       </c>
       <c r="R5" t="n">
-        <v>7389685</v>
+        <v>7389491</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1041,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049611</v>
+        <v>127049638</v>
       </c>
       <c r="B6" t="n">
-        <v>97331</v>
+        <v>92620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>812004</v>
+        <v>811921</v>
       </c>
       <c r="R6" t="n">
-        <v>7389528</v>
+        <v>7389590</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049638</v>
+        <v>127049639</v>
       </c>
       <c r="B7" t="n">
         <v>92620</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811921</v>
+        <v>811937</v>
       </c>
       <c r="R7" t="n">
-        <v>7389590</v>
+        <v>7389558</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049639</v>
+        <v>127049611</v>
       </c>
       <c r="B8" t="n">
-        <v>92620</v>
+        <v>97331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811937</v>
+        <v>812004</v>
       </c>
       <c r="R8" t="n">
-        <v>7389558</v>
+        <v>7389528</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049628</v>
+        <v>127049620</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811980</v>
+        <v>812079</v>
       </c>
       <c r="R12" t="n">
-        <v>7389540</v>
+        <v>7389510</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049618</v>
+        <v>127049628</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>812047</v>
+        <v>811980</v>
       </c>
       <c r="R13" t="n">
-        <v>7389473</v>
+        <v>7389540</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049596</v>
+        <v>127049618</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811955</v>
+        <v>812047</v>
       </c>
       <c r="R14" t="n">
-        <v>7389537</v>
+        <v>7389473</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049620</v>
+        <v>127049596</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>812079</v>
+        <v>811955</v>
       </c>
       <c r="R15" t="n">
-        <v>7389510</v>
+        <v>7389537</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049637</v>
+        <v>127049593</v>
       </c>
       <c r="B22" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R22" t="n">
-        <v>7389571</v>
+        <v>7389548</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049640</v>
+        <v>127049637</v>
       </c>
       <c r="B23" t="n">
         <v>92620</v>
@@ -2768,7 +2768,7 @@
         <v>811936</v>
       </c>
       <c r="R23" t="n">
-        <v>7389556</v>
+        <v>7389571</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2827,32 +2827,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127049593</v>
+        <v>127049640</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R24" t="n">
-        <v>7389548</v>
+        <v>7389556</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -4874,32 +4874,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049626</v>
+        <v>127049606</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>97331</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811984</v>
+        <v>812115</v>
       </c>
       <c r="R45" t="n">
-        <v>7389705</v>
+        <v>7389567</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049641</v>
+        <v>127049626</v>
       </c>
       <c r="B46" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811963</v>
+        <v>811984</v>
       </c>
       <c r="R46" t="n">
-        <v>7389548</v>
+        <v>7389705</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,32 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049614</v>
+        <v>127049641</v>
       </c>
       <c r="B47" t="n">
-        <v>80993</v>
+        <v>92620</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>812078</v>
+        <v>811963</v>
       </c>
       <c r="R47" t="n">
-        <v>7389625</v>
+        <v>7389548</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5165,32 +5165,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127049606</v>
+        <v>127049614</v>
       </c>
       <c r="B48" t="n">
-        <v>97331</v>
+        <v>80993</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>812115</v>
+        <v>812078</v>
       </c>
       <c r="R48" t="n">
-        <v>7389567</v>
+        <v>7389625</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B52" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,38 +5567,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R52" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5631,11 +5627,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5662,10 +5653,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B53" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5673,34 +5664,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R53" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5733,6 +5728,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271855</v>
+        <v>127271883</v>
       </c>
       <c r="B61" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,38 +6449,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811859</v>
+        <v>812004</v>
       </c>
       <c r="R61" t="n">
-        <v>7390026</v>
+        <v>7389960</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6513,11 +6509,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6544,32 +6535,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271883</v>
+        <v>127271911</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812004</v>
+        <v>812117</v>
       </c>
       <c r="R62" t="n">
-        <v>7389960</v>
+        <v>7389993</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6641,45 +6632,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271911</v>
+        <v>127271855</v>
       </c>
       <c r="B63" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812117</v>
+        <v>811859</v>
       </c>
       <c r="R63" t="n">
-        <v>7389993</v>
+        <v>7390026</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6712,6 +6707,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8018,45 +8018,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127271851</v>
       </c>
       <c r="B77" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>812117</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389911</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8089,6 +8093,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8115,45 +8124,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127271865</v>
       </c>
       <c r="B78" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>812024</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389558</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8186,6 +8199,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8212,32 +8230,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271917</v>
       </c>
       <c r="B79" t="n">
-        <v>91348</v>
+        <v>92620</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8265,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>812088</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389936</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8309,49 +8327,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271851</v>
+        <v>127271908</v>
       </c>
       <c r="B80" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812117</v>
+        <v>812128</v>
       </c>
       <c r="R80" t="n">
-        <v>7389911</v>
+        <v>7389752</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8384,11 +8398,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8415,10 +8424,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271865</v>
+        <v>127271877</v>
       </c>
       <c r="B81" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8426,38 +8435,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812024</v>
+        <v>812195</v>
       </c>
       <c r="R81" t="n">
-        <v>7389558</v>
+        <v>7389776</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8490,11 +8495,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9205,7 +9205,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271891</v>
+        <v>127271894</v>
       </c>
       <c r="B89" t="n">
         <v>79018</v>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812077</v>
+        <v>811982</v>
       </c>
       <c r="R89" t="n">
-        <v>7389800</v>
+        <v>7389609</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271894</v>
+        <v>127271836</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,21 +9313,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811982</v>
+        <v>811958</v>
       </c>
       <c r="R90" t="n">
-        <v>7389609</v>
+        <v>7389950</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9399,10 +9399,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271836</v>
+        <v>127271891</v>
       </c>
       <c r="B91" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9410,21 +9410,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9434,10 +9434,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811958</v>
+        <v>812077</v>
       </c>
       <c r="R91" t="n">
-        <v>7389950</v>
+        <v>7389800</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271840</v>
+        <v>127271856</v>
       </c>
       <c r="B94" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,34 +9715,38 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812127</v>
+        <v>811876</v>
       </c>
       <c r="R94" t="n">
-        <v>7389936</v>
+        <v>7389968</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9775,6 +9779,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9801,7 +9810,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271856</v>
+        <v>127271857</v>
       </c>
       <c r="B95" t="n">
         <v>57661</v>
@@ -9830,20 +9839,16 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811876</v>
+        <v>812050</v>
       </c>
       <c r="R95" t="n">
-        <v>7389968</v>
+        <v>7389925</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9876,11 +9881,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9907,10 +9907,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271857</v>
+        <v>127271840</v>
       </c>
       <c r="B96" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9918,21 +9918,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812050</v>
+        <v>812127</v>
       </c>
       <c r="R96" t="n">
-        <v>7389925</v>
+        <v>7389936</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -12174,49 +12174,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271861</v>
+        <v>127271918</v>
       </c>
       <c r="B119" t="n">
-        <v>57661</v>
+        <v>92620</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812106</v>
+        <v>812162</v>
       </c>
       <c r="R119" t="n">
-        <v>7389819</v>
+        <v>7389925</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12249,11 +12245,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12280,7 +12271,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271850</v>
+        <v>127271861</v>
       </c>
       <c r="B120" t="n">
         <v>57661</v>
@@ -12319,10 +12310,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812124</v>
+        <v>812106</v>
       </c>
       <c r="R120" t="n">
-        <v>7389758</v>
+        <v>7389819</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12359,7 +12350,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Mellersta området</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12386,45 +12377,49 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271918</v>
+        <v>127271850</v>
       </c>
       <c r="B121" t="n">
-        <v>92620</v>
+        <v>57661</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812162</v>
+        <v>812124</v>
       </c>
       <c r="R121" t="n">
-        <v>7389925</v>
+        <v>7389758</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12457,6 +12452,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127049629</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049592</v>
+        <v>127049602</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812072</v>
+        <v>812043</v>
       </c>
       <c r="R3" t="n">
-        <v>7389539</v>
+        <v>7389685</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -843,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049602</v>
+        <v>127049592</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,38 +889,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812043</v>
+        <v>812072</v>
       </c>
       <c r="R4" t="n">
-        <v>7389685</v>
+        <v>7389539</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -944,11 +949,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,7 +978,7 @@
         <v>127049608</v>
       </c>
       <c r="B5" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127049638</v>
       </c>
       <c r="B6" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>127049639</v>
       </c>
       <c r="B7" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>127049611</v>
       </c>
       <c r="B8" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127049595</v>
+        <v>127049621</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811948</v>
+        <v>812153</v>
       </c>
       <c r="R9" t="n">
-        <v>7389545</v>
+        <v>7389594</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127049621</v>
+        <v>127049595</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>812153</v>
+        <v>811948</v>
       </c>
       <c r="R10" t="n">
-        <v>7389594</v>
+        <v>7389545</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1560,7 +1560,7 @@
         <v>127049612</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049620</v>
+        <v>127049628</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>812079</v>
+        <v>811980</v>
       </c>
       <c r="R12" t="n">
-        <v>7389510</v>
+        <v>7389540</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049628</v>
+        <v>127049620</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811980</v>
+        <v>812079</v>
       </c>
       <c r="R13" t="n">
-        <v>7389540</v>
+        <v>7389510</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1851,7 +1851,7 @@
         <v>127049618</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127049596</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>127049623</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127049645</v>
       </c>
       <c r="B17" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049630</v>
+        <v>127049622</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>812021</v>
+        <v>812088</v>
       </c>
       <c r="R18" t="n">
-        <v>7389474</v>
+        <v>7389588</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049631</v>
+        <v>127049601</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,34 +2344,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812026</v>
+        <v>811940</v>
       </c>
       <c r="R19" t="n">
-        <v>7389461</v>
+        <v>7389556</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2404,6 +2408,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2430,10 +2439,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127049622</v>
+        <v>127049631</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>812088</v>
+        <v>812026</v>
       </c>
       <c r="R20" t="n">
-        <v>7389588</v>
+        <v>7389461</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2527,10 +2536,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127049601</v>
+        <v>127049630</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2538,38 +2547,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811940</v>
+        <v>812021</v>
       </c>
       <c r="R21" t="n">
-        <v>7389556</v>
+        <v>7389474</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2602,11 +2607,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049593</v>
+        <v>127049637</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R22" t="n">
-        <v>7389548</v>
+        <v>7389571</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049637</v>
+        <v>127049640</v>
       </c>
       <c r="B23" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>811936</v>
       </c>
       <c r="R23" t="n">
-        <v>7389571</v>
+        <v>7389556</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2827,32 +2827,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127049640</v>
+        <v>127049593</v>
       </c>
       <c r="B24" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R24" t="n">
-        <v>7389556</v>
+        <v>7389548</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2927,7 +2927,7 @@
         <v>127049613</v>
       </c>
       <c r="B25" t="n">
-        <v>80993</v>
+        <v>80995</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127049605</v>
       </c>
       <c r="B26" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049642</v>
+        <v>127049633</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>78687</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811969</v>
+        <v>811950</v>
       </c>
       <c r="R27" t="n">
-        <v>7389545</v>
+        <v>7389574</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049643</v>
+        <v>127049642</v>
       </c>
       <c r="B28" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811987</v>
+        <v>811969</v>
       </c>
       <c r="R28" t="n">
-        <v>7389527</v>
+        <v>7389545</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049609</v>
+        <v>127049643</v>
       </c>
       <c r="B29" t="n">
-        <v>97331</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3323,21 +3323,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811991</v>
+        <v>811987</v>
       </c>
       <c r="R29" t="n">
-        <v>7389623</v>
+        <v>7389527</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,32 +3409,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049633</v>
+        <v>127049609</v>
       </c>
       <c r="B30" t="n">
-        <v>78685</v>
+        <v>97333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811950</v>
+        <v>811991</v>
       </c>
       <c r="R30" t="n">
-        <v>7389574</v>
+        <v>7389623</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049594</v>
+        <v>127049610</v>
       </c>
       <c r="B31" t="n">
-        <v>79636</v>
+        <v>97333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811945</v>
+        <v>811967</v>
       </c>
       <c r="R31" t="n">
-        <v>7389563</v>
+        <v>7389626</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049610</v>
+        <v>127049594</v>
       </c>
       <c r="B32" t="n">
-        <v>97331</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811967</v>
+        <v>811945</v>
       </c>
       <c r="R32" t="n">
-        <v>7389626</v>
+        <v>7389563</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3703,7 +3703,7 @@
         <v>127049635</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>127049625</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>127049619</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127049607</v>
       </c>
       <c r="B36" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127049616</v>
+        <v>127049624</v>
       </c>
       <c r="B37" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811934</v>
+        <v>812000</v>
       </c>
       <c r="R37" t="n">
-        <v>7389548</v>
+        <v>7389736</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127049624</v>
+        <v>127049616</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>812000</v>
+        <v>811934</v>
       </c>
       <c r="R38" t="n">
-        <v>7389736</v>
+        <v>7389548</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4285,7 +4285,7 @@
         <v>127049648</v>
       </c>
       <c r="B39" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127049591</v>
+        <v>127049632</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4391,34 +4391,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>812066</v>
+        <v>812117</v>
       </c>
       <c r="R40" t="n">
-        <v>7389504</v>
+        <v>7389623</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4451,6 +4455,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4477,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127049647</v>
+        <v>127049591</v>
       </c>
       <c r="B41" t="n">
-        <v>77996</v>
+        <v>79638</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4488,21 +4497,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4512,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811948</v>
+        <v>812066</v>
       </c>
       <c r="R41" t="n">
-        <v>7389545</v>
+        <v>7389504</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4574,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127049632</v>
+        <v>127049647</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>77998</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4585,38 +4594,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>812117</v>
+        <v>811948</v>
       </c>
       <c r="R42" t="n">
-        <v>7389623</v>
+        <v>7389545</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4649,11 +4654,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4680,32 +4680,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127049634</v>
+        <v>127049615</v>
       </c>
       <c r="B43" t="n">
-        <v>92620</v>
+        <v>80995</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>812073</v>
+        <v>811948</v>
       </c>
       <c r="R43" t="n">
-        <v>7389533</v>
+        <v>7389545</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4777,32 +4777,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127049615</v>
+        <v>127049634</v>
       </c>
       <c r="B44" t="n">
-        <v>80993</v>
+        <v>92622</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811948</v>
+        <v>812073</v>
       </c>
       <c r="R44" t="n">
-        <v>7389545</v>
+        <v>7389533</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4874,10 +4874,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049606</v>
+        <v>127049641</v>
       </c>
       <c r="B45" t="n">
-        <v>97331</v>
+        <v>92622</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>812115</v>
+        <v>811963</v>
       </c>
       <c r="R45" t="n">
-        <v>7389567</v>
+        <v>7389548</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,10 +4971,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049626</v>
+        <v>127049614</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>80995</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4982,21 +4982,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811984</v>
+        <v>812078</v>
       </c>
       <c r="R46" t="n">
-        <v>7389705</v>
+        <v>7389625</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,32 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049641</v>
+        <v>127049626</v>
       </c>
       <c r="B47" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811963</v>
+        <v>811984</v>
       </c>
       <c r="R47" t="n">
-        <v>7389548</v>
+        <v>7389705</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5165,32 +5165,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127049614</v>
+        <v>127049606</v>
       </c>
       <c r="B48" t="n">
-        <v>80993</v>
+        <v>97333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1049</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>812078</v>
+        <v>812115</v>
       </c>
       <c r="R48" t="n">
-        <v>7389625</v>
+        <v>7389567</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5265,7 +5265,7 @@
         <v>127049600</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>127049598</v>
       </c>
       <c r="B50" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>127049599</v>
       </c>
       <c r="B51" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>127271845</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>127271854</v>
       </c>
       <c r="B53" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>127271889</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>127271920</v>
       </c>
       <c r="B55" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127271925</v>
       </c>
       <c r="B56" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>127271847</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>127271910</v>
       </c>
       <c r="B58" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>127271923</v>
       </c>
       <c r="B59" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6341,32 +6341,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271875</v>
+        <v>127271883</v>
       </c>
       <c r="B60" t="n">
-        <v>58031</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812093</v>
+        <v>812004</v>
       </c>
       <c r="R60" t="n">
-        <v>7389656</v>
+        <v>7389960</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6438,32 +6438,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271883</v>
+        <v>127271875</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>58033</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812004</v>
+        <v>812093</v>
       </c>
       <c r="R61" t="n">
-        <v>7389960</v>
+        <v>7389656</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6535,45 +6535,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271911</v>
+        <v>127271855</v>
       </c>
       <c r="B62" t="n">
-        <v>92620</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812117</v>
+        <v>811859</v>
       </c>
       <c r="R62" t="n">
-        <v>7389993</v>
+        <v>7390026</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6606,6 +6610,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6632,49 +6641,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271855</v>
+        <v>127271911</v>
       </c>
       <c r="B63" t="n">
-        <v>57661</v>
+        <v>92622</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811859</v>
+        <v>812117</v>
       </c>
       <c r="R63" t="n">
-        <v>7390026</v>
+        <v>7389993</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6707,11 +6712,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271888</v>
+        <v>127271858</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,34 +6749,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811957</v>
+        <v>812068</v>
       </c>
       <c r="R64" t="n">
-        <v>7389943</v>
+        <v>7389929</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6809,6 +6813,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6835,10 +6844,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271858</v>
+        <v>127271888</v>
       </c>
       <c r="B65" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6846,38 +6855,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>812068</v>
+        <v>811957</v>
       </c>
       <c r="R65" t="n">
-        <v>7389929</v>
+        <v>7389943</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6910,11 +6915,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271886</v>
+        <v>127271881</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811852</v>
+        <v>812133</v>
       </c>
       <c r="R66" t="n">
-        <v>7390093</v>
+        <v>7389830</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7038,32 +7038,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271912</v>
+        <v>127271842</v>
       </c>
       <c r="B67" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811981</v>
+        <v>812161</v>
       </c>
       <c r="R67" t="n">
-        <v>7389988</v>
+        <v>7389878</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7135,32 +7135,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271921</v>
+        <v>127271841</v>
       </c>
       <c r="B68" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7170,10 +7170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812092</v>
+        <v>812139</v>
       </c>
       <c r="R68" t="n">
-        <v>7389721</v>
+        <v>7389967</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,32 +7232,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271909</v>
+        <v>127271886</v>
       </c>
       <c r="B69" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812175</v>
+        <v>811852</v>
       </c>
       <c r="R69" t="n">
-        <v>7389748</v>
+        <v>7390093</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,10 +7329,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271881</v>
+        <v>127271852</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7340,34 +7340,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812133</v>
+        <v>812054</v>
       </c>
       <c r="R70" t="n">
-        <v>7389830</v>
+        <v>7390009</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7400,6 +7404,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7426,49 +7435,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271852</v>
+        <v>127271912</v>
       </c>
       <c r="B71" t="n">
-        <v>57661</v>
+        <v>92622</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812054</v>
+        <v>811981</v>
       </c>
       <c r="R71" t="n">
-        <v>7390009</v>
+        <v>7389988</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7501,11 +7506,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7532,32 +7532,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271876</v>
+        <v>127271921</v>
       </c>
       <c r="B72" t="n">
-        <v>80993</v>
+        <v>92622</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7567,10 +7567,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812128</v>
+        <v>812092</v>
       </c>
       <c r="R72" t="n">
-        <v>7390038</v>
+        <v>7389721</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7611,7 +7611,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7630,32 +7629,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271841</v>
+        <v>127271909</v>
       </c>
       <c r="B73" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7665,10 +7664,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812139</v>
+        <v>812175</v>
       </c>
       <c r="R73" t="n">
-        <v>7389967</v>
+        <v>7389748</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7727,10 +7726,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271842</v>
+        <v>127271876</v>
       </c>
       <c r="B74" t="n">
-        <v>79636</v>
+        <v>80995</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7738,21 +7737,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7762,10 +7761,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812161</v>
+        <v>812128</v>
       </c>
       <c r="R74" t="n">
-        <v>7389878</v>
+        <v>7390038</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7806,6 +7805,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>127271880</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>127271924</v>
       </c>
       <c r="B76" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>127271851</v>
       </c>
       <c r="B77" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>127271865</v>
       </c>
       <c r="B78" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>127271917</v>
       </c>
       <c r="B79" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127271908</v>
       </c>
       <c r="B80" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>127271877</v>
       </c>
       <c r="B81" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>127271895</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>127271878</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R84" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8815,7 +8815,7 @@
         <v>127271890</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271843</v>
+        <v>127271882</v>
       </c>
       <c r="B86" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8920,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812074</v>
+        <v>812120</v>
       </c>
       <c r="R86" t="n">
-        <v>7389829</v>
+        <v>7389917</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B87" t="n">
-        <v>57658</v>
+        <v>79638</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R87" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,11 +9077,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9108,10 +9103,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B88" t="n">
-        <v>79636</v>
+        <v>57660</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9119,21 +9114,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R88" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9179,6 +9174,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271894</v>
+        <v>127271849</v>
       </c>
       <c r="B89" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811982</v>
+        <v>812114</v>
       </c>
       <c r="R89" t="n">
-        <v>7389609</v>
+        <v>7389969</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9276,6 +9276,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9302,10 +9307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271836</v>
+        <v>127271897</v>
       </c>
       <c r="B90" t="n">
-        <v>79636</v>
+        <v>57663</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,34 +9318,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811958</v>
+        <v>812122</v>
       </c>
       <c r="R90" t="n">
-        <v>7389950</v>
+        <v>7389709</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9373,6 +9382,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9399,10 +9413,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271891</v>
+        <v>127271836</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9410,21 +9424,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9434,10 +9448,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>812077</v>
+        <v>811958</v>
       </c>
       <c r="R91" t="n">
-        <v>7389800</v>
+        <v>7389950</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9496,10 +9510,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271849</v>
+        <v>127271891</v>
       </c>
       <c r="B92" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9507,21 +9521,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9531,10 +9545,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>812114</v>
+        <v>812077</v>
       </c>
       <c r="R92" t="n">
-        <v>7389969</v>
+        <v>7389800</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9567,11 +9581,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9598,10 +9607,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271897</v>
+        <v>127271894</v>
       </c>
       <c r="B93" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9609,38 +9618,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>812122</v>
+        <v>811982</v>
       </c>
       <c r="R93" t="n">
-        <v>7389709</v>
+        <v>7389609</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9673,11 +9678,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271856</v>
+        <v>127271840</v>
       </c>
       <c r="B94" t="n">
-        <v>57661</v>
+        <v>79638</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,38 +9715,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811876</v>
+        <v>812127</v>
       </c>
       <c r="R94" t="n">
-        <v>7389968</v>
+        <v>7389936</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9779,11 +9775,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9813,7 +9804,7 @@
         <v>127271857</v>
       </c>
       <c r="B95" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9907,10 +9898,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271840</v>
+        <v>127271868</v>
       </c>
       <c r="B96" t="n">
-        <v>79636</v>
+        <v>57823</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9918,21 +9909,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9942,10 +9933,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812127</v>
+        <v>812092</v>
       </c>
       <c r="R96" t="n">
-        <v>7389936</v>
+        <v>7389656</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10004,10 +9995,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271868</v>
+        <v>127271856</v>
       </c>
       <c r="B97" t="n">
-        <v>57821</v>
+        <v>57663</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,34 +10006,38 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812092</v>
+        <v>811876</v>
       </c>
       <c r="R97" t="n">
-        <v>7389656</v>
+        <v>7389968</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10075,6 +10070,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10104,7 +10104,7 @@
         <v>127271915</v>
       </c>
       <c r="B98" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>127271874</v>
       </c>
       <c r="B99" t="n">
-        <v>57765</v>
+        <v>57767</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10295,10 +10295,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271864</v>
+        <v>127271893</v>
       </c>
       <c r="B100" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10306,38 +10306,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812087</v>
+        <v>812066</v>
       </c>
       <c r="R100" t="n">
-        <v>7389653</v>
+        <v>7389634</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10370,11 +10366,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10401,32 +10392,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271907</v>
+        <v>127271884</v>
       </c>
       <c r="B101" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10436,10 +10427,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>812162</v>
+        <v>811977</v>
       </c>
       <c r="R101" t="n">
-        <v>7389625</v>
+        <v>7389985</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10498,10 +10489,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271893</v>
+        <v>127271864</v>
       </c>
       <c r="B102" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10509,34 +10500,38 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>812066</v>
+        <v>812087</v>
       </c>
       <c r="R102" t="n">
-        <v>7389634</v>
+        <v>7389653</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10569,6 +10564,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10595,10 +10595,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271916</v>
+        <v>127271907</v>
       </c>
       <c r="B103" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811958</v>
+        <v>812162</v>
       </c>
       <c r="R103" t="n">
-        <v>7389946</v>
+        <v>7389625</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10692,32 +10692,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271884</v>
+        <v>127271916</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10727,10 +10727,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811977</v>
+        <v>811958</v>
       </c>
       <c r="R104" t="n">
-        <v>7389985</v>
+        <v>7389946</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10789,32 +10789,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271913</v>
+        <v>127271844</v>
       </c>
       <c r="B105" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811963</v>
+        <v>812114</v>
       </c>
       <c r="R105" t="n">
-        <v>7390029</v>
+        <v>7389680</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10889,7 +10889,7 @@
         <v>127271892</v>
       </c>
       <c r="B106" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>127271879</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11080,45 +11080,49 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271906</v>
+        <v>127271853</v>
       </c>
       <c r="B108" t="n">
-        <v>92620</v>
+        <v>57663</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812166</v>
+        <v>811970</v>
       </c>
       <c r="R108" t="n">
-        <v>7389625</v>
+        <v>7390085</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11151,6 +11155,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11177,49 +11186,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271853</v>
+        <v>127271913</v>
       </c>
       <c r="B109" t="n">
-        <v>57661</v>
+        <v>92622</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811970</v>
+        <v>811963</v>
       </c>
       <c r="R109" t="n">
-        <v>7390085</v>
+        <v>7390029</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11252,11 +11257,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11283,32 +11283,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271844</v>
+        <v>127271906</v>
       </c>
       <c r="B110" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>812114</v>
+        <v>812166</v>
       </c>
       <c r="R110" t="n">
-        <v>7389680</v>
+        <v>7389625</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11383,7 +11383,7 @@
         <v>127271922</v>
       </c>
       <c r="B111" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>127271885</v>
       </c>
       <c r="B112" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>127271860</v>
       </c>
       <c r="B113" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11680,32 +11680,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271887</v>
+        <v>127271866</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>56855</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811866</v>
+        <v>811935</v>
       </c>
       <c r="R114" t="n">
-        <v>7390052</v>
+        <v>7389957</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11780,7 +11780,7 @@
         <v>127271919</v>
       </c>
       <c r="B115" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>127271914</v>
       </c>
       <c r="B116" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11971,10 +11971,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271862</v>
+        <v>127271887</v>
       </c>
       <c r="B117" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11982,38 +11982,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>812079</v>
+        <v>811866</v>
       </c>
       <c r="R117" t="n">
-        <v>7389800</v>
+        <v>7390052</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12046,11 +12042,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12077,45 +12068,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271866</v>
+        <v>127271862</v>
       </c>
       <c r="B118" t="n">
-        <v>56853</v>
+        <v>57663</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811935</v>
+        <v>812079</v>
       </c>
       <c r="R118" t="n">
-        <v>7389957</v>
+        <v>7389800</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12148,6 +12143,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12174,45 +12174,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271918</v>
+        <v>127271850</v>
       </c>
       <c r="B119" t="n">
-        <v>92620</v>
+        <v>57663</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812162</v>
+        <v>812124</v>
       </c>
       <c r="R119" t="n">
-        <v>7389925</v>
+        <v>7389758</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12245,6 +12249,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12271,49 +12280,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271861</v>
+        <v>127271918</v>
       </c>
       <c r="B120" t="n">
-        <v>57661</v>
+        <v>92622</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812106</v>
+        <v>812162</v>
       </c>
       <c r="R120" t="n">
-        <v>7389819</v>
+        <v>7389925</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12346,11 +12351,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12377,10 +12377,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271850</v>
+        <v>127271861</v>
       </c>
       <c r="B121" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12416,10 +12416,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812124</v>
+        <v>812106</v>
       </c>
       <c r="R121" t="n">
-        <v>7389758</v>
+        <v>7389819</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Mellersta området</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12486,7 +12486,7 @@
         <v>127388830</v>
       </c>
       <c r="B122" t="n">
-        <v>91491</v>
+        <v>91493</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049602</v>
+        <v>127049592</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812043</v>
+        <v>812072</v>
       </c>
       <c r="R3" t="n">
-        <v>7389685</v>
+        <v>7389539</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049592</v>
+        <v>127049602</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,34 +880,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812072</v>
+        <v>812043</v>
       </c>
       <c r="R4" t="n">
-        <v>7389539</v>
+        <v>7389685</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -949,6 +944,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127049621</v>
+        <v>127049595</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>812153</v>
+        <v>811948</v>
       </c>
       <c r="R9" t="n">
-        <v>7389594</v>
+        <v>7389545</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127049595</v>
+        <v>127049621</v>
       </c>
       <c r="B10" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811948</v>
+        <v>812153</v>
       </c>
       <c r="R10" t="n">
-        <v>7389545</v>
+        <v>7389594</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049628</v>
+        <v>127049620</v>
       </c>
       <c r="B12" t="n">
         <v>79020</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811980</v>
+        <v>812079</v>
       </c>
       <c r="R12" t="n">
-        <v>7389540</v>
+        <v>7389510</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049620</v>
+        <v>127049628</v>
       </c>
       <c r="B13" t="n">
         <v>79020</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>812079</v>
+        <v>811980</v>
       </c>
       <c r="R13" t="n">
-        <v>7389510</v>
+        <v>7389540</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049622</v>
+        <v>127049630</v>
       </c>
       <c r="B18" t="n">
         <v>79020</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>812088</v>
+        <v>812021</v>
       </c>
       <c r="R18" t="n">
-        <v>7389588</v>
+        <v>7389474</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049601</v>
+        <v>127049631</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,38 +2344,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811940</v>
+        <v>812026</v>
       </c>
       <c r="R19" t="n">
-        <v>7389556</v>
+        <v>7389461</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2408,11 +2404,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2439,7 +2430,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127049631</v>
+        <v>127049622</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2474,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>812026</v>
+        <v>812088</v>
       </c>
       <c r="R20" t="n">
-        <v>7389461</v>
+        <v>7389588</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,10 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127049630</v>
+        <v>127049601</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2547,34 +2538,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>812021</v>
+        <v>811940</v>
       </c>
       <c r="R21" t="n">
-        <v>7389474</v>
+        <v>7389556</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2607,6 +2602,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3118,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049633</v>
+        <v>127049609</v>
       </c>
       <c r="B27" t="n">
-        <v>78687</v>
+        <v>97333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811950</v>
+        <v>811991</v>
       </c>
       <c r="R27" t="n">
-        <v>7389574</v>
+        <v>7389623</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049642</v>
+        <v>127049633</v>
       </c>
       <c r="B28" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811969</v>
+        <v>811950</v>
       </c>
       <c r="R28" t="n">
-        <v>7389545</v>
+        <v>7389574</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049643</v>
+        <v>127049642</v>
       </c>
       <c r="B29" t="n">
         <v>92622</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811987</v>
+        <v>811969</v>
       </c>
       <c r="R29" t="n">
-        <v>7389527</v>
+        <v>7389545</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049609</v>
+        <v>127049643</v>
       </c>
       <c r="B30" t="n">
-        <v>97333</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811991</v>
+        <v>811987</v>
       </c>
       <c r="R30" t="n">
-        <v>7389623</v>
+        <v>7389527</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049610</v>
+        <v>127049594</v>
       </c>
       <c r="B31" t="n">
-        <v>97333</v>
+        <v>79638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811967</v>
+        <v>811945</v>
       </c>
       <c r="R31" t="n">
-        <v>7389626</v>
+        <v>7389563</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049594</v>
+        <v>127049610</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>97333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811945</v>
+        <v>811967</v>
       </c>
       <c r="R32" t="n">
-        <v>7389563</v>
+        <v>7389626</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3700,10 +3700,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127049635</v>
+        <v>127049607</v>
       </c>
       <c r="B33" t="n">
-        <v>92622</v>
+        <v>97333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3711,21 +3711,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>812027</v>
+        <v>812105</v>
       </c>
       <c r="R33" t="n">
-        <v>7389564</v>
+        <v>7389559</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049625</v>
+        <v>127049635</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811987</v>
+        <v>812027</v>
       </c>
       <c r="R34" t="n">
-        <v>7389722</v>
+        <v>7389564</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127049619</v>
+        <v>127049625</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>812060</v>
+        <v>811987</v>
       </c>
       <c r="R35" t="n">
-        <v>7389489</v>
+        <v>7389722</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3991,32 +3991,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127049607</v>
+        <v>127049619</v>
       </c>
       <c r="B36" t="n">
-        <v>97333</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>812105</v>
+        <v>812060</v>
       </c>
       <c r="R36" t="n">
-        <v>7389559</v>
+        <v>7389489</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4874,32 +4874,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049641</v>
+        <v>127049626</v>
       </c>
       <c r="B45" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811963</v>
+        <v>811984</v>
       </c>
       <c r="R45" t="n">
-        <v>7389548</v>
+        <v>7389705</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049614</v>
+        <v>127049641</v>
       </c>
       <c r="B46" t="n">
-        <v>80995</v>
+        <v>92622</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>812078</v>
+        <v>811963</v>
       </c>
       <c r="R46" t="n">
-        <v>7389625</v>
+        <v>7389548</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049626</v>
+        <v>127049614</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>80995</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5079,21 +5079,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811984</v>
+        <v>812078</v>
       </c>
       <c r="R47" t="n">
-        <v>7389705</v>
+        <v>7389625</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B52" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,34 +5567,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R52" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5627,6 +5631,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5653,10 +5662,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5664,38 +5673,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R53" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5728,11 +5733,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B56" t="n">
-        <v>78426</v>
+        <v>92622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R56" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B57" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R57" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B58" t="n">
-        <v>92622</v>
+        <v>78426</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R58" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B59" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R59" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,32 +6341,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271883</v>
+        <v>127271911</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812004</v>
+        <v>812117</v>
       </c>
       <c r="R60" t="n">
-        <v>7389960</v>
+        <v>7389993</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6438,32 +6438,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271875</v>
+        <v>127271883</v>
       </c>
       <c r="B61" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812093</v>
+        <v>812004</v>
       </c>
       <c r="R61" t="n">
-        <v>7389656</v>
+        <v>7389960</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6535,27 +6535,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271855</v>
+        <v>127271875</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>58033</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6564,20 +6564,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811859</v>
+        <v>812093</v>
       </c>
       <c r="R62" t="n">
-        <v>7390026</v>
+        <v>7389656</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6610,11 +6606,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6641,45 +6632,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271911</v>
+        <v>127271855</v>
       </c>
       <c r="B63" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812117</v>
+        <v>811859</v>
       </c>
       <c r="R63" t="n">
-        <v>7389993</v>
+        <v>7390026</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6712,6 +6707,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271858</v>
+        <v>127271888</v>
       </c>
       <c r="B64" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,38 +6749,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>812068</v>
+        <v>811957</v>
       </c>
       <c r="R64" t="n">
-        <v>7389929</v>
+        <v>7389943</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6813,11 +6809,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6844,10 +6835,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271888</v>
+        <v>127271858</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6855,34 +6846,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811957</v>
+        <v>812068</v>
       </c>
       <c r="R65" t="n">
-        <v>7389943</v>
+        <v>7389929</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6915,6 +6910,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271881</v>
+        <v>127271876</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>80995</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812133</v>
+        <v>812128</v>
       </c>
       <c r="R66" t="n">
-        <v>7389830</v>
+        <v>7390038</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7020,6 +7020,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7038,10 +7039,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271842</v>
+        <v>127271881</v>
       </c>
       <c r="B67" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7049,21 +7050,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7074,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812161</v>
+        <v>812133</v>
       </c>
       <c r="R67" t="n">
-        <v>7389878</v>
+        <v>7389830</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7135,10 +7136,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271841</v>
+        <v>127271886</v>
       </c>
       <c r="B68" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7146,21 +7147,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7170,10 +7171,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812139</v>
+        <v>811852</v>
       </c>
       <c r="R68" t="n">
-        <v>7389967</v>
+        <v>7390093</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,10 +7233,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271886</v>
+        <v>127271842</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7243,21 +7244,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7267,10 +7268,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811852</v>
+        <v>812161</v>
       </c>
       <c r="R69" t="n">
-        <v>7390093</v>
+        <v>7389878</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,10 +7330,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271852</v>
+        <v>127271841</v>
       </c>
       <c r="B70" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7340,38 +7341,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812054</v>
+        <v>812139</v>
       </c>
       <c r="R70" t="n">
-        <v>7390009</v>
+        <v>7389967</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7404,11 +7401,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7435,45 +7427,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271912</v>
+        <v>127271852</v>
       </c>
       <c r="B71" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811981</v>
+        <v>812054</v>
       </c>
       <c r="R71" t="n">
-        <v>7389988</v>
+        <v>7390009</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7506,6 +7502,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7532,7 +7533,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271921</v>
+        <v>127271912</v>
       </c>
       <c r="B72" t="n">
         <v>92622</v>
@@ -7567,10 +7568,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812092</v>
+        <v>811981</v>
       </c>
       <c r="R72" t="n">
-        <v>7389721</v>
+        <v>7389988</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7629,7 +7630,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271909</v>
+        <v>127271921</v>
       </c>
       <c r="B73" t="n">
         <v>92622</v>
@@ -7664,10 +7665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812175</v>
+        <v>812092</v>
       </c>
       <c r="R73" t="n">
-        <v>7389748</v>
+        <v>7389721</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7726,32 +7727,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271876</v>
+        <v>127271909</v>
       </c>
       <c r="B74" t="n">
-        <v>80995</v>
+        <v>92622</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7761,10 +7762,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812128</v>
+        <v>812175</v>
       </c>
       <c r="R74" t="n">
-        <v>7390038</v>
+        <v>7389748</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7805,7 +7806,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -7824,32 +7824,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127271880</v>
+        <v>127271924</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>812207</v>
+        <v>812019</v>
       </c>
       <c r="R75" t="n">
-        <v>7389858</v>
+        <v>7389582</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7921,32 +7921,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127271924</v>
+        <v>127271880</v>
       </c>
       <c r="B76" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>812019</v>
+        <v>812207</v>
       </c>
       <c r="R76" t="n">
-        <v>7389582</v>
+        <v>7389858</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8018,49 +8018,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271851</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812117</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389911</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8093,11 +8089,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8124,49 +8115,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271865</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812024</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389558</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8199,11 +8186,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8230,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271917</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92622</v>
+        <v>91350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8265,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812088</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389936</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8327,45 +8309,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271908</v>
+        <v>127271851</v>
       </c>
       <c r="B80" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812128</v>
+        <v>812117</v>
       </c>
       <c r="R80" t="n">
-        <v>7389752</v>
+        <v>7389911</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8398,6 +8384,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8424,10 +8415,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271877</v>
+        <v>127271865</v>
       </c>
       <c r="B81" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8435,34 +8426,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812195</v>
+        <v>812024</v>
       </c>
       <c r="R81" t="n">
-        <v>7389776</v>
+        <v>7389558</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8495,6 +8490,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271843</v>
+        <v>127271890</v>
       </c>
       <c r="B84" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812074</v>
+        <v>812121</v>
       </c>
       <c r="R84" t="n">
-        <v>7389829</v>
+        <v>7389928</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8812,7 +8812,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271890</v>
+        <v>127271882</v>
       </c>
       <c r="B85" t="n">
         <v>79020</v>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812121</v>
+        <v>812120</v>
       </c>
       <c r="R85" t="n">
-        <v>7389928</v>
+        <v>7389917</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8920,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R86" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B87" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R87" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,6 +9077,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9103,10 +9108,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B88" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9114,21 +9119,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R88" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9174,11 +9179,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9413,10 +9413,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271836</v>
+        <v>127271891</v>
       </c>
       <c r="B91" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9424,21 +9424,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811958</v>
+        <v>812077</v>
       </c>
       <c r="R91" t="n">
-        <v>7389950</v>
+        <v>7389800</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9510,7 +9510,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271891</v>
+        <v>127271894</v>
       </c>
       <c r="B92" t="n">
         <v>79020</v>
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>812077</v>
+        <v>811982</v>
       </c>
       <c r="R92" t="n">
-        <v>7389800</v>
+        <v>7389609</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9607,10 +9607,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271894</v>
+        <v>127271836</v>
       </c>
       <c r="B93" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9618,21 +9618,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811982</v>
+        <v>811958</v>
       </c>
       <c r="R93" t="n">
-        <v>7389609</v>
+        <v>7389950</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271840</v>
+        <v>127271857</v>
       </c>
       <c r="B94" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812127</v>
+        <v>812050</v>
       </c>
       <c r="R94" t="n">
-        <v>7389936</v>
+        <v>7389925</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9801,7 +9801,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271857</v>
+        <v>127271856</v>
       </c>
       <c r="B95" t="n">
         <v>57663</v>
@@ -9830,16 +9830,20 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812050</v>
+        <v>811876</v>
       </c>
       <c r="R95" t="n">
-        <v>7389925</v>
+        <v>7389968</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9872,6 +9876,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9995,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271856</v>
+        <v>127271840</v>
       </c>
       <c r="B97" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10006,38 +10015,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811876</v>
+        <v>812127</v>
       </c>
       <c r="R97" t="n">
-        <v>7389968</v>
+        <v>7389936</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10070,11 +10075,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10295,32 +10295,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271893</v>
+        <v>127271907</v>
       </c>
       <c r="B100" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812066</v>
+        <v>812162</v>
       </c>
       <c r="R100" t="n">
-        <v>7389634</v>
+        <v>7389625</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10392,32 +10392,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271884</v>
+        <v>127271916</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811977</v>
+        <v>811958</v>
       </c>
       <c r="R101" t="n">
-        <v>7389985</v>
+        <v>7389946</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271864</v>
+        <v>127271893</v>
       </c>
       <c r="B102" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10500,38 +10500,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>812087</v>
+        <v>812066</v>
       </c>
       <c r="R102" t="n">
-        <v>7389653</v>
+        <v>7389634</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10564,11 +10560,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10595,32 +10586,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271907</v>
+        <v>127271884</v>
       </c>
       <c r="B103" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10630,10 +10621,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>812162</v>
+        <v>811977</v>
       </c>
       <c r="R103" t="n">
-        <v>7389625</v>
+        <v>7389985</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10692,45 +10683,49 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271916</v>
+        <v>127271864</v>
       </c>
       <c r="B104" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811958</v>
+        <v>812087</v>
       </c>
       <c r="R104" t="n">
-        <v>7389946</v>
+        <v>7389653</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10763,6 +10758,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,10 +10789,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271844</v>
+        <v>127271853</v>
       </c>
       <c r="B105" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10800,34 +10800,38 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>812114</v>
+        <v>811970</v>
       </c>
       <c r="R105" t="n">
-        <v>7389680</v>
+        <v>7390085</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10860,6 +10864,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10886,32 +10895,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271892</v>
+        <v>127271913</v>
       </c>
       <c r="B106" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10921,10 +10930,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812106</v>
+        <v>811963</v>
       </c>
       <c r="R106" t="n">
-        <v>7389684</v>
+        <v>7390029</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10983,32 +10992,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271879</v>
+        <v>127271906</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11018,10 +11027,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812228</v>
+        <v>812166</v>
       </c>
       <c r="R107" t="n">
-        <v>7389839</v>
+        <v>7389625</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11080,10 +11089,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271853</v>
+        <v>127271892</v>
       </c>
       <c r="B108" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11091,38 +11100,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811970</v>
+        <v>812106</v>
       </c>
       <c r="R108" t="n">
-        <v>7390085</v>
+        <v>7389684</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11155,11 +11160,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11186,32 +11186,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271913</v>
+        <v>127271879</v>
       </c>
       <c r="B109" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811963</v>
+        <v>812228</v>
       </c>
       <c r="R109" t="n">
-        <v>7390029</v>
+        <v>7389839</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11283,32 +11283,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271906</v>
+        <v>127271844</v>
       </c>
       <c r="B110" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>812166</v>
+        <v>812114</v>
       </c>
       <c r="R110" t="n">
-        <v>7389625</v>
+        <v>7389680</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271866</v>
+        <v>127271919</v>
       </c>
       <c r="B114" t="n">
-        <v>56855</v>
+        <v>92622</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11691,21 +11691,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811935</v>
+        <v>812158</v>
       </c>
       <c r="R114" t="n">
-        <v>7389957</v>
+        <v>7389883</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,7 +11777,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271919</v>
+        <v>127271914</v>
       </c>
       <c r="B115" t="n">
         <v>92622</v>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>812158</v>
+        <v>811875</v>
       </c>
       <c r="R115" t="n">
-        <v>7389883</v>
+        <v>7389980</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,32 +11874,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271914</v>
+        <v>127271887</v>
       </c>
       <c r="B116" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811875</v>
+        <v>811866</v>
       </c>
       <c r="R116" t="n">
-        <v>7389980</v>
+        <v>7390052</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11971,32 +11971,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271887</v>
+        <v>127271866</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811866</v>
+        <v>811935</v>
       </c>
       <c r="R117" t="n">
-        <v>7390052</v>
+        <v>7389957</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12174,49 +12174,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271850</v>
+        <v>127271918</v>
       </c>
       <c r="B119" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812124</v>
+        <v>812162</v>
       </c>
       <c r="R119" t="n">
-        <v>7389758</v>
+        <v>7389925</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12249,11 +12245,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12280,45 +12271,49 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271918</v>
+        <v>127271850</v>
       </c>
       <c r="B120" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812162</v>
+        <v>812124</v>
       </c>
       <c r="R120" t="n">
-        <v>7389925</v>
+        <v>7389758</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12351,6 +12346,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD120" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049637</v>
+        <v>127049593</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R22" t="n">
-        <v>7389571</v>
+        <v>7389548</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049640</v>
+        <v>127049637</v>
       </c>
       <c r="B23" t="n">
         <v>92622</v>
@@ -2768,7 +2768,7 @@
         <v>811936</v>
       </c>
       <c r="R23" t="n">
-        <v>7389556</v>
+        <v>7389571</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2827,32 +2827,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127049593</v>
+        <v>127049640</v>
       </c>
       <c r="B24" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R24" t="n">
-        <v>7389548</v>
+        <v>7389556</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049609</v>
+        <v>127049633</v>
       </c>
       <c r="B27" t="n">
-        <v>97333</v>
+        <v>78687</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811991</v>
+        <v>811950</v>
       </c>
       <c r="R27" t="n">
-        <v>7389623</v>
+        <v>7389574</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049633</v>
+        <v>127049642</v>
       </c>
       <c r="B28" t="n">
-        <v>78687</v>
+        <v>92622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811950</v>
+        <v>811969</v>
       </c>
       <c r="R28" t="n">
-        <v>7389574</v>
+        <v>7389545</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049642</v>
+        <v>127049643</v>
       </c>
       <c r="B29" t="n">
         <v>92622</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811969</v>
+        <v>811987</v>
       </c>
       <c r="R29" t="n">
-        <v>7389545</v>
+        <v>7389527</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049643</v>
+        <v>127049609</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>97333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811987</v>
+        <v>811991</v>
       </c>
       <c r="R30" t="n">
-        <v>7389527</v>
+        <v>7389623</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R54" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B55" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R55" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271911</v>
+        <v>127271875</v>
       </c>
       <c r="B60" t="n">
-        <v>92622</v>
+        <v>58033</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6352,21 +6352,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812117</v>
+        <v>812093</v>
       </c>
       <c r="R60" t="n">
-        <v>7389993</v>
+        <v>7389656</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6438,32 +6438,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271883</v>
+        <v>127271911</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812004</v>
+        <v>812117</v>
       </c>
       <c r="R61" t="n">
-        <v>7389960</v>
+        <v>7389993</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6535,32 +6535,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271875</v>
+        <v>127271883</v>
       </c>
       <c r="B62" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812093</v>
+        <v>812004</v>
       </c>
       <c r="R62" t="n">
-        <v>7389656</v>
+        <v>7389960</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8018,32 +8018,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127271877</v>
       </c>
       <c r="B77" t="n">
-        <v>92622</v>
+        <v>91350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>812195</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389776</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8115,7 +8115,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127271917</v>
       </c>
       <c r="B78" t="n">
         <v>92622</v>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>812088</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389936</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8212,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271908</v>
       </c>
       <c r="B79" t="n">
-        <v>91350</v>
+        <v>92622</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>812128</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389752</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B87" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R87" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,11 +9077,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9108,10 +9103,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B88" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9119,21 +9114,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R88" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9179,6 +9174,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9907,10 +9907,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271868</v>
+        <v>127271840</v>
       </c>
       <c r="B96" t="n">
-        <v>57823</v>
+        <v>79638</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9918,21 +9918,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812092</v>
+        <v>812127</v>
       </c>
       <c r="R96" t="n">
-        <v>7389656</v>
+        <v>7389936</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271840</v>
+        <v>127271868</v>
       </c>
       <c r="B97" t="n">
-        <v>79638</v>
+        <v>57823</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812127</v>
+        <v>812092</v>
       </c>
       <c r="R97" t="n">
-        <v>7389936</v>
+        <v>7389656</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10295,45 +10295,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271907</v>
+        <v>127271864</v>
       </c>
       <c r="B100" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812162</v>
+        <v>812087</v>
       </c>
       <c r="R100" t="n">
-        <v>7389625</v>
+        <v>7389653</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10366,6 +10370,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10392,7 +10401,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271916</v>
+        <v>127271907</v>
       </c>
       <c r="B101" t="n">
         <v>92622</v>
@@ -10427,10 +10436,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811958</v>
+        <v>812162</v>
       </c>
       <c r="R101" t="n">
-        <v>7389946</v>
+        <v>7389625</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10489,32 +10498,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271893</v>
+        <v>127271916</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10524,10 +10533,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>812066</v>
+        <v>811958</v>
       </c>
       <c r="R102" t="n">
-        <v>7389634</v>
+        <v>7389946</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10586,7 +10595,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271884</v>
+        <v>127271893</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10621,10 +10630,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811977</v>
+        <v>812066</v>
       </c>
       <c r="R103" t="n">
-        <v>7389985</v>
+        <v>7389634</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10683,10 +10692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271864</v>
+        <v>127271884</v>
       </c>
       <c r="B104" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10694,38 +10703,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>812087</v>
+        <v>811977</v>
       </c>
       <c r="R104" t="n">
-        <v>7389653</v>
+        <v>7389985</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10758,11 +10763,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11971,45 +11971,49 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271866</v>
+        <v>127271862</v>
       </c>
       <c r="B117" t="n">
-        <v>56855</v>
+        <v>57663</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811935</v>
+        <v>812079</v>
       </c>
       <c r="R117" t="n">
-        <v>7389957</v>
+        <v>7389800</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12042,6 +12046,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12068,49 +12077,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271862</v>
+        <v>127271866</v>
       </c>
       <c r="B118" t="n">
-        <v>57663</v>
+        <v>56855</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>812079</v>
+        <v>811935</v>
       </c>
       <c r="R118" t="n">
-        <v>7389800</v>
+        <v>7389957</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12143,11 +12148,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049592</v>
+        <v>127049608</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>97333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812072</v>
+        <v>812055</v>
       </c>
       <c r="R3" t="n">
-        <v>7389539</v>
+        <v>7389491</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049602</v>
+        <v>127049592</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,38 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812043</v>
+        <v>812072</v>
       </c>
       <c r="R4" t="n">
-        <v>7389685</v>
+        <v>7389539</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -944,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -975,45 +966,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049608</v>
+        <v>127049602</v>
       </c>
       <c r="B5" t="n">
-        <v>97333</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812055</v>
+        <v>812043</v>
       </c>
       <c r="R5" t="n">
-        <v>7389491</v>
+        <v>7389685</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1046,6 +1041,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049638</v>
+        <v>127049611</v>
       </c>
       <c r="B6" t="n">
-        <v>92622</v>
+        <v>97333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811921</v>
+        <v>812004</v>
       </c>
       <c r="R6" t="n">
-        <v>7389590</v>
+        <v>7389528</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049639</v>
+        <v>127049638</v>
       </c>
       <c r="B7" t="n">
         <v>92622</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811937</v>
+        <v>811921</v>
       </c>
       <c r="R7" t="n">
-        <v>7389558</v>
+        <v>7389590</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049611</v>
+        <v>127049639</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>812004</v>
+        <v>811937</v>
       </c>
       <c r="R8" t="n">
-        <v>7389528</v>
+        <v>7389558</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049628</v>
+        <v>127049596</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811980</v>
+        <v>811955</v>
       </c>
       <c r="R13" t="n">
-        <v>7389540</v>
+        <v>7389537</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049596</v>
+        <v>127049628</v>
       </c>
       <c r="B15" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811955</v>
+        <v>811980</v>
       </c>
       <c r="R15" t="n">
-        <v>7389537</v>
+        <v>7389540</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127049623</v>
+        <v>127049645</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>812077</v>
+        <v>812008</v>
       </c>
       <c r="R16" t="n">
-        <v>7389513</v>
+        <v>7389456</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127049645</v>
+        <v>127049623</v>
       </c>
       <c r="B17" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>812008</v>
+        <v>812077</v>
       </c>
       <c r="R17" t="n">
-        <v>7389456</v>
+        <v>7389513</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049630</v>
+        <v>127049601</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,34 +2247,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>812021</v>
+        <v>811940</v>
       </c>
       <c r="R18" t="n">
-        <v>7389474</v>
+        <v>7389556</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2307,6 +2311,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2333,7 +2342,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049631</v>
+        <v>127049630</v>
       </c>
       <c r="B19" t="n">
         <v>79020</v>
@@ -2368,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812026</v>
+        <v>812021</v>
       </c>
       <c r="R19" t="n">
-        <v>7389461</v>
+        <v>7389474</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2430,7 +2439,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127049622</v>
+        <v>127049631</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2465,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>812088</v>
+        <v>812026</v>
       </c>
       <c r="R20" t="n">
-        <v>7389588</v>
+        <v>7389461</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2527,10 +2536,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127049601</v>
+        <v>127049622</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2538,38 +2547,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811940</v>
+        <v>812088</v>
       </c>
       <c r="R21" t="n">
-        <v>7389556</v>
+        <v>7389588</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2602,11 +2607,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3797,32 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049635</v>
+        <v>127049625</v>
       </c>
       <c r="B34" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>812027</v>
+        <v>811987</v>
       </c>
       <c r="R34" t="n">
-        <v>7389564</v>
+        <v>7389722</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127049625</v>
+        <v>127049619</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811987</v>
+        <v>812060</v>
       </c>
       <c r="R35" t="n">
-        <v>7389722</v>
+        <v>7389489</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3991,32 +3991,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127049619</v>
+        <v>127049635</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>812060</v>
+        <v>812027</v>
       </c>
       <c r="R36" t="n">
-        <v>7389489</v>
+        <v>7389564</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127049624</v>
+        <v>127049616</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>812000</v>
+        <v>811934</v>
       </c>
       <c r="R37" t="n">
-        <v>7389736</v>
+        <v>7389548</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127049616</v>
+        <v>127049624</v>
       </c>
       <c r="B38" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811934</v>
+        <v>812000</v>
       </c>
       <c r="R38" t="n">
-        <v>7389548</v>
+        <v>7389736</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127049632</v>
+        <v>127049591</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4391,38 +4391,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>812117</v>
+        <v>812066</v>
       </c>
       <c r="R40" t="n">
-        <v>7389623</v>
+        <v>7389504</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4455,11 +4451,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4486,10 +4477,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127049591</v>
+        <v>127049647</v>
       </c>
       <c r="B41" t="n">
-        <v>79638</v>
+        <v>77998</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4497,21 +4488,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4521,10 +4512,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>812066</v>
+        <v>811948</v>
       </c>
       <c r="R41" t="n">
-        <v>7389504</v>
+        <v>7389545</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4583,10 +4574,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127049647</v>
+        <v>127049632</v>
       </c>
       <c r="B42" t="n">
-        <v>77998</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4594,34 +4585,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811948</v>
+        <v>812117</v>
       </c>
       <c r="R42" t="n">
-        <v>7389545</v>
+        <v>7389623</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4654,6 +4649,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4680,32 +4680,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127049615</v>
+        <v>127049634</v>
       </c>
       <c r="B43" t="n">
-        <v>80995</v>
+        <v>92622</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811948</v>
+        <v>812073</v>
       </c>
       <c r="R43" t="n">
-        <v>7389545</v>
+        <v>7389533</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4777,32 +4777,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127049634</v>
+        <v>127049615</v>
       </c>
       <c r="B44" t="n">
-        <v>92622</v>
+        <v>80995</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>812073</v>
+        <v>811948</v>
       </c>
       <c r="R44" t="n">
-        <v>7389533</v>
+        <v>7389545</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B52" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,38 +5567,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R52" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5631,11 +5627,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5662,10 +5653,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B53" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5673,34 +5664,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R53" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5733,6 +5728,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B54" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R54" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R55" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B56" t="n">
-        <v>92622</v>
+        <v>78426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R56" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B57" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R57" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B58" t="n">
-        <v>78426</v>
+        <v>92622</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R58" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B59" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R59" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,27 +6341,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271875</v>
+        <v>127271855</v>
       </c>
       <c r="B60" t="n">
-        <v>58033</v>
+        <v>57663</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6370,16 +6370,20 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812093</v>
+        <v>811859</v>
       </c>
       <c r="R60" t="n">
-        <v>7389656</v>
+        <v>7390026</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6412,6 +6416,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6438,10 +6447,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271911</v>
+        <v>127271875</v>
       </c>
       <c r="B61" t="n">
-        <v>92622</v>
+        <v>58033</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,21 +6458,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6473,10 +6482,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812117</v>
+        <v>812093</v>
       </c>
       <c r="R61" t="n">
-        <v>7389993</v>
+        <v>7389656</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6632,49 +6641,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271855</v>
+        <v>127271911</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811859</v>
+        <v>812117</v>
       </c>
       <c r="R63" t="n">
-        <v>7390026</v>
+        <v>7389993</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6707,11 +6712,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271876</v>
+        <v>127271842</v>
       </c>
       <c r="B66" t="n">
-        <v>80995</v>
+        <v>79638</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812128</v>
+        <v>812161</v>
       </c>
       <c r="R66" t="n">
-        <v>7390038</v>
+        <v>7389878</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7020,7 +7020,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7039,7 +7038,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271881</v>
+        <v>127271886</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -7074,10 +7073,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812133</v>
+        <v>811852</v>
       </c>
       <c r="R67" t="n">
-        <v>7389830</v>
+        <v>7390093</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7136,32 +7135,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271886</v>
+        <v>127271912</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7171,10 +7170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811852</v>
+        <v>811981</v>
       </c>
       <c r="R68" t="n">
-        <v>7390093</v>
+        <v>7389988</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7233,32 +7232,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271842</v>
+        <v>127271921</v>
       </c>
       <c r="B69" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7268,10 +7267,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812161</v>
+        <v>812092</v>
       </c>
       <c r="R69" t="n">
-        <v>7389878</v>
+        <v>7389721</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7330,32 +7329,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271841</v>
+        <v>127271909</v>
       </c>
       <c r="B70" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7365,10 +7364,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812139</v>
+        <v>812175</v>
       </c>
       <c r="R70" t="n">
-        <v>7389967</v>
+        <v>7389748</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7427,10 +7426,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271852</v>
+        <v>127271881</v>
       </c>
       <c r="B71" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7438,38 +7437,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812054</v>
+        <v>812133</v>
       </c>
       <c r="R71" t="n">
-        <v>7390009</v>
+        <v>7389830</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7502,11 +7497,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7533,32 +7523,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271912</v>
+        <v>127271876</v>
       </c>
       <c r="B72" t="n">
-        <v>92622</v>
+        <v>80995</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7568,10 +7558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811981</v>
+        <v>812128</v>
       </c>
       <c r="R72" t="n">
-        <v>7389988</v>
+        <v>7390038</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7612,6 +7602,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7630,45 +7621,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271921</v>
+        <v>127271852</v>
       </c>
       <c r="B73" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812092</v>
+        <v>812054</v>
       </c>
       <c r="R73" t="n">
-        <v>7389721</v>
+        <v>7390009</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7701,6 +7696,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7727,32 +7727,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271909</v>
+        <v>127271841</v>
       </c>
       <c r="B74" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812175</v>
+        <v>812139</v>
       </c>
       <c r="R74" t="n">
-        <v>7389748</v>
+        <v>7389967</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7824,32 +7824,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127271924</v>
+        <v>127271880</v>
       </c>
       <c r="B75" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>812019</v>
+        <v>812207</v>
       </c>
       <c r="R75" t="n">
-        <v>7389582</v>
+        <v>7389858</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7921,32 +7921,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127271880</v>
+        <v>127271924</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>812207</v>
+        <v>812019</v>
       </c>
       <c r="R76" t="n">
-        <v>7389858</v>
+        <v>7389582</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8018,32 +8018,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271877</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>91350</v>
+        <v>92622</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812195</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389776</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8115,7 +8115,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271917</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
         <v>92622</v>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812088</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389936</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8212,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271908</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92622</v>
+        <v>91350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812128</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389752</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271890</v>
+        <v>127271843</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812121</v>
+        <v>812074</v>
       </c>
       <c r="R84" t="n">
-        <v>7389928</v>
+        <v>7389829</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8812,7 +8812,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271882</v>
+        <v>127271890</v>
       </c>
       <c r="B85" t="n">
         <v>79020</v>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812120</v>
+        <v>812121</v>
       </c>
       <c r="R85" t="n">
-        <v>7389917</v>
+        <v>7389928</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271843</v>
+        <v>127271882</v>
       </c>
       <c r="B86" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8920,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812074</v>
+        <v>812120</v>
       </c>
       <c r="R86" t="n">
-        <v>7389829</v>
+        <v>7389917</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B87" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R87" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,6 +9077,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9103,10 +9108,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B88" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9114,21 +9119,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R88" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9174,11 +9179,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9510,10 +9510,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271894</v>
+        <v>127271836</v>
       </c>
       <c r="B92" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9521,21 +9521,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811982</v>
+        <v>811958</v>
       </c>
       <c r="R92" t="n">
-        <v>7389609</v>
+        <v>7389950</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9607,10 +9607,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271836</v>
+        <v>127271894</v>
       </c>
       <c r="B93" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9618,21 +9618,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811958</v>
+        <v>811982</v>
       </c>
       <c r="R93" t="n">
-        <v>7389950</v>
+        <v>7389609</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271857</v>
+        <v>127271868</v>
       </c>
       <c r="B94" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812050</v>
+        <v>812092</v>
       </c>
       <c r="R94" t="n">
-        <v>7389925</v>
+        <v>7389656</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271856</v>
+        <v>127271840</v>
       </c>
       <c r="B95" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,38 +9812,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811876</v>
+        <v>812127</v>
       </c>
       <c r="R95" t="n">
-        <v>7389968</v>
+        <v>7389936</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9876,11 +9872,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9907,10 +9898,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271840</v>
+        <v>127271856</v>
       </c>
       <c r="B96" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9918,34 +9909,38 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812127</v>
+        <v>811876</v>
       </c>
       <c r="R96" t="n">
-        <v>7389936</v>
+        <v>7389968</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9978,6 +9973,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271868</v>
+        <v>127271857</v>
       </c>
       <c r="B97" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812092</v>
+        <v>812050</v>
       </c>
       <c r="R97" t="n">
-        <v>7389656</v>
+        <v>7389925</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127271915</v>
+        <v>127271874</v>
       </c>
       <c r="B98" t="n">
-        <v>92622</v>
+        <v>57767</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10112,21 +10112,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811935</v>
+        <v>812168</v>
       </c>
       <c r="R98" t="n">
-        <v>7389943</v>
+        <v>7389829</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10198,10 +10198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127271874</v>
+        <v>127271915</v>
       </c>
       <c r="B99" t="n">
-        <v>57767</v>
+        <v>92622</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10209,21 +10209,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>812168</v>
+        <v>811935</v>
       </c>
       <c r="R99" t="n">
-        <v>7389829</v>
+        <v>7389943</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10295,49 +10295,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271864</v>
+        <v>127271907</v>
       </c>
       <c r="B100" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812087</v>
+        <v>812162</v>
       </c>
       <c r="R100" t="n">
-        <v>7389653</v>
+        <v>7389625</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10370,11 +10366,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10401,32 +10392,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271907</v>
+        <v>127271893</v>
       </c>
       <c r="B101" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10436,10 +10427,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>812162</v>
+        <v>812066</v>
       </c>
       <c r="R101" t="n">
-        <v>7389625</v>
+        <v>7389634</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10595,7 +10586,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271893</v>
+        <v>127271884</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10630,10 +10621,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>812066</v>
+        <v>811977</v>
       </c>
       <c r="R103" t="n">
-        <v>7389634</v>
+        <v>7389985</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10692,10 +10683,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271884</v>
+        <v>127271864</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10703,34 +10694,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811977</v>
+        <v>812087</v>
       </c>
       <c r="R104" t="n">
-        <v>7389985</v>
+        <v>7389653</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10763,6 +10758,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,49 +10789,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271853</v>
+        <v>127271913</v>
       </c>
       <c r="B105" t="n">
-        <v>57663</v>
+        <v>92622</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811970</v>
+        <v>811963</v>
       </c>
       <c r="R105" t="n">
-        <v>7390085</v>
+        <v>7390029</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10864,11 +10860,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10895,32 +10886,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271913</v>
+        <v>127271892</v>
       </c>
       <c r="B106" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10930,10 +10921,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811963</v>
+        <v>812106</v>
       </c>
       <c r="R106" t="n">
-        <v>7390029</v>
+        <v>7389684</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10992,32 +10983,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271906</v>
+        <v>127271879</v>
       </c>
       <c r="B107" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11027,10 +11018,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812166</v>
+        <v>812228</v>
       </c>
       <c r="R107" t="n">
-        <v>7389625</v>
+        <v>7389839</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11089,32 +11080,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271892</v>
+        <v>127271906</v>
       </c>
       <c r="B108" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11124,10 +11115,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812106</v>
+        <v>812166</v>
       </c>
       <c r="R108" t="n">
-        <v>7389684</v>
+        <v>7389625</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11186,10 +11177,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271879</v>
+        <v>127271853</v>
       </c>
       <c r="B109" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11197,34 +11188,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812228</v>
+        <v>811970</v>
       </c>
       <c r="R109" t="n">
-        <v>7389839</v>
+        <v>7390085</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11257,6 +11252,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12271,7 +12271,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271850</v>
+        <v>127271861</v>
       </c>
       <c r="B120" t="n">
         <v>57663</v>
@@ -12310,10 +12310,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812124</v>
+        <v>812106</v>
       </c>
       <c r="R120" t="n">
-        <v>7389758</v>
+        <v>7389819</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Mellersta området</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12377,7 +12377,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271861</v>
+        <v>127271850</v>
       </c>
       <c r="B121" t="n">
         <v>57663</v>
@@ -12416,10 +12416,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812106</v>
+        <v>812124</v>
       </c>
       <c r="R121" t="n">
-        <v>7389819</v>
+        <v>7389758</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049608</v>
+        <v>127049592</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>79638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812055</v>
+        <v>812072</v>
       </c>
       <c r="R3" t="n">
-        <v>7389491</v>
+        <v>7389539</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049592</v>
+        <v>127049608</v>
       </c>
       <c r="B4" t="n">
-        <v>79638</v>
+        <v>97339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812072</v>
+        <v>812055</v>
       </c>
       <c r="R4" t="n">
-        <v>7389539</v>
+        <v>7389491</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049611</v>
+        <v>127049638</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>92628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>812004</v>
+        <v>811921</v>
       </c>
       <c r="R6" t="n">
-        <v>7389528</v>
+        <v>7389590</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049638</v>
+        <v>127049639</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811921</v>
+        <v>811937</v>
       </c>
       <c r="R7" t="n">
-        <v>7389590</v>
+        <v>7389558</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049639</v>
+        <v>127049611</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>97339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811937</v>
+        <v>812004</v>
       </c>
       <c r="R8" t="n">
-        <v>7389558</v>
+        <v>7389528</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127049595</v>
+        <v>127049621</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811948</v>
+        <v>812153</v>
       </c>
       <c r="R9" t="n">
-        <v>7389545</v>
+        <v>7389594</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127049621</v>
+        <v>127049595</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>812153</v>
+        <v>811948</v>
       </c>
       <c r="R10" t="n">
-        <v>7389594</v>
+        <v>7389545</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049596</v>
+        <v>127049628</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811955</v>
+        <v>811980</v>
       </c>
       <c r="R13" t="n">
-        <v>7389537</v>
+        <v>7389540</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049628</v>
+        <v>127049596</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811980</v>
+        <v>811955</v>
       </c>
       <c r="R15" t="n">
-        <v>7389540</v>
+        <v>7389537</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,32 +2042,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127049645</v>
+        <v>127049623</v>
       </c>
       <c r="B16" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>812008</v>
+        <v>812077</v>
       </c>
       <c r="R16" t="n">
-        <v>7389456</v>
+        <v>7389513</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,32 +2139,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127049623</v>
+        <v>127049645</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>812077</v>
+        <v>812008</v>
       </c>
       <c r="R17" t="n">
-        <v>7389513</v>
+        <v>7389456</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049601</v>
+        <v>127049630</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,38 +2247,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811940</v>
+        <v>812021</v>
       </c>
       <c r="R18" t="n">
-        <v>7389556</v>
+        <v>7389474</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2311,11 +2307,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2342,7 +2333,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049630</v>
+        <v>127049631</v>
       </c>
       <c r="B19" t="n">
         <v>79020</v>
@@ -2377,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812021</v>
+        <v>812026</v>
       </c>
       <c r="R19" t="n">
-        <v>7389474</v>
+        <v>7389461</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2439,7 +2430,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127049631</v>
+        <v>127049622</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2474,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>812026</v>
+        <v>812088</v>
       </c>
       <c r="R20" t="n">
-        <v>7389461</v>
+        <v>7389588</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2536,10 +2527,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127049622</v>
+        <v>127049601</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2547,34 +2538,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>812088</v>
+        <v>811940</v>
       </c>
       <c r="R21" t="n">
-        <v>7389588</v>
+        <v>7389556</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2607,6 +2602,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,7 +2733,7 @@
         <v>127049637</v>
       </c>
       <c r="B23" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>127049640</v>
       </c>
       <c r="B24" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127049605</v>
       </c>
       <c r="B26" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049633</v>
+        <v>127049609</v>
       </c>
       <c r="B27" t="n">
-        <v>78687</v>
+        <v>97339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811950</v>
+        <v>811991</v>
       </c>
       <c r="R27" t="n">
-        <v>7389574</v>
+        <v>7389623</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049642</v>
+        <v>127049633</v>
       </c>
       <c r="B28" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811969</v>
+        <v>811950</v>
       </c>
       <c r="R28" t="n">
-        <v>7389545</v>
+        <v>7389574</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049643</v>
+        <v>127049642</v>
       </c>
       <c r="B29" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811987</v>
+        <v>811969</v>
       </c>
       <c r="R29" t="n">
-        <v>7389527</v>
+        <v>7389545</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049609</v>
+        <v>127049643</v>
       </c>
       <c r="B30" t="n">
-        <v>97333</v>
+        <v>92628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811991</v>
+        <v>811987</v>
       </c>
       <c r="R30" t="n">
-        <v>7389623</v>
+        <v>7389527</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3606,7 +3606,7 @@
         <v>127049610</v>
       </c>
       <c r="B32" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>127049607</v>
       </c>
       <c r="B33" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049625</v>
+        <v>127049635</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811987</v>
+        <v>812027</v>
       </c>
       <c r="R34" t="n">
-        <v>7389722</v>
+        <v>7389564</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127049619</v>
+        <v>127049625</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>812060</v>
+        <v>811987</v>
       </c>
       <c r="R35" t="n">
-        <v>7389489</v>
+        <v>7389722</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3991,32 +3991,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127049635</v>
+        <v>127049619</v>
       </c>
       <c r="B36" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>812027</v>
+        <v>812060</v>
       </c>
       <c r="R36" t="n">
-        <v>7389564</v>
+        <v>7389489</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127049616</v>
+        <v>127049624</v>
       </c>
       <c r="B37" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811934</v>
+        <v>812000</v>
       </c>
       <c r="R37" t="n">
-        <v>7389548</v>
+        <v>7389736</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127049624</v>
+        <v>127049616</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>812000</v>
+        <v>811934</v>
       </c>
       <c r="R38" t="n">
-        <v>7389736</v>
+        <v>7389548</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127049591</v>
+        <v>127049632</v>
       </c>
       <c r="B40" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4391,34 +4391,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>812066</v>
+        <v>812117</v>
       </c>
       <c r="R40" t="n">
-        <v>7389504</v>
+        <v>7389623</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4451,6 +4455,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4477,10 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127049647</v>
+        <v>127049591</v>
       </c>
       <c r="B41" t="n">
-        <v>77998</v>
+        <v>79638</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4488,21 +4497,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4512,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811948</v>
+        <v>812066</v>
       </c>
       <c r="R41" t="n">
-        <v>7389545</v>
+        <v>7389504</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4574,10 +4583,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127049632</v>
+        <v>127049647</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>77998</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4585,38 +4594,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>812117</v>
+        <v>811948</v>
       </c>
       <c r="R42" t="n">
-        <v>7389623</v>
+        <v>7389545</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4649,11 +4654,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4683,7 +4683,7 @@
         <v>127049634</v>
       </c>
       <c r="B43" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4874,10 +4874,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049626</v>
+        <v>127049614</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>80995</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811984</v>
+        <v>812078</v>
       </c>
       <c r="R45" t="n">
-        <v>7389705</v>
+        <v>7389625</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,10 +4971,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049641</v>
+        <v>127049606</v>
       </c>
       <c r="B46" t="n">
-        <v>92622</v>
+        <v>97339</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4982,21 +4982,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811963</v>
+        <v>812115</v>
       </c>
       <c r="R46" t="n">
-        <v>7389548</v>
+        <v>7389567</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049614</v>
+        <v>127049626</v>
       </c>
       <c r="B47" t="n">
-        <v>80995</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5079,21 +5079,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>812078</v>
+        <v>811984</v>
       </c>
       <c r="R47" t="n">
-        <v>7389625</v>
+        <v>7389705</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5165,10 +5165,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127049606</v>
+        <v>127049641</v>
       </c>
       <c r="B48" t="n">
-        <v>97333</v>
+        <v>92628</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5176,21 +5176,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>812115</v>
+        <v>811963</v>
       </c>
       <c r="R48" t="n">
-        <v>7389567</v>
+        <v>7389548</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R54" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B55" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R55" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271847</v>
+        <v>127271910</v>
       </c>
       <c r="B57" t="n">
-        <v>79638</v>
+        <v>92628</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812034</v>
+        <v>812192</v>
       </c>
       <c r="R57" t="n">
-        <v>7389561</v>
+        <v>7389757</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271910</v>
+        <v>127271923</v>
       </c>
       <c r="B58" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812192</v>
+        <v>811986</v>
       </c>
       <c r="R58" t="n">
-        <v>7389757</v>
+        <v>7389610</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B59" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R59" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,49 +6341,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271855</v>
+        <v>127271911</v>
       </c>
       <c r="B60" t="n">
-        <v>57663</v>
+        <v>92628</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811859</v>
+        <v>812117</v>
       </c>
       <c r="R60" t="n">
-        <v>7390026</v>
+        <v>7389993</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6416,11 +6412,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6447,32 +6438,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271875</v>
+        <v>127271883</v>
       </c>
       <c r="B61" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6482,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812093</v>
+        <v>812004</v>
       </c>
       <c r="R61" t="n">
-        <v>7389656</v>
+        <v>7389960</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6544,10 +6535,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271883</v>
+        <v>127271855</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6555,34 +6546,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812004</v>
+        <v>811859</v>
       </c>
       <c r="R62" t="n">
-        <v>7389960</v>
+        <v>7390026</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6615,6 +6610,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6641,10 +6641,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271911</v>
+        <v>127271875</v>
       </c>
       <c r="B63" t="n">
-        <v>92622</v>
+        <v>58033</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6652,21 +6652,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812117</v>
+        <v>812093</v>
       </c>
       <c r="R63" t="n">
-        <v>7389993</v>
+        <v>7389656</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271842</v>
+        <v>127271852</v>
       </c>
       <c r="B66" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,34 +6952,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812161</v>
+        <v>812054</v>
       </c>
       <c r="R66" t="n">
-        <v>7389878</v>
+        <v>7390009</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7012,6 +7016,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7038,32 +7047,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271886</v>
+        <v>127271921</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811852</v>
+        <v>812092</v>
       </c>
       <c r="R67" t="n">
-        <v>7390093</v>
+        <v>7389721</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7135,10 +7144,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271912</v>
+        <v>127271909</v>
       </c>
       <c r="B68" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7170,10 +7179,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811981</v>
+        <v>812175</v>
       </c>
       <c r="R68" t="n">
-        <v>7389988</v>
+        <v>7389748</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,10 +7241,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271921</v>
+        <v>127271912</v>
       </c>
       <c r="B69" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7267,10 +7276,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812092</v>
+        <v>811981</v>
       </c>
       <c r="R69" t="n">
-        <v>7389721</v>
+        <v>7389988</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,32 +7338,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271909</v>
+        <v>127271886</v>
       </c>
       <c r="B70" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7364,10 +7373,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812175</v>
+        <v>811852</v>
       </c>
       <c r="R70" t="n">
-        <v>7389748</v>
+        <v>7390093</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7621,10 +7630,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271852</v>
+        <v>127271841</v>
       </c>
       <c r="B73" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7632,38 +7641,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812054</v>
+        <v>812139</v>
       </c>
       <c r="R73" t="n">
-        <v>7390009</v>
+        <v>7389967</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7696,11 +7701,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7727,7 +7727,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271841</v>
+        <v>127271842</v>
       </c>
       <c r="B74" t="n">
         <v>79638</v>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812139</v>
+        <v>812161</v>
       </c>
       <c r="R74" t="n">
-        <v>7389967</v>
+        <v>7389878</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7824,32 +7824,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127271880</v>
+        <v>127271924</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>812207</v>
+        <v>812019</v>
       </c>
       <c r="R75" t="n">
-        <v>7389858</v>
+        <v>7389582</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7921,32 +7921,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127271924</v>
+        <v>127271880</v>
       </c>
       <c r="B76" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>812019</v>
+        <v>812207</v>
       </c>
       <c r="R76" t="n">
-        <v>7389582</v>
+        <v>7389858</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127271908</v>
       </c>
       <c r="B77" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>812128</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389752</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8115,10 +8115,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127271917</v>
       </c>
       <c r="B78" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8150,10 +8150,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>812088</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389936</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8215,7 +8215,7 @@
         <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271843</v>
+        <v>127271882</v>
       </c>
       <c r="B84" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812074</v>
+        <v>812120</v>
       </c>
       <c r="R84" t="n">
-        <v>7389829</v>
+        <v>7389917</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8920,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R86" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271872</v>
+        <v>127271838</v>
       </c>
       <c r="B87" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9017,21 +9017,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811880</v>
+        <v>811971</v>
       </c>
       <c r="R87" t="n">
-        <v>7390107</v>
+        <v>7389931</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9077,11 +9077,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9108,10 +9103,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271838</v>
+        <v>127271872</v>
       </c>
       <c r="B88" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9119,21 +9114,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811971</v>
+        <v>811880</v>
       </c>
       <c r="R88" t="n">
-        <v>7389931</v>
+        <v>7390107</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9179,6 +9174,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271849</v>
+        <v>127271891</v>
       </c>
       <c r="B89" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812114</v>
+        <v>812077</v>
       </c>
       <c r="R89" t="n">
-        <v>7389969</v>
+        <v>7389800</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9276,11 +9276,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9307,10 +9302,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271897</v>
+        <v>127271894</v>
       </c>
       <c r="B90" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9318,38 +9313,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>812122</v>
+        <v>811982</v>
       </c>
       <c r="R90" t="n">
-        <v>7389709</v>
+        <v>7389609</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9382,11 +9373,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9413,10 +9399,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271891</v>
+        <v>127271836</v>
       </c>
       <c r="B91" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9424,21 +9410,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9448,10 +9434,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>812077</v>
+        <v>811958</v>
       </c>
       <c r="R91" t="n">
-        <v>7389800</v>
+        <v>7389950</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9510,10 +9496,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271836</v>
+        <v>127271849</v>
       </c>
       <c r="B92" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9521,21 +9507,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9545,10 +9531,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811958</v>
+        <v>812114</v>
       </c>
       <c r="R92" t="n">
-        <v>7389950</v>
+        <v>7389969</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9581,6 +9567,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9607,10 +9598,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271894</v>
+        <v>127271897</v>
       </c>
       <c r="B93" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9618,34 +9609,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811982</v>
+        <v>812122</v>
       </c>
       <c r="R93" t="n">
-        <v>7389609</v>
+        <v>7389709</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9678,6 +9673,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271868</v>
+        <v>127271840</v>
       </c>
       <c r="B94" t="n">
-        <v>57823</v>
+        <v>79638</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812092</v>
+        <v>812127</v>
       </c>
       <c r="R94" t="n">
-        <v>7389656</v>
+        <v>7389936</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271840</v>
+        <v>127271856</v>
       </c>
       <c r="B95" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,34 +9812,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812127</v>
+        <v>811876</v>
       </c>
       <c r="R95" t="n">
-        <v>7389936</v>
+        <v>7389968</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9872,6 +9876,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9898,7 +9907,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271856</v>
+        <v>127271857</v>
       </c>
       <c r="B96" t="n">
         <v>57663</v>
@@ -9927,20 +9936,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811876</v>
+        <v>812050</v>
       </c>
       <c r="R96" t="n">
-        <v>7389968</v>
+        <v>7389925</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9973,11 +9978,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271857</v>
+        <v>127271868</v>
       </c>
       <c r="B97" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812050</v>
+        <v>812092</v>
       </c>
       <c r="R97" t="n">
-        <v>7389925</v>
+        <v>7389656</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10101,10 +10101,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127271874</v>
+        <v>127271915</v>
       </c>
       <c r="B98" t="n">
-        <v>57767</v>
+        <v>92628</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10112,21 +10112,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>812168</v>
+        <v>811935</v>
       </c>
       <c r="R98" t="n">
-        <v>7389829</v>
+        <v>7389943</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10198,10 +10198,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127271915</v>
+        <v>127271874</v>
       </c>
       <c r="B99" t="n">
-        <v>92622</v>
+        <v>57767</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10209,21 +10209,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811935</v>
+        <v>812168</v>
       </c>
       <c r="R99" t="n">
-        <v>7389943</v>
+        <v>7389829</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10295,32 +10295,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271907</v>
+        <v>127271893</v>
       </c>
       <c r="B100" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812162</v>
+        <v>812066</v>
       </c>
       <c r="R100" t="n">
-        <v>7389625</v>
+        <v>7389634</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271893</v>
+        <v>127271864</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10403,34 +10403,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>812066</v>
+        <v>812087</v>
       </c>
       <c r="R101" t="n">
-        <v>7389634</v>
+        <v>7389653</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10463,6 +10467,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10492,7 +10501,7 @@
         <v>127271916</v>
       </c>
       <c r="B102" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10586,32 +10595,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271884</v>
+        <v>127271907</v>
       </c>
       <c r="B103" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10621,10 +10630,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811977</v>
+        <v>812162</v>
       </c>
       <c r="R103" t="n">
-        <v>7389985</v>
+        <v>7389625</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10683,10 +10692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271864</v>
+        <v>127271884</v>
       </c>
       <c r="B104" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10694,38 +10703,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>812087</v>
+        <v>811977</v>
       </c>
       <c r="R104" t="n">
-        <v>7389653</v>
+        <v>7389985</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10758,11 +10763,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,32 +10789,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271913</v>
+        <v>127271892</v>
       </c>
       <c r="B105" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811963</v>
+        <v>812106</v>
       </c>
       <c r="R105" t="n">
-        <v>7390029</v>
+        <v>7389684</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10886,7 +10886,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271892</v>
+        <v>127271879</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -10921,10 +10921,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812106</v>
+        <v>812228</v>
       </c>
       <c r="R106" t="n">
-        <v>7389684</v>
+        <v>7389839</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10983,10 +10983,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271879</v>
+        <v>127271853</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10994,34 +10994,38 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812228</v>
+        <v>811970</v>
       </c>
       <c r="R107" t="n">
-        <v>7389839</v>
+        <v>7390085</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11054,6 +11058,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11080,10 +11089,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271906</v>
+        <v>127271913</v>
       </c>
       <c r="B108" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11115,10 +11124,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812166</v>
+        <v>811963</v>
       </c>
       <c r="R108" t="n">
-        <v>7389625</v>
+        <v>7390029</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11177,49 +11186,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271853</v>
+        <v>127271906</v>
       </c>
       <c r="B109" t="n">
-        <v>57663</v>
+        <v>92628</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811970</v>
+        <v>812166</v>
       </c>
       <c r="R109" t="n">
-        <v>7390085</v>
+        <v>7389625</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11252,11 +11257,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11383,7 +11383,7 @@
         <v>127271922</v>
       </c>
       <c r="B111" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271919</v>
+        <v>127271914</v>
       </c>
       <c r="B114" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>812158</v>
+        <v>811875</v>
       </c>
       <c r="R114" t="n">
-        <v>7389883</v>
+        <v>7389980</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271914</v>
+        <v>127271919</v>
       </c>
       <c r="B115" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811875</v>
+        <v>812158</v>
       </c>
       <c r="R115" t="n">
-        <v>7389980</v>
+        <v>7389883</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12177,7 +12177,7 @@
         <v>127271918</v>
       </c>
       <c r="B119" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>127388830</v>
       </c>
       <c r="B122" t="n">
-        <v>91493</v>
+        <v>91499</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -5265,7 +5265,7 @@
         <v>127049600</v>
       </c>
       <c r="B49" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>127049598</v>
       </c>
       <c r="B50" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>127049599</v>
       </c>
       <c r="B51" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B52" t="n">
-        <v>79638</v>
+        <v>57666</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,34 +5567,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R52" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5627,6 +5631,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5653,10 +5662,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B53" t="n">
-        <v>57663</v>
+        <v>79641</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5664,38 +5673,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R53" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5728,11 +5733,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B54" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R54" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R55" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B56" t="n">
-        <v>78426</v>
+        <v>92631</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R56" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,10 +6050,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271910</v>
+        <v>127271923</v>
       </c>
       <c r="B57" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812192</v>
+        <v>811986</v>
       </c>
       <c r="R57" t="n">
-        <v>7389757</v>
+        <v>7389610</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271923</v>
+        <v>127271925</v>
       </c>
       <c r="B58" t="n">
-        <v>92628</v>
+        <v>78429</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811986</v>
+        <v>812066</v>
       </c>
       <c r="R58" t="n">
-        <v>7389610</v>
+        <v>7389760</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6247,7 +6247,7 @@
         <v>127271847</v>
       </c>
       <c r="B59" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>127271911</v>
       </c>
       <c r="B60" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271883</v>
+        <v>127271855</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6449,34 +6449,38 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812004</v>
+        <v>811859</v>
       </c>
       <c r="R61" t="n">
-        <v>7389960</v>
+        <v>7390026</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6509,6 +6513,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6535,10 +6544,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271855</v>
+        <v>127271883</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6546,38 +6555,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811859</v>
+        <v>812004</v>
       </c>
       <c r="R62" t="n">
-        <v>7390026</v>
+        <v>7389960</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6610,11 +6615,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6644,7 +6644,7 @@
         <v>127271875</v>
       </c>
       <c r="B63" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271888</v>
+        <v>127271858</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,34 +6749,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811957</v>
+        <v>812068</v>
       </c>
       <c r="R64" t="n">
-        <v>7389943</v>
+        <v>7389929</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6809,6 +6813,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6835,10 +6844,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271858</v>
+        <v>127271888</v>
       </c>
       <c r="B65" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6846,38 +6855,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>812068</v>
+        <v>811957</v>
       </c>
       <c r="R65" t="n">
-        <v>7389929</v>
+        <v>7389943</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6910,11 +6915,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6944,7 +6944,7 @@
         <v>127271852</v>
       </c>
       <c r="B66" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7047,32 +7047,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271921</v>
+        <v>127271876</v>
       </c>
       <c r="B67" t="n">
-        <v>92628</v>
+        <v>80998</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7082,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812092</v>
+        <v>812128</v>
       </c>
       <c r="R67" t="n">
-        <v>7389721</v>
+        <v>7390038</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7126,6 +7126,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7144,10 +7145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271909</v>
+        <v>127271912</v>
       </c>
       <c r="B68" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7179,10 +7180,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812175</v>
+        <v>811981</v>
       </c>
       <c r="R68" t="n">
-        <v>7389748</v>
+        <v>7389988</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7241,10 +7242,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271912</v>
+        <v>127271921</v>
       </c>
       <c r="B69" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7276,10 +7277,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811981</v>
+        <v>812092</v>
       </c>
       <c r="R69" t="n">
-        <v>7389988</v>
+        <v>7389721</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7338,32 +7339,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271886</v>
+        <v>127271909</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7373,10 +7374,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811852</v>
+        <v>812175</v>
       </c>
       <c r="R70" t="n">
-        <v>7390093</v>
+        <v>7389748</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7435,10 +7436,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271881</v>
+        <v>127271841</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7446,21 +7447,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7470,10 +7471,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812133</v>
+        <v>812139</v>
       </c>
       <c r="R71" t="n">
-        <v>7389830</v>
+        <v>7389967</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7532,10 +7533,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271876</v>
+        <v>127271842</v>
       </c>
       <c r="B72" t="n">
-        <v>80995</v>
+        <v>79641</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7543,21 +7544,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7567,10 +7568,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812128</v>
+        <v>812161</v>
       </c>
       <c r="R72" t="n">
-        <v>7390038</v>
+        <v>7389878</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7611,7 +7612,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7630,10 +7630,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271841</v>
+        <v>127271886</v>
       </c>
       <c r="B73" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7641,21 +7641,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7665,10 +7665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812139</v>
+        <v>811852</v>
       </c>
       <c r="R73" t="n">
-        <v>7389967</v>
+        <v>7390093</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7727,10 +7727,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271842</v>
+        <v>127271881</v>
       </c>
       <c r="B74" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7738,21 +7738,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812161</v>
+        <v>812133</v>
       </c>
       <c r="R74" t="n">
-        <v>7389878</v>
+        <v>7389830</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7824,32 +7824,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127271924</v>
+        <v>127271880</v>
       </c>
       <c r="B75" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>812019</v>
+        <v>812207</v>
       </c>
       <c r="R75" t="n">
-        <v>7389582</v>
+        <v>7389858</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7921,32 +7921,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127271880</v>
+        <v>127271924</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>812207</v>
+        <v>812019</v>
       </c>
       <c r="R76" t="n">
-        <v>7389858</v>
+        <v>7389582</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8018,45 +8018,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271908</v>
+        <v>127271851</v>
       </c>
       <c r="B77" t="n">
-        <v>92628</v>
+        <v>57666</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812128</v>
+        <v>812117</v>
       </c>
       <c r="R77" t="n">
-        <v>7389752</v>
+        <v>7389911</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8089,6 +8093,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8115,45 +8124,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271917</v>
+        <v>127271865</v>
       </c>
       <c r="B78" t="n">
-        <v>92628</v>
+        <v>57666</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812088</v>
+        <v>812024</v>
       </c>
       <c r="R78" t="n">
-        <v>7389936</v>
+        <v>7389558</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8186,6 +8199,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8212,32 +8230,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271917</v>
       </c>
       <c r="B79" t="n">
-        <v>91356</v>
+        <v>92631</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8265,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>812088</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389936</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8309,49 +8327,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271851</v>
+        <v>127271908</v>
       </c>
       <c r="B80" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812117</v>
+        <v>812128</v>
       </c>
       <c r="R80" t="n">
-        <v>7389911</v>
+        <v>7389752</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8384,11 +8398,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8415,10 +8424,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271865</v>
+        <v>127271877</v>
       </c>
       <c r="B81" t="n">
-        <v>57663</v>
+        <v>91359</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8426,38 +8435,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812024</v>
+        <v>812195</v>
       </c>
       <c r="R81" t="n">
-        <v>7389558</v>
+        <v>7389776</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8490,11 +8495,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8524,7 +8524,7 @@
         <v>127271895</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>127271878</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>127271882</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271890</v>
+        <v>127271843</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812121</v>
+        <v>812074</v>
       </c>
       <c r="R85" t="n">
-        <v>7389928</v>
+        <v>7389829</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271843</v>
+        <v>127271890</v>
       </c>
       <c r="B86" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8920,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812074</v>
+        <v>812121</v>
       </c>
       <c r="R86" t="n">
-        <v>7389829</v>
+        <v>7389928</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9009,7 +9009,7 @@
         <v>127271838</v>
       </c>
       <c r="B87" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>127271872</v>
       </c>
       <c r="B88" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271891</v>
+        <v>127271849</v>
       </c>
       <c r="B89" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812077</v>
+        <v>812114</v>
       </c>
       <c r="R89" t="n">
-        <v>7389800</v>
+        <v>7389969</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9276,6 +9276,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9302,10 +9307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271894</v>
+        <v>127271897</v>
       </c>
       <c r="B90" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,34 +9318,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811982</v>
+        <v>812122</v>
       </c>
       <c r="R90" t="n">
-        <v>7389609</v>
+        <v>7389709</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9373,6 +9382,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9399,10 +9413,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271836</v>
+        <v>127271891</v>
       </c>
       <c r="B91" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9410,21 +9424,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9434,10 +9448,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811958</v>
+        <v>812077</v>
       </c>
       <c r="R91" t="n">
-        <v>7389950</v>
+        <v>7389800</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9496,10 +9510,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271849</v>
+        <v>127271836</v>
       </c>
       <c r="B92" t="n">
-        <v>57663</v>
+        <v>79641</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9507,21 +9521,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9531,10 +9545,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>812114</v>
+        <v>811958</v>
       </c>
       <c r="R92" t="n">
-        <v>7389969</v>
+        <v>7389950</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9567,11 +9581,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9598,10 +9607,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271897</v>
+        <v>127271894</v>
       </c>
       <c r="B93" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9609,38 +9618,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>812122</v>
+        <v>811982</v>
       </c>
       <c r="R93" t="n">
-        <v>7389709</v>
+        <v>7389609</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9673,11 +9678,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271840</v>
+        <v>127271868</v>
       </c>
       <c r="B94" t="n">
-        <v>79638</v>
+        <v>57826</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812127</v>
+        <v>812092</v>
       </c>
       <c r="R94" t="n">
-        <v>7389936</v>
+        <v>7389656</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9804,7 +9804,7 @@
         <v>127271856</v>
       </c>
       <c r="B95" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>127271857</v>
       </c>
       <c r="B96" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271868</v>
+        <v>127271840</v>
       </c>
       <c r="B97" t="n">
-        <v>57823</v>
+        <v>79641</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812092</v>
+        <v>812127</v>
       </c>
       <c r="R97" t="n">
-        <v>7389656</v>
+        <v>7389936</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10104,7 +10104,7 @@
         <v>127271915</v>
       </c>
       <c r="B98" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>127271874</v>
       </c>
       <c r="B99" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10295,32 +10295,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271893</v>
+        <v>127271907</v>
       </c>
       <c r="B100" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812066</v>
+        <v>812162</v>
       </c>
       <c r="R100" t="n">
-        <v>7389634</v>
+        <v>7389625</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10392,49 +10392,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271864</v>
+        <v>127271916</v>
       </c>
       <c r="B101" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>812087</v>
+        <v>811958</v>
       </c>
       <c r="R101" t="n">
-        <v>7389653</v>
+        <v>7389946</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10467,11 +10463,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10498,45 +10489,49 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271916</v>
+        <v>127271864</v>
       </c>
       <c r="B102" t="n">
-        <v>92628</v>
+        <v>57666</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811958</v>
+        <v>812087</v>
       </c>
       <c r="R102" t="n">
-        <v>7389946</v>
+        <v>7389653</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10569,6 +10564,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10595,32 +10595,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271907</v>
+        <v>127271893</v>
       </c>
       <c r="B103" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>812162</v>
+        <v>812066</v>
       </c>
       <c r="R103" t="n">
-        <v>7389625</v>
+        <v>7389634</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10695,7 +10695,7 @@
         <v>127271884</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10789,32 +10789,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271892</v>
+        <v>127271913</v>
       </c>
       <c r="B105" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>812106</v>
+        <v>811963</v>
       </c>
       <c r="R105" t="n">
-        <v>7389684</v>
+        <v>7390029</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10886,32 +10886,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271879</v>
+        <v>127271906</v>
       </c>
       <c r="B106" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10921,10 +10921,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812228</v>
+        <v>812166</v>
       </c>
       <c r="R106" t="n">
-        <v>7389839</v>
+        <v>7389625</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10983,10 +10983,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271853</v>
+        <v>127271892</v>
       </c>
       <c r="B107" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10994,38 +10994,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811970</v>
+        <v>812106</v>
       </c>
       <c r="R107" t="n">
-        <v>7390085</v>
+        <v>7389684</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11058,11 +11054,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11089,32 +11080,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271913</v>
+        <v>127271879</v>
       </c>
       <c r="B108" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11124,10 +11115,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811963</v>
+        <v>812228</v>
       </c>
       <c r="R108" t="n">
-        <v>7390029</v>
+        <v>7389839</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11186,32 +11177,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271906</v>
+        <v>127271844</v>
       </c>
       <c r="B109" t="n">
-        <v>92628</v>
+        <v>79641</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11221,10 +11212,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812166</v>
+        <v>812114</v>
       </c>
       <c r="R109" t="n">
-        <v>7389625</v>
+        <v>7389680</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11283,10 +11274,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271844</v>
+        <v>127271853</v>
       </c>
       <c r="B110" t="n">
-        <v>79638</v>
+        <v>57666</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11294,34 +11285,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>812114</v>
+        <v>811970</v>
       </c>
       <c r="R110" t="n">
-        <v>7389680</v>
+        <v>7390085</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11354,6 +11349,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11383,7 +11383,7 @@
         <v>127271922</v>
       </c>
       <c r="B111" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>127271885</v>
       </c>
       <c r="B112" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>127271860</v>
       </c>
       <c r="B113" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271914</v>
+        <v>127271919</v>
       </c>
       <c r="B114" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811875</v>
+        <v>812158</v>
       </c>
       <c r="R114" t="n">
-        <v>7389980</v>
+        <v>7389883</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,10 +11777,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271919</v>
+        <v>127271914</v>
       </c>
       <c r="B115" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>812158</v>
+        <v>811875</v>
       </c>
       <c r="R115" t="n">
-        <v>7389883</v>
+        <v>7389980</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11877,7 +11877,7 @@
         <v>127271887</v>
       </c>
       <c r="B116" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>127271862</v>
       </c>
       <c r="B117" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>127271866</v>
       </c>
       <c r="B118" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12174,45 +12174,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271918</v>
+        <v>127271850</v>
       </c>
       <c r="B119" t="n">
-        <v>92628</v>
+        <v>57666</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812162</v>
+        <v>812124</v>
       </c>
       <c r="R119" t="n">
-        <v>7389925</v>
+        <v>7389758</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12245,6 +12249,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12271,49 +12280,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271861</v>
+        <v>127271918</v>
       </c>
       <c r="B120" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812106</v>
+        <v>812162</v>
       </c>
       <c r="R120" t="n">
-        <v>7389819</v>
+        <v>7389925</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12346,11 +12351,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12377,10 +12377,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271850</v>
+        <v>127271861</v>
       </c>
       <c r="B121" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12416,10 +12416,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812124</v>
+        <v>812106</v>
       </c>
       <c r="R121" t="n">
-        <v>7389758</v>
+        <v>7389819</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Mellersta området</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12486,7 +12486,7 @@
         <v>127388830</v>
       </c>
       <c r="B122" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -5265,7 +5265,7 @@
         <v>127049600</v>
       </c>
       <c r="B49" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>127049598</v>
       </c>
       <c r="B50" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>127049599</v>
       </c>
       <c r="B51" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>127271854</v>
       </c>
       <c r="B52" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>127271845</v>
       </c>
       <c r="B53" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B54" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R54" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B55" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R55" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B56" t="n">
-        <v>92631</v>
+        <v>78435</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R56" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B57" t="n">
-        <v>92631</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R57" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B58" t="n">
-        <v>78429</v>
+        <v>92639</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R58" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B59" t="n">
-        <v>79641</v>
+        <v>92639</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R59" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6344,7 +6344,7 @@
         <v>127271911</v>
       </c>
       <c r="B60" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>127271855</v>
       </c>
       <c r="B61" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6544,32 +6544,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271883</v>
+        <v>127271875</v>
       </c>
       <c r="B62" t="n">
-        <v>79023</v>
+        <v>58042</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812004</v>
+        <v>812093</v>
       </c>
       <c r="R62" t="n">
-        <v>7389960</v>
+        <v>7389656</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6641,32 +6641,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271875</v>
+        <v>127271883</v>
       </c>
       <c r="B63" t="n">
-        <v>58036</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812093</v>
+        <v>812004</v>
       </c>
       <c r="R63" t="n">
-        <v>7389656</v>
+        <v>7389960</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6741,7 +6741,7 @@
         <v>127271858</v>
       </c>
       <c r="B64" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>127271888</v>
       </c>
       <c r="B65" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>127271852</v>
       </c>
       <c r="B66" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>127271876</v>
       </c>
       <c r="B67" t="n">
-        <v>80998</v>
+        <v>81004</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>127271912</v>
       </c>
       <c r="B68" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>127271921</v>
       </c>
       <c r="B69" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>127271909</v>
       </c>
       <c r="B70" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7436,10 +7436,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271841</v>
+        <v>127271881</v>
       </c>
       <c r="B71" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7447,21 +7447,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812139</v>
+        <v>812133</v>
       </c>
       <c r="R71" t="n">
-        <v>7389967</v>
+        <v>7389830</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7536,7 +7536,7 @@
         <v>127271842</v>
       </c>
       <c r="B72" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7630,10 +7630,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271886</v>
+        <v>127271841</v>
       </c>
       <c r="B73" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7641,21 +7641,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7665,10 +7665,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811852</v>
+        <v>812139</v>
       </c>
       <c r="R73" t="n">
-        <v>7390093</v>
+        <v>7389967</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7727,10 +7727,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271881</v>
+        <v>127271886</v>
       </c>
       <c r="B74" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812133</v>
+        <v>811852</v>
       </c>
       <c r="R74" t="n">
-        <v>7389830</v>
+        <v>7390093</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7827,7 +7827,7 @@
         <v>127271880</v>
       </c>
       <c r="B75" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>127271924</v>
       </c>
       <c r="B76" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,49 +8018,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271851</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812117</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389911</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8093,11 +8089,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8124,49 +8115,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271865</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812024</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389558</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8199,11 +8186,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8230,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271917</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92631</v>
+        <v>91367</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8265,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812088</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389936</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8327,45 +8309,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271908</v>
+        <v>127271865</v>
       </c>
       <c r="B80" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812128</v>
+        <v>812024</v>
       </c>
       <c r="R80" t="n">
-        <v>7389752</v>
+        <v>7389558</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8398,6 +8384,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8424,10 +8415,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271877</v>
+        <v>127271851</v>
       </c>
       <c r="B81" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8435,34 +8426,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812195</v>
+        <v>812117</v>
       </c>
       <c r="R81" t="n">
-        <v>7389776</v>
+        <v>7389911</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8495,6 +8490,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8524,7 +8524,7 @@
         <v>127271895</v>
       </c>
       <c r="B82" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>127271878</v>
       </c>
       <c r="B83" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B84" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R84" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271843</v>
+        <v>127271890</v>
       </c>
       <c r="B85" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812074</v>
+        <v>812121</v>
       </c>
       <c r="R85" t="n">
-        <v>7389829</v>
+        <v>7389928</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271890</v>
+        <v>127271882</v>
       </c>
       <c r="B86" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812121</v>
+        <v>812120</v>
       </c>
       <c r="R86" t="n">
-        <v>7389928</v>
+        <v>7389917</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9009,7 +9009,7 @@
         <v>127271838</v>
       </c>
       <c r="B87" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>127271872</v>
       </c>
       <c r="B88" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>127271849</v>
       </c>
       <c r="B89" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>127271897</v>
       </c>
       <c r="B90" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271891</v>
+        <v>127271836</v>
       </c>
       <c r="B91" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9424,21 +9424,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>812077</v>
+        <v>811958</v>
       </c>
       <c r="R91" t="n">
-        <v>7389800</v>
+        <v>7389950</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9510,10 +9510,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271836</v>
+        <v>127271891</v>
       </c>
       <c r="B92" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9521,21 +9521,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811958</v>
+        <v>812077</v>
       </c>
       <c r="R92" t="n">
-        <v>7389950</v>
+        <v>7389800</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9610,7 +9610,7 @@
         <v>127271894</v>
       </c>
       <c r="B93" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271868</v>
+        <v>127271857</v>
       </c>
       <c r="B94" t="n">
-        <v>57826</v>
+        <v>57672</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812092</v>
+        <v>812050</v>
       </c>
       <c r="R94" t="n">
-        <v>7389656</v>
+        <v>7389925</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9804,7 +9804,7 @@
         <v>127271856</v>
       </c>
       <c r="B95" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9907,10 +9907,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271857</v>
+        <v>127271840</v>
       </c>
       <c r="B96" t="n">
-        <v>57666</v>
+        <v>79647</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9918,21 +9918,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812050</v>
+        <v>812127</v>
       </c>
       <c r="R96" t="n">
-        <v>7389925</v>
+        <v>7389936</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271840</v>
+        <v>127271868</v>
       </c>
       <c r="B97" t="n">
-        <v>79641</v>
+        <v>57832</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812127</v>
+        <v>812092</v>
       </c>
       <c r="R97" t="n">
-        <v>7389936</v>
+        <v>7389656</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10104,7 +10104,7 @@
         <v>127271915</v>
       </c>
       <c r="B98" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>127271874</v>
       </c>
       <c r="B99" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>127271907</v>
       </c>
       <c r="B100" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>127271916</v>
       </c>
       <c r="B101" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>127271864</v>
       </c>
       <c r="B102" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>127271893</v>
       </c>
       <c r="B103" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>127271884</v>
       </c>
       <c r="B104" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10789,45 +10789,49 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271913</v>
+        <v>127271853</v>
       </c>
       <c r="B105" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811963</v>
+        <v>811970</v>
       </c>
       <c r="R105" t="n">
-        <v>7390029</v>
+        <v>7390085</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10860,6 +10864,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10886,32 +10895,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271906</v>
+        <v>127271844</v>
       </c>
       <c r="B106" t="n">
-        <v>92631</v>
+        <v>79647</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10921,10 +10930,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812166</v>
+        <v>812114</v>
       </c>
       <c r="R106" t="n">
-        <v>7389625</v>
+        <v>7389680</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10986,7 +10995,7 @@
         <v>127271892</v>
       </c>
       <c r="B107" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11083,7 +11092,7 @@
         <v>127271879</v>
       </c>
       <c r="B108" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11177,32 +11186,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271844</v>
+        <v>127271913</v>
       </c>
       <c r="B109" t="n">
-        <v>79641</v>
+        <v>92639</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11212,10 +11221,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812114</v>
+        <v>811963</v>
       </c>
       <c r="R109" t="n">
-        <v>7389680</v>
+        <v>7390029</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11274,49 +11283,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271853</v>
+        <v>127271906</v>
       </c>
       <c r="B110" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811970</v>
+        <v>812166</v>
       </c>
       <c r="R110" t="n">
-        <v>7390085</v>
+        <v>7389625</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11349,11 +11354,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11380,32 +11380,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271922</v>
+        <v>127271885</v>
       </c>
       <c r="B111" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>812120</v>
+        <v>811960</v>
       </c>
       <c r="R111" t="n">
-        <v>7389691</v>
+        <v>7390029</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11477,32 +11477,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271885</v>
+        <v>127271922</v>
       </c>
       <c r="B112" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811960</v>
+        <v>812120</v>
       </c>
       <c r="R112" t="n">
-        <v>7390029</v>
+        <v>7389691</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11577,7 +11577,7 @@
         <v>127271860</v>
       </c>
       <c r="B113" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>127271919</v>
       </c>
       <c r="B114" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>127271914</v>
       </c>
       <c r="B115" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271887</v>
+        <v>127271862</v>
       </c>
       <c r="B116" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11885,34 +11885,38 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811866</v>
+        <v>812079</v>
       </c>
       <c r="R116" t="n">
-        <v>7390052</v>
+        <v>7389800</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11945,6 +11949,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11971,10 +11980,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271862</v>
+        <v>127271887</v>
       </c>
       <c r="B117" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11982,38 +11991,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>812079</v>
+        <v>811866</v>
       </c>
       <c r="R117" t="n">
-        <v>7389800</v>
+        <v>7390052</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12046,11 +12051,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12080,7 +12080,7 @@
         <v>127271866</v>
       </c>
       <c r="B118" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12174,49 +12174,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271850</v>
+        <v>127271918</v>
       </c>
       <c r="B119" t="n">
-        <v>57666</v>
+        <v>92639</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812124</v>
+        <v>812162</v>
       </c>
       <c r="R119" t="n">
-        <v>7389758</v>
+        <v>7389925</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12249,11 +12245,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12280,45 +12271,49 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271918</v>
+        <v>127271850</v>
       </c>
       <c r="B120" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812162</v>
+        <v>812124</v>
       </c>
       <c r="R120" t="n">
-        <v>7389925</v>
+        <v>7389758</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12351,6 +12346,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12380,7 +12380,7 @@
         <v>127271861</v>
       </c>
       <c r="B121" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>127388830</v>
       </c>
       <c r="B122" t="n">
-        <v>91502</v>
+        <v>91510</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B54" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R54" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R55" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6150,7 +6150,7 @@
         <v>127271910</v>
       </c>
       <c r="B58" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>127271923</v>
       </c>
       <c r="B59" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271911</v>
+        <v>127271875</v>
       </c>
       <c r="B60" t="n">
-        <v>92639</v>
+        <v>58042</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6352,21 +6352,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812117</v>
+        <v>812093</v>
       </c>
       <c r="R60" t="n">
-        <v>7389993</v>
+        <v>7389656</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6544,32 +6544,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271875</v>
+        <v>127271883</v>
       </c>
       <c r="B62" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812093</v>
+        <v>812004</v>
       </c>
       <c r="R62" t="n">
-        <v>7389656</v>
+        <v>7389960</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6641,32 +6641,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271883</v>
+        <v>127271911</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812004</v>
+        <v>812117</v>
       </c>
       <c r="R63" t="n">
-        <v>7389960</v>
+        <v>7389993</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271852</v>
+        <v>127271876</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>81004</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,38 +6952,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812054</v>
+        <v>812128</v>
       </c>
       <c r="R66" t="n">
-        <v>7390009</v>
+        <v>7390038</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7018,17 +7014,13 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7047,10 +7039,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271876</v>
+        <v>127271841</v>
       </c>
       <c r="B67" t="n">
-        <v>81004</v>
+        <v>79647</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7058,21 +7050,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7082,10 +7074,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812128</v>
+        <v>812139</v>
       </c>
       <c r="R67" t="n">
-        <v>7390038</v>
+        <v>7389967</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7126,7 +7118,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7145,32 +7136,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271912</v>
+        <v>127271842</v>
       </c>
       <c r="B68" t="n">
-        <v>92639</v>
+        <v>79647</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7180,10 +7171,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811981</v>
+        <v>812161</v>
       </c>
       <c r="R68" t="n">
-        <v>7389988</v>
+        <v>7389878</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7242,32 +7233,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271921</v>
+        <v>127271886</v>
       </c>
       <c r="B69" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7277,10 +7268,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812092</v>
+        <v>811852</v>
       </c>
       <c r="R69" t="n">
-        <v>7389721</v>
+        <v>7390093</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7339,10 +7330,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271909</v>
+        <v>127271912</v>
       </c>
       <c r="B70" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7374,10 +7365,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812175</v>
+        <v>811981</v>
       </c>
       <c r="R70" t="n">
-        <v>7389748</v>
+        <v>7389988</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7436,32 +7427,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271881</v>
+        <v>127271921</v>
       </c>
       <c r="B71" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7471,10 +7462,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812133</v>
+        <v>812092</v>
       </c>
       <c r="R71" t="n">
-        <v>7389830</v>
+        <v>7389721</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7533,32 +7524,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271842</v>
+        <v>127271909</v>
       </c>
       <c r="B72" t="n">
-        <v>79647</v>
+        <v>92640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7568,10 +7559,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812161</v>
+        <v>812175</v>
       </c>
       <c r="R72" t="n">
-        <v>7389878</v>
+        <v>7389748</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7630,10 +7621,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271841</v>
+        <v>127271881</v>
       </c>
       <c r="B73" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7641,21 +7632,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7665,10 +7656,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812139</v>
+        <v>812133</v>
       </c>
       <c r="R73" t="n">
-        <v>7389967</v>
+        <v>7389830</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7727,10 +7718,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271886</v>
+        <v>127271852</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7738,34 +7729,38 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811852</v>
+        <v>812054</v>
       </c>
       <c r="R74" t="n">
-        <v>7390093</v>
+        <v>7390009</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7798,6 +7793,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7924,7 +7924,7 @@
         <v>127271924</v>
       </c>
       <c r="B76" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8018,45 +8018,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127271851</v>
       </c>
       <c r="B77" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>812117</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389911</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8089,6 +8093,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8115,45 +8124,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127271865</v>
       </c>
       <c r="B78" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>812024</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389558</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8186,6 +8199,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8212,32 +8230,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271917</v>
       </c>
       <c r="B79" t="n">
-        <v>91367</v>
+        <v>92640</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8265,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>812088</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389936</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8309,49 +8327,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271865</v>
+        <v>127271908</v>
       </c>
       <c r="B80" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812024</v>
+        <v>812128</v>
       </c>
       <c r="R80" t="n">
-        <v>7389558</v>
+        <v>7389752</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8384,11 +8398,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8415,10 +8424,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271851</v>
+        <v>127271877</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8426,38 +8435,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812117</v>
+        <v>812195</v>
       </c>
       <c r="R81" t="n">
-        <v>7389911</v>
+        <v>7389776</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8490,11 +8495,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8812,7 +8812,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271890</v>
+        <v>127271882</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812121</v>
+        <v>812120</v>
       </c>
       <c r="R85" t="n">
-        <v>7389928</v>
+        <v>7389917</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,7 +8909,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271882</v>
+        <v>127271890</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -8944,10 +8944,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812120</v>
+        <v>812121</v>
       </c>
       <c r="R86" t="n">
-        <v>7389917</v>
+        <v>7389928</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271849</v>
+        <v>127271836</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812114</v>
+        <v>811958</v>
       </c>
       <c r="R89" t="n">
-        <v>7389969</v>
+        <v>7389950</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9276,11 +9276,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9307,7 +9302,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271897</v>
+        <v>127271849</v>
       </c>
       <c r="B90" t="n">
         <v>57672</v>
@@ -9335,21 +9330,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>812122</v>
+        <v>812114</v>
       </c>
       <c r="R90" t="n">
-        <v>7389709</v>
+        <v>7389969</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9386,7 +9377,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Observerad och filmad under födosök.</t>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9413,10 +9404,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271836</v>
+        <v>127271897</v>
       </c>
       <c r="B91" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9424,34 +9415,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811958</v>
+        <v>812122</v>
       </c>
       <c r="R91" t="n">
-        <v>7389950</v>
+        <v>7389709</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9484,6 +9479,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9704,10 +9704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271857</v>
+        <v>127271840</v>
       </c>
       <c r="B94" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9715,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812050</v>
+        <v>812127</v>
       </c>
       <c r="R94" t="n">
-        <v>7389925</v>
+        <v>7389936</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9907,10 +9907,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271840</v>
+        <v>127271857</v>
       </c>
       <c r="B96" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9918,21 +9918,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812127</v>
+        <v>812050</v>
       </c>
       <c r="R96" t="n">
-        <v>7389936</v>
+        <v>7389925</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10104,7 +10104,7 @@
         <v>127271915</v>
       </c>
       <c r="B98" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10295,45 +10295,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271907</v>
+        <v>127271864</v>
       </c>
       <c r="B100" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812162</v>
+        <v>812087</v>
       </c>
       <c r="R100" t="n">
-        <v>7389625</v>
+        <v>7389653</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10366,6 +10370,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10392,10 +10401,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271916</v>
+        <v>127271907</v>
       </c>
       <c r="B101" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10427,10 +10436,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811958</v>
+        <v>812162</v>
       </c>
       <c r="R101" t="n">
-        <v>7389946</v>
+        <v>7389625</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10489,10 +10498,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271864</v>
+        <v>127271893</v>
       </c>
       <c r="B102" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10500,38 +10509,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>812087</v>
+        <v>812066</v>
       </c>
       <c r="R102" t="n">
-        <v>7389653</v>
+        <v>7389634</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10564,11 +10569,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10595,32 +10595,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271893</v>
+        <v>127271916</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>812066</v>
+        <v>811958</v>
       </c>
       <c r="R103" t="n">
-        <v>7389634</v>
+        <v>7389946</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10789,10 +10789,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271853</v>
+        <v>127271844</v>
       </c>
       <c r="B105" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10800,38 +10800,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811970</v>
+        <v>812114</v>
       </c>
       <c r="R105" t="n">
-        <v>7390085</v>
+        <v>7389680</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10864,11 +10860,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10895,10 +10886,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271844</v>
+        <v>127271853</v>
       </c>
       <c r="B106" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10906,34 +10897,38 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812114</v>
+        <v>811970</v>
       </c>
       <c r="R106" t="n">
-        <v>7389680</v>
+        <v>7390085</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10966,6 +10961,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10992,32 +10992,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271892</v>
+        <v>127271913</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812106</v>
+        <v>811963</v>
       </c>
       <c r="R107" t="n">
-        <v>7389684</v>
+        <v>7390029</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11089,7 +11089,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271879</v>
+        <v>127271892</v>
       </c>
       <c r="B108" t="n">
         <v>79029</v>
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812228</v>
+        <v>812106</v>
       </c>
       <c r="R108" t="n">
-        <v>7389839</v>
+        <v>7389684</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11186,32 +11186,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271913</v>
+        <v>127271879</v>
       </c>
       <c r="B109" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811963</v>
+        <v>812228</v>
       </c>
       <c r="R109" t="n">
-        <v>7390029</v>
+        <v>7389839</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11286,7 +11286,7 @@
         <v>127271906</v>
       </c>
       <c r="B110" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11380,10 +11380,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271885</v>
+        <v>127271860</v>
       </c>
       <c r="B111" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11391,34 +11391,38 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811960</v>
+        <v>812080</v>
       </c>
       <c r="R111" t="n">
-        <v>7390029</v>
+        <v>7389823</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11451,6 +11455,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11480,7 +11489,7 @@
         <v>127271922</v>
       </c>
       <c r="B112" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11574,10 +11583,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127271860</v>
+        <v>127271885</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11585,38 +11594,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>812080</v>
+        <v>811960</v>
       </c>
       <c r="R113" t="n">
-        <v>7389823</v>
+        <v>7390029</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11649,11 +11654,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11680,45 +11680,49 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271919</v>
+        <v>127271862</v>
       </c>
       <c r="B114" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>812158</v>
+        <v>812079</v>
       </c>
       <c r="R114" t="n">
-        <v>7389883</v>
+        <v>7389800</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11751,6 +11755,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11777,10 +11786,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271914</v>
+        <v>127271919</v>
       </c>
       <c r="B115" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11812,10 +11821,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811875</v>
+        <v>812158</v>
       </c>
       <c r="R115" t="n">
-        <v>7389980</v>
+        <v>7389883</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,49 +11883,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271862</v>
+        <v>127271914</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>812079</v>
+        <v>811875</v>
       </c>
       <c r="R116" t="n">
-        <v>7389800</v>
+        <v>7389980</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11949,11 +11954,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12174,45 +12174,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271918</v>
+        <v>127271861</v>
       </c>
       <c r="B119" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812162</v>
+        <v>812106</v>
       </c>
       <c r="R119" t="n">
-        <v>7389925</v>
+        <v>7389819</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12245,6 +12249,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12377,49 +12386,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271861</v>
+        <v>127271918</v>
       </c>
       <c r="B121" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812106</v>
+        <v>812162</v>
       </c>
       <c r="R121" t="n">
-        <v>7389819</v>
+        <v>7389925</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12452,11 +12457,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12486,7 +12486,7 @@
         <v>127388830</v>
       </c>
       <c r="B122" t="n">
-        <v>91510</v>
+        <v>91511</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,38 +5567,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R52" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5631,11 +5627,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5662,10 +5653,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B53" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5673,34 +5664,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R53" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5733,6 +5728,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R54" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B55" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R55" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B56" t="n">
-        <v>78435</v>
+        <v>92640</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R56" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>92640</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R57" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B58" t="n">
-        <v>92640</v>
+        <v>78435</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R58" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B59" t="n">
-        <v>92640</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R59" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,27 +6341,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271875</v>
+        <v>127271855</v>
       </c>
       <c r="B60" t="n">
-        <v>58042</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6370,16 +6370,20 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>812093</v>
+        <v>811859</v>
       </c>
       <c r="R60" t="n">
-        <v>7389656</v>
+        <v>7390026</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6412,6 +6416,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6438,27 +6447,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271855</v>
+        <v>127271875</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>58042</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6467,20 +6476,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811859</v>
+        <v>812093</v>
       </c>
       <c r="R61" t="n">
-        <v>7390026</v>
+        <v>7389656</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6513,11 +6518,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6544,32 +6544,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271883</v>
+        <v>127271911</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812004</v>
+        <v>812117</v>
       </c>
       <c r="R62" t="n">
-        <v>7389960</v>
+        <v>7389993</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6641,32 +6641,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271911</v>
+        <v>127271883</v>
       </c>
       <c r="B63" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812117</v>
+        <v>812004</v>
       </c>
       <c r="R63" t="n">
-        <v>7389993</v>
+        <v>7389960</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271858</v>
+        <v>127271888</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,38 +6749,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>812068</v>
+        <v>811957</v>
       </c>
       <c r="R64" t="n">
-        <v>7389929</v>
+        <v>7389943</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6813,11 +6809,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6844,10 +6835,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271888</v>
+        <v>127271858</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6855,34 +6846,38 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811957</v>
+        <v>812068</v>
       </c>
       <c r="R65" t="n">
-        <v>7389943</v>
+        <v>7389929</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6915,6 +6910,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271876</v>
+        <v>127271841</v>
       </c>
       <c r="B66" t="n">
-        <v>81004</v>
+        <v>79647</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812128</v>
+        <v>812139</v>
       </c>
       <c r="R66" t="n">
-        <v>7390038</v>
+        <v>7389967</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7020,7 +7020,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7039,7 +7038,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271841</v>
+        <v>127271842</v>
       </c>
       <c r="B67" t="n">
         <v>79647</v>
@@ -7074,10 +7073,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812139</v>
+        <v>812161</v>
       </c>
       <c r="R67" t="n">
-        <v>7389967</v>
+        <v>7389878</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7136,10 +7135,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271842</v>
+        <v>127271886</v>
       </c>
       <c r="B68" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7147,21 +7146,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7171,10 +7170,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>812161</v>
+        <v>811852</v>
       </c>
       <c r="R68" t="n">
-        <v>7389878</v>
+        <v>7390093</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7233,7 +7232,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271886</v>
+        <v>127271881</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7268,10 +7267,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811852</v>
+        <v>812133</v>
       </c>
       <c r="R69" t="n">
-        <v>7390093</v>
+        <v>7389830</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7330,32 +7329,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271912</v>
+        <v>127271876</v>
       </c>
       <c r="B70" t="n">
-        <v>92640</v>
+        <v>81004</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7365,10 +7364,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811981</v>
+        <v>812128</v>
       </c>
       <c r="R70" t="n">
-        <v>7389988</v>
+        <v>7390038</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7409,6 +7408,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7427,7 +7427,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271921</v>
+        <v>127271912</v>
       </c>
       <c r="B71" t="n">
         <v>92640</v>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>812092</v>
+        <v>811981</v>
       </c>
       <c r="R71" t="n">
-        <v>7389721</v>
+        <v>7389988</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271909</v>
+        <v>127271921</v>
       </c>
       <c r="B72" t="n">
         <v>92640</v>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812175</v>
+        <v>812092</v>
       </c>
       <c r="R72" t="n">
-        <v>7389748</v>
+        <v>7389721</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7621,32 +7621,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271881</v>
+        <v>127271909</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812133</v>
+        <v>812175</v>
       </c>
       <c r="R73" t="n">
-        <v>7389830</v>
+        <v>7389748</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7824,32 +7824,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127271880</v>
+        <v>127271924</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>812207</v>
+        <v>812019</v>
       </c>
       <c r="R75" t="n">
-        <v>7389858</v>
+        <v>7389582</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7921,32 +7921,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127271924</v>
+        <v>127271880</v>
       </c>
       <c r="B76" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>812019</v>
+        <v>812207</v>
       </c>
       <c r="R76" t="n">
-        <v>7389582</v>
+        <v>7389858</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8018,49 +8018,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271851</v>
+        <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812117</v>
+        <v>812088</v>
       </c>
       <c r="R77" t="n">
-        <v>7389911</v>
+        <v>7389936</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8093,11 +8089,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8124,49 +8115,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271865</v>
+        <v>127271908</v>
       </c>
       <c r="B78" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812024</v>
+        <v>812128</v>
       </c>
       <c r="R78" t="n">
-        <v>7389558</v>
+        <v>7389752</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8199,11 +8186,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8230,32 +8212,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271917</v>
+        <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>92640</v>
+        <v>91368</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8265,10 +8247,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812088</v>
+        <v>812195</v>
       </c>
       <c r="R79" t="n">
-        <v>7389936</v>
+        <v>7389776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8327,45 +8309,49 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271908</v>
+        <v>127271851</v>
       </c>
       <c r="B80" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812128</v>
+        <v>812117</v>
       </c>
       <c r="R80" t="n">
-        <v>7389752</v>
+        <v>7389911</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8398,6 +8384,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8424,10 +8415,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271877</v>
+        <v>127271865</v>
       </c>
       <c r="B81" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8435,34 +8426,38 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812195</v>
+        <v>812024</v>
       </c>
       <c r="R81" t="n">
-        <v>7389776</v>
+        <v>7389558</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8495,6 +8490,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8715,10 +8715,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271843</v>
+        <v>127271882</v>
       </c>
       <c r="B84" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812074</v>
+        <v>812120</v>
       </c>
       <c r="R84" t="n">
-        <v>7389829</v>
+        <v>7389917</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B85" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R85" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271836</v>
+        <v>127271891</v>
       </c>
       <c r="B89" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811958</v>
+        <v>812077</v>
       </c>
       <c r="R89" t="n">
-        <v>7389950</v>
+        <v>7389800</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271849</v>
+        <v>127271836</v>
       </c>
       <c r="B90" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,21 +9313,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9337,10 +9337,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>812114</v>
+        <v>811958</v>
       </c>
       <c r="R90" t="n">
-        <v>7389969</v>
+        <v>7389950</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9373,11 +9373,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9404,10 +9399,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271897</v>
+        <v>127271894</v>
       </c>
       <c r="B91" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9415,38 +9410,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>812122</v>
+        <v>811982</v>
       </c>
       <c r="R91" t="n">
-        <v>7389709</v>
+        <v>7389609</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9479,11 +9470,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9510,10 +9496,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271891</v>
+        <v>127271849</v>
       </c>
       <c r="B92" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9521,21 +9507,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9545,10 +9531,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>812077</v>
+        <v>812114</v>
       </c>
       <c r="R92" t="n">
-        <v>7389800</v>
+        <v>7389969</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9581,6 +9567,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9607,10 +9598,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271894</v>
+        <v>127271897</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9618,34 +9609,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811982</v>
+        <v>812122</v>
       </c>
       <c r="R93" t="n">
-        <v>7389609</v>
+        <v>7389709</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9678,6 +9673,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271856</v>
+        <v>127271868</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,38 +9812,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811876</v>
+        <v>812092</v>
       </c>
       <c r="R95" t="n">
-        <v>7389968</v>
+        <v>7389656</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9876,11 +9872,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9907,7 +9898,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271857</v>
+        <v>127271856</v>
       </c>
       <c r="B96" t="n">
         <v>57672</v>
@@ -9936,16 +9927,20 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>812050</v>
+        <v>811876</v>
       </c>
       <c r="R96" t="n">
-        <v>7389925</v>
+        <v>7389968</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9978,6 +9973,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271868</v>
+        <v>127271857</v>
       </c>
       <c r="B97" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812092</v>
+        <v>812050</v>
       </c>
       <c r="R97" t="n">
-        <v>7389656</v>
+        <v>7389925</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10295,49 +10295,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271864</v>
+        <v>127271907</v>
       </c>
       <c r="B100" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812087</v>
+        <v>812162</v>
       </c>
       <c r="R100" t="n">
-        <v>7389653</v>
+        <v>7389625</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10370,11 +10366,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10401,7 +10392,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271907</v>
+        <v>127271916</v>
       </c>
       <c r="B101" t="n">
         <v>92640</v>
@@ -10436,10 +10427,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>812162</v>
+        <v>811958</v>
       </c>
       <c r="R101" t="n">
-        <v>7389625</v>
+        <v>7389946</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10595,32 +10586,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271916</v>
+        <v>127271884</v>
       </c>
       <c r="B103" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10630,10 +10621,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811958</v>
+        <v>811977</v>
       </c>
       <c r="R103" t="n">
-        <v>7389946</v>
+        <v>7389985</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10692,10 +10683,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271884</v>
+        <v>127271864</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10703,34 +10694,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811977</v>
+        <v>812087</v>
       </c>
       <c r="R104" t="n">
-        <v>7389985</v>
+        <v>7389653</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10763,6 +10758,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,32 +10789,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271844</v>
+        <v>127271913</v>
       </c>
       <c r="B105" t="n">
-        <v>79647</v>
+        <v>92640</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10824,10 +10824,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>812114</v>
+        <v>811963</v>
       </c>
       <c r="R105" t="n">
-        <v>7389680</v>
+        <v>7390029</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10886,49 +10886,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271853</v>
+        <v>127271906</v>
       </c>
       <c r="B106" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811970</v>
+        <v>812166</v>
       </c>
       <c r="R106" t="n">
-        <v>7390085</v>
+        <v>7389625</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10961,11 +10957,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10992,32 +10983,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271913</v>
+        <v>127271892</v>
       </c>
       <c r="B107" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11027,10 +11018,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811963</v>
+        <v>812106</v>
       </c>
       <c r="R107" t="n">
-        <v>7390029</v>
+        <v>7389684</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11089,7 +11080,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271892</v>
+        <v>127271879</v>
       </c>
       <c r="B108" t="n">
         <v>79029</v>
@@ -11124,10 +11115,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812106</v>
+        <v>812228</v>
       </c>
       <c r="R108" t="n">
-        <v>7389684</v>
+        <v>7389839</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11186,10 +11177,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271879</v>
+        <v>127271844</v>
       </c>
       <c r="B109" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11197,21 +11188,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11221,10 +11212,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812228</v>
+        <v>812114</v>
       </c>
       <c r="R109" t="n">
-        <v>7389839</v>
+        <v>7389680</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11283,45 +11274,49 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271906</v>
+        <v>127271853</v>
       </c>
       <c r="B110" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>812166</v>
+        <v>811970</v>
       </c>
       <c r="R110" t="n">
-        <v>7389625</v>
+        <v>7390085</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11354,6 +11349,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11380,49 +11380,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271860</v>
+        <v>127271922</v>
       </c>
       <c r="B111" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>812080</v>
+        <v>812120</v>
       </c>
       <c r="R111" t="n">
-        <v>7389823</v>
+        <v>7389691</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11455,11 +11451,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11486,32 +11477,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271922</v>
+        <v>127271885</v>
       </c>
       <c r="B112" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11521,10 +11512,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>812120</v>
+        <v>811960</v>
       </c>
       <c r="R112" t="n">
-        <v>7389691</v>
+        <v>7390029</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11583,10 +11574,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127271885</v>
+        <v>127271860</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11594,34 +11585,38 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811960</v>
+        <v>812080</v>
       </c>
       <c r="R113" t="n">
-        <v>7390029</v>
+        <v>7389823</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11654,6 +11649,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11680,10 +11680,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271862</v>
+        <v>127271887</v>
       </c>
       <c r="B114" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11691,38 +11691,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>812079</v>
+        <v>811866</v>
       </c>
       <c r="R114" t="n">
-        <v>7389800</v>
+        <v>7390052</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11755,11 +11751,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11786,10 +11777,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271919</v>
+        <v>127271866</v>
       </c>
       <c r="B115" t="n">
-        <v>92640</v>
+        <v>56864</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11797,21 +11788,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11821,10 +11812,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>812158</v>
+        <v>811935</v>
       </c>
       <c r="R115" t="n">
-        <v>7389883</v>
+        <v>7389957</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11883,7 +11874,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271914</v>
+        <v>127271919</v>
       </c>
       <c r="B116" t="n">
         <v>92640</v>
@@ -11918,10 +11909,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811875</v>
+        <v>812158</v>
       </c>
       <c r="R116" t="n">
-        <v>7389980</v>
+        <v>7389883</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11980,32 +11971,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271887</v>
+        <v>127271914</v>
       </c>
       <c r="B117" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12015,10 +12006,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811866</v>
+        <v>811875</v>
       </c>
       <c r="R117" t="n">
-        <v>7390052</v>
+        <v>7389980</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12077,45 +12068,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271866</v>
+        <v>127271862</v>
       </c>
       <c r="B118" t="n">
-        <v>56864</v>
+        <v>57672</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811935</v>
+        <v>812079</v>
       </c>
       <c r="R118" t="n">
-        <v>7389957</v>
+        <v>7389800</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12148,6 +12143,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12174,49 +12174,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271861</v>
+        <v>127271918</v>
       </c>
       <c r="B119" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812106</v>
+        <v>812162</v>
       </c>
       <c r="R119" t="n">
-        <v>7389819</v>
+        <v>7389925</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12249,11 +12245,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12280,7 +12271,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271850</v>
+        <v>127271861</v>
       </c>
       <c r="B120" t="n">
         <v>57672</v>
@@ -12319,10 +12310,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812124</v>
+        <v>812106</v>
       </c>
       <c r="R120" t="n">
-        <v>7389758</v>
+        <v>7389819</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12359,7 +12350,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Mellersta området</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12386,45 +12377,49 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271918</v>
+        <v>127271850</v>
       </c>
       <c r="B121" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812162</v>
+        <v>812124</v>
       </c>
       <c r="R121" t="n">
-        <v>7389925</v>
+        <v>7389758</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12457,6 +12452,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -12486,7 +12486,7 @@
         <v>127388830</v>
       </c>
       <c r="B122" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -12486,7 +12486,7 @@
         <v>127388830</v>
       </c>
       <c r="B122" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127049629</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049592</v>
+        <v>127049602</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812072</v>
+        <v>812043</v>
       </c>
       <c r="R3" t="n">
-        <v>7389539</v>
+        <v>7389685</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -843,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +881,7 @@
         <v>127049608</v>
       </c>
       <c r="B4" t="n">
-        <v>97339</v>
+        <v>97320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049602</v>
+        <v>127049592</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,38 +986,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812043</v>
+        <v>812072</v>
       </c>
       <c r="R5" t="n">
-        <v>7389685</v>
+        <v>7389539</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1041,11 +1046,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049638</v>
+        <v>127049611</v>
       </c>
       <c r="B6" t="n">
-        <v>92628</v>
+        <v>97320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811921</v>
+        <v>812004</v>
       </c>
       <c r="R6" t="n">
-        <v>7389590</v>
+        <v>7389528</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1169,10 +1169,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049639</v>
+        <v>127049638</v>
       </c>
       <c r="B7" t="n">
-        <v>92628</v>
+        <v>92609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811937</v>
+        <v>811921</v>
       </c>
       <c r="R7" t="n">
-        <v>7389558</v>
+        <v>7389590</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049611</v>
+        <v>127049639</v>
       </c>
       <c r="B8" t="n">
-        <v>97339</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>812004</v>
+        <v>811937</v>
       </c>
       <c r="R8" t="n">
-        <v>7389528</v>
+        <v>7389558</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127049621</v>
+        <v>127049595</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>812153</v>
+        <v>811948</v>
       </c>
       <c r="R9" t="n">
-        <v>7389594</v>
+        <v>7389545</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127049595</v>
+        <v>127049621</v>
       </c>
       <c r="B10" t="n">
-        <v>79638</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811948</v>
+        <v>812153</v>
       </c>
       <c r="R10" t="n">
-        <v>7389545</v>
+        <v>7389594</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1560,7 +1560,7 @@
         <v>127049612</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>127049620</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>127049628</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049618</v>
+        <v>127049596</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>812047</v>
+        <v>811955</v>
       </c>
       <c r="R14" t="n">
-        <v>7389473</v>
+        <v>7389537</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049596</v>
+        <v>127049618</v>
       </c>
       <c r="B15" t="n">
-        <v>79638</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811955</v>
+        <v>812047</v>
       </c>
       <c r="R15" t="n">
-        <v>7389537</v>
+        <v>7389473</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2045,7 +2045,7 @@
         <v>127049623</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>127049645</v>
       </c>
       <c r="B17" t="n">
-        <v>92628</v>
+        <v>92609</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049630</v>
+        <v>127049631</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>812021</v>
+        <v>812026</v>
       </c>
       <c r="R18" t="n">
-        <v>7389474</v>
+        <v>7389461</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049631</v>
+        <v>127049630</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812026</v>
+        <v>812021</v>
       </c>
       <c r="R19" t="n">
-        <v>7389461</v>
+        <v>7389474</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2433,7 +2433,7 @@
         <v>127049622</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>127049601</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049593</v>
+        <v>127049637</v>
       </c>
       <c r="B22" t="n">
-        <v>79638</v>
+        <v>92609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811934</v>
+        <v>811936</v>
       </c>
       <c r="R22" t="n">
-        <v>7389548</v>
+        <v>7389571</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049637</v>
+        <v>127049640</v>
       </c>
       <c r="B23" t="n">
-        <v>92628</v>
+        <v>92609</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>811936</v>
       </c>
       <c r="R23" t="n">
-        <v>7389571</v>
+        <v>7389556</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2827,32 +2827,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127049640</v>
+        <v>127049593</v>
       </c>
       <c r="B24" t="n">
-        <v>92628</v>
+        <v>79629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811936</v>
+        <v>811934</v>
       </c>
       <c r="R24" t="n">
-        <v>7389556</v>
+        <v>7389548</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2927,7 +2927,7 @@
         <v>127049613</v>
       </c>
       <c r="B25" t="n">
-        <v>80995</v>
+        <v>80986</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>127049605</v>
       </c>
       <c r="B26" t="n">
-        <v>92656</v>
+        <v>92637</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049609</v>
+        <v>127049633</v>
       </c>
       <c r="B27" t="n">
-        <v>97339</v>
+        <v>78678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811991</v>
+        <v>811950</v>
       </c>
       <c r="R27" t="n">
-        <v>7389623</v>
+        <v>7389574</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049633</v>
+        <v>127049642</v>
       </c>
       <c r="B28" t="n">
-        <v>78687</v>
+        <v>92609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811950</v>
+        <v>811969</v>
       </c>
       <c r="R28" t="n">
-        <v>7389574</v>
+        <v>7389545</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049642</v>
+        <v>127049643</v>
       </c>
       <c r="B29" t="n">
-        <v>92628</v>
+        <v>92609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811969</v>
+        <v>811987</v>
       </c>
       <c r="R29" t="n">
-        <v>7389545</v>
+        <v>7389527</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049643</v>
+        <v>127049609</v>
       </c>
       <c r="B30" t="n">
-        <v>92628</v>
+        <v>97320</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3420,21 +3420,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811987</v>
+        <v>811991</v>
       </c>
       <c r="R30" t="n">
-        <v>7389527</v>
+        <v>7389623</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3506,32 +3506,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049594</v>
+        <v>127049610</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>97320</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811945</v>
+        <v>811967</v>
       </c>
       <c r="R31" t="n">
-        <v>7389563</v>
+        <v>7389626</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3603,32 +3603,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049610</v>
+        <v>127049594</v>
       </c>
       <c r="B32" t="n">
-        <v>97339</v>
+        <v>79629</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811967</v>
+        <v>811945</v>
       </c>
       <c r="R32" t="n">
-        <v>7389626</v>
+        <v>7389563</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3700,32 +3700,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127049607</v>
+        <v>127049619</v>
       </c>
       <c r="B33" t="n">
-        <v>97339</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>812105</v>
+        <v>812060</v>
       </c>
       <c r="R33" t="n">
-        <v>7389559</v>
+        <v>7389489</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049635</v>
+        <v>127049625</v>
       </c>
       <c r="B34" t="n">
-        <v>92628</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>812027</v>
+        <v>811987</v>
       </c>
       <c r="R34" t="n">
-        <v>7389564</v>
+        <v>7389722</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3894,32 +3894,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127049625</v>
+        <v>127049635</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>92609</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811987</v>
+        <v>812027</v>
       </c>
       <c r="R35" t="n">
-        <v>7389722</v>
+        <v>7389564</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3991,32 +3991,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127049619</v>
+        <v>127049607</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>97320</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>812060</v>
+        <v>812105</v>
       </c>
       <c r="R36" t="n">
-        <v>7389489</v>
+        <v>7389559</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4091,7 +4091,7 @@
         <v>127049624</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>127049616</v>
       </c>
       <c r="B38" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>127049648</v>
       </c>
       <c r="B39" t="n">
-        <v>78426</v>
+        <v>78417</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127049632</v>
+        <v>127049591</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>79629</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4391,38 +4391,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>812117</v>
+        <v>812066</v>
       </c>
       <c r="R40" t="n">
-        <v>7389623</v>
+        <v>7389504</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4455,11 +4451,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4486,10 +4477,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127049591</v>
+        <v>127049647</v>
       </c>
       <c r="B41" t="n">
-        <v>79638</v>
+        <v>77989</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4497,21 +4488,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4521,10 +4512,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>812066</v>
+        <v>811948</v>
       </c>
       <c r="R41" t="n">
-        <v>7389504</v>
+        <v>7389545</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4583,10 +4574,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127049647</v>
+        <v>127049632</v>
       </c>
       <c r="B42" t="n">
-        <v>77998</v>
+        <v>57657</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4594,34 +4585,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811948</v>
+        <v>812117</v>
       </c>
       <c r="R42" t="n">
-        <v>7389545</v>
+        <v>7389623</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4654,6 +4649,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4683,7 +4683,7 @@
         <v>127049634</v>
       </c>
       <c r="B43" t="n">
-        <v>92628</v>
+        <v>92609</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>127049615</v>
       </c>
       <c r="B44" t="n">
-        <v>80995</v>
+        <v>80986</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4874,10 +4874,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049614</v>
+        <v>127049626</v>
       </c>
       <c r="B45" t="n">
-        <v>80995</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>812078</v>
+        <v>811984</v>
       </c>
       <c r="R45" t="n">
-        <v>7389625</v>
+        <v>7389705</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,10 +4971,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049606</v>
+        <v>127049641</v>
       </c>
       <c r="B46" t="n">
-        <v>97339</v>
+        <v>92609</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4982,21 +4982,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>812115</v>
+        <v>811963</v>
       </c>
       <c r="R46" t="n">
-        <v>7389567</v>
+        <v>7389548</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049626</v>
+        <v>127049614</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>80986</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5079,21 +5079,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811984</v>
+        <v>812078</v>
       </c>
       <c r="R47" t="n">
-        <v>7389705</v>
+        <v>7389625</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5165,10 +5165,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127049641</v>
+        <v>127049606</v>
       </c>
       <c r="B48" t="n">
-        <v>92628</v>
+        <v>97320</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5176,21 +5176,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811963</v>
+        <v>812115</v>
       </c>
       <c r="R48" t="n">
-        <v>7389548</v>
+        <v>7389567</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5265,7 +5265,7 @@
         <v>127049600</v>
       </c>
       <c r="B49" t="n">
-        <v>79618</v>
+        <v>79600</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>127049598</v>
       </c>
       <c r="B50" t="n">
-        <v>79618</v>
+        <v>79600</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>127049599</v>
       </c>
       <c r="B51" t="n">
-        <v>79618</v>
+        <v>79600</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271845</v>
+        <v>127271854</v>
       </c>
       <c r="B52" t="n">
-        <v>79647</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,34 +5567,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811999</v>
+        <v>811858</v>
       </c>
       <c r="R52" t="n">
-        <v>7389631</v>
+        <v>7390099</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5627,6 +5631,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5653,10 +5662,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271854</v>
+        <v>127271845</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>79629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5664,38 +5673,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811858</v>
+        <v>811999</v>
       </c>
       <c r="R53" t="n">
-        <v>7390099</v>
+        <v>7389631</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5728,11 +5733,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5759,32 +5759,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271920</v>
+        <v>127271889</v>
       </c>
       <c r="B54" t="n">
-        <v>92640</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>812127</v>
+        <v>811973</v>
       </c>
       <c r="R54" t="n">
-        <v>7389853</v>
+        <v>7389939</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,32 +5856,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271889</v>
+        <v>127271920</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>92609</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5891,10 +5891,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811973</v>
+        <v>812127</v>
       </c>
       <c r="R55" t="n">
-        <v>7389939</v>
+        <v>7389853</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5953,32 +5953,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271910</v>
+        <v>127271925</v>
       </c>
       <c r="B56" t="n">
-        <v>92640</v>
+        <v>78417</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812192</v>
+        <v>812066</v>
       </c>
       <c r="R56" t="n">
-        <v>7389757</v>
+        <v>7389760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6050,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271923</v>
+        <v>127271847</v>
       </c>
       <c r="B57" t="n">
-        <v>92640</v>
+        <v>79629</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811986</v>
+        <v>812034</v>
       </c>
       <c r="R57" t="n">
-        <v>7389610</v>
+        <v>7389561</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6147,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271925</v>
+        <v>127271910</v>
       </c>
       <c r="B58" t="n">
-        <v>78435</v>
+        <v>92609</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812066</v>
+        <v>812192</v>
       </c>
       <c r="R58" t="n">
-        <v>7389760</v>
+        <v>7389757</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6244,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271847</v>
+        <v>127271923</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>92609</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>812034</v>
+        <v>811986</v>
       </c>
       <c r="R59" t="n">
-        <v>7389561</v>
+        <v>7389610</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271855</v>
+        <v>127271883</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6352,38 +6352,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811859</v>
+        <v>812004</v>
       </c>
       <c r="R60" t="n">
-        <v>7390026</v>
+        <v>7389960</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6416,11 +6412,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6447,10 +6438,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271875</v>
+        <v>127271911</v>
       </c>
       <c r="B61" t="n">
-        <v>58042</v>
+        <v>92609</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6458,21 +6449,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6482,10 +6473,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812093</v>
+        <v>812117</v>
       </c>
       <c r="R61" t="n">
-        <v>7389656</v>
+        <v>7389993</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6544,45 +6535,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271911</v>
+        <v>127271855</v>
       </c>
       <c r="B62" t="n">
-        <v>92640</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812117</v>
+        <v>811859</v>
       </c>
       <c r="R62" t="n">
-        <v>7389993</v>
+        <v>7390026</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6615,6 +6610,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6641,32 +6641,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271883</v>
+        <v>127271875</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>58027</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812004</v>
+        <v>812093</v>
       </c>
       <c r="R63" t="n">
-        <v>7389960</v>
+        <v>7389656</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271888</v>
+        <v>127271858</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6749,34 +6749,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811957</v>
+        <v>812068</v>
       </c>
       <c r="R64" t="n">
-        <v>7389943</v>
+        <v>7389929</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6809,6 +6813,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6835,10 +6844,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271858</v>
+        <v>127271888</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6846,38 +6855,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>812068</v>
+        <v>811957</v>
       </c>
       <c r="R65" t="n">
-        <v>7389929</v>
+        <v>7389943</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6910,11 +6915,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6941,10 +6941,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271841</v>
+        <v>127271876</v>
       </c>
       <c r="B66" t="n">
-        <v>79647</v>
+        <v>80986</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812139</v>
+        <v>812128</v>
       </c>
       <c r="R66" t="n">
-        <v>7389967</v>
+        <v>7390038</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7020,6 +7020,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7038,10 +7039,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271842</v>
+        <v>127271852</v>
       </c>
       <c r="B67" t="n">
-        <v>79647</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7049,34 +7050,38 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812161</v>
+        <v>812054</v>
       </c>
       <c r="R67" t="n">
-        <v>7389878</v>
+        <v>7390009</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7109,6 +7114,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7135,10 +7145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271886</v>
+        <v>127271841</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>79629</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7146,21 +7156,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7170,10 +7180,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811852</v>
+        <v>812139</v>
       </c>
       <c r="R68" t="n">
-        <v>7390093</v>
+        <v>7389967</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,10 +7242,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271881</v>
+        <v>127271842</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>79629</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7243,21 +7253,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7267,10 +7277,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812133</v>
+        <v>812161</v>
       </c>
       <c r="R69" t="n">
-        <v>7389830</v>
+        <v>7389878</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,10 +7339,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271876</v>
+        <v>127271886</v>
       </c>
       <c r="B70" t="n">
-        <v>81004</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7340,21 +7350,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7364,10 +7374,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812128</v>
+        <v>811852</v>
       </c>
       <c r="R70" t="n">
-        <v>7390038</v>
+        <v>7390093</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7408,7 +7418,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7430,7 +7439,7 @@
         <v>127271912</v>
       </c>
       <c r="B71" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7527,7 +7536,7 @@
         <v>127271921</v>
       </c>
       <c r="B72" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7624,7 +7633,7 @@
         <v>127271909</v>
       </c>
       <c r="B73" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7718,10 +7727,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271852</v>
+        <v>127271881</v>
       </c>
       <c r="B74" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7729,38 +7738,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812054</v>
+        <v>812133</v>
       </c>
       <c r="R74" t="n">
-        <v>7390009</v>
+        <v>7389830</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7793,11 +7798,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7824,32 +7824,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127271924</v>
+        <v>127271880</v>
       </c>
       <c r="B75" t="n">
-        <v>92640</v>
+        <v>79011</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7859,10 +7859,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>812019</v>
+        <v>812207</v>
       </c>
       <c r="R75" t="n">
-        <v>7389582</v>
+        <v>7389858</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7921,32 +7921,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127271880</v>
+        <v>127271924</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>92609</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>812207</v>
+        <v>812019</v>
       </c>
       <c r="R76" t="n">
-        <v>7389858</v>
+        <v>7389582</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8021,7 +8021,7 @@
         <v>127271917</v>
       </c>
       <c r="B77" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>127271908</v>
       </c>
       <c r="B78" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>127271877</v>
       </c>
       <c r="B79" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>127271851</v>
       </c>
       <c r="B80" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>127271865</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>127271895</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>127271878</v>
       </c>
       <c r="B83" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>127271882</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>127271843</v>
       </c>
       <c r="B85" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>127271890</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>127271838</v>
       </c>
       <c r="B87" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>127271872</v>
       </c>
       <c r="B88" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271891</v>
+        <v>127271849</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9216,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812077</v>
+        <v>812114</v>
       </c>
       <c r="R89" t="n">
-        <v>7389800</v>
+        <v>7389969</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9276,6 +9276,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9302,10 +9307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271836</v>
+        <v>127271897</v>
       </c>
       <c r="B90" t="n">
-        <v>79647</v>
+        <v>57657</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9313,34 +9318,38 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811958</v>
+        <v>812122</v>
       </c>
       <c r="R90" t="n">
-        <v>7389950</v>
+        <v>7389709</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9373,6 +9382,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9399,10 +9413,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271894</v>
+        <v>127271891</v>
       </c>
       <c r="B91" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9434,10 +9448,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811982</v>
+        <v>812077</v>
       </c>
       <c r="R91" t="n">
-        <v>7389609</v>
+        <v>7389800</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9496,10 +9510,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271849</v>
+        <v>127271836</v>
       </c>
       <c r="B92" t="n">
-        <v>57672</v>
+        <v>79629</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9507,21 +9521,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9531,10 +9545,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>812114</v>
+        <v>811958</v>
       </c>
       <c r="R92" t="n">
-        <v>7389969</v>
+        <v>7389950</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9567,11 +9581,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9598,10 +9607,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271897</v>
+        <v>127271894</v>
       </c>
       <c r="B93" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9609,38 +9618,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>812122</v>
+        <v>811982</v>
       </c>
       <c r="R93" t="n">
-        <v>7389709</v>
+        <v>7389609</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9673,11 +9678,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9707,7 +9707,7 @@
         <v>127271840</v>
       </c>
       <c r="B94" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9801,10 +9801,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271868</v>
+        <v>127271856</v>
       </c>
       <c r="B95" t="n">
-        <v>57832</v>
+        <v>57657</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,34 +9812,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812092</v>
+        <v>811876</v>
       </c>
       <c r="R95" t="n">
-        <v>7389656</v>
+        <v>7389968</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9872,6 +9876,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9898,10 +9907,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271856</v>
+        <v>127271857</v>
       </c>
       <c r="B96" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9927,20 +9936,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811876</v>
+        <v>812050</v>
       </c>
       <c r="R96" t="n">
-        <v>7389968</v>
+        <v>7389925</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9973,11 +9978,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +10004,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271857</v>
+        <v>127271868</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>57817</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10015,21 +10015,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812050</v>
+        <v>812092</v>
       </c>
       <c r="R97" t="n">
-        <v>7389925</v>
+        <v>7389656</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10104,7 +10104,7 @@
         <v>127271915</v>
       </c>
       <c r="B98" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>127271874</v>
       </c>
       <c r="B99" t="n">
-        <v>57776</v>
+        <v>57761</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10295,45 +10295,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271907</v>
+        <v>127271864</v>
       </c>
       <c r="B100" t="n">
-        <v>92640</v>
+        <v>57657</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812162</v>
+        <v>812087</v>
       </c>
       <c r="R100" t="n">
-        <v>7389625</v>
+        <v>7389653</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10366,6 +10370,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10392,10 +10401,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271916</v>
+        <v>127271907</v>
       </c>
       <c r="B101" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10427,10 +10436,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811958</v>
+        <v>812162</v>
       </c>
       <c r="R101" t="n">
-        <v>7389946</v>
+        <v>7389625</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10492,7 +10501,7 @@
         <v>127271893</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10586,32 +10595,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271884</v>
+        <v>127271916</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>92609</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10621,10 +10630,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811977</v>
+        <v>811958</v>
       </c>
       <c r="R103" t="n">
-        <v>7389985</v>
+        <v>7389946</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10683,10 +10692,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271864</v>
+        <v>127271884</v>
       </c>
       <c r="B104" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10694,38 +10703,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>812087</v>
+        <v>811977</v>
       </c>
       <c r="R104" t="n">
-        <v>7389653</v>
+        <v>7389985</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10758,11 +10763,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,45 +10789,49 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271913</v>
+        <v>127271853</v>
       </c>
       <c r="B105" t="n">
-        <v>92640</v>
+        <v>57657</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811963</v>
+        <v>811970</v>
       </c>
       <c r="R105" t="n">
-        <v>7390029</v>
+        <v>7390085</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10860,6 +10864,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10886,10 +10895,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271906</v>
+        <v>127271913</v>
       </c>
       <c r="B106" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10921,10 +10930,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812166</v>
+        <v>811963</v>
       </c>
       <c r="R106" t="n">
-        <v>7389625</v>
+        <v>7390029</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10986,7 +10995,7 @@
         <v>127271892</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11083,7 +11092,7 @@
         <v>127271879</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11177,32 +11186,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271844</v>
+        <v>127271906</v>
       </c>
       <c r="B109" t="n">
-        <v>79647</v>
+        <v>92609</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11212,10 +11221,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812114</v>
+        <v>812166</v>
       </c>
       <c r="R109" t="n">
-        <v>7389680</v>
+        <v>7389625</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11274,10 +11283,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271853</v>
+        <v>127271844</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>79629</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11285,38 +11294,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811970</v>
+        <v>812114</v>
       </c>
       <c r="R110" t="n">
-        <v>7390085</v>
+        <v>7389680</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11349,11 +11354,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11383,7 +11383,7 @@
         <v>127271922</v>
       </c>
       <c r="B111" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>127271885</v>
       </c>
       <c r="B112" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>127271860</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11680,10 +11680,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271887</v>
+        <v>127271862</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11691,34 +11691,38 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811866</v>
+        <v>812079</v>
       </c>
       <c r="R114" t="n">
-        <v>7390052</v>
+        <v>7389800</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11751,6 +11755,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11780,7 +11789,7 @@
         <v>127271866</v>
       </c>
       <c r="B115" t="n">
-        <v>56864</v>
+        <v>56849</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11874,32 +11883,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271919</v>
+        <v>127271887</v>
       </c>
       <c r="B116" t="n">
-        <v>92640</v>
+        <v>79011</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11909,10 +11918,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>812158</v>
+        <v>811866</v>
       </c>
       <c r="R116" t="n">
-        <v>7389883</v>
+        <v>7390052</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11971,10 +11980,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271914</v>
+        <v>127271919</v>
       </c>
       <c r="B117" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12006,10 +12015,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811875</v>
+        <v>812158</v>
       </c>
       <c r="R117" t="n">
-        <v>7389980</v>
+        <v>7389883</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12068,49 +12077,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271862</v>
+        <v>127271914</v>
       </c>
       <c r="B118" t="n">
-        <v>57672</v>
+        <v>92609</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>812079</v>
+        <v>811875</v>
       </c>
       <c r="R118" t="n">
-        <v>7389800</v>
+        <v>7389980</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12143,11 +12148,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12177,7 +12177,7 @@
         <v>127271918</v>
       </c>
       <c r="B119" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>127271861</v>
       </c>
       <c r="B120" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>127271850</v>
       </c>
       <c r="B121" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127049629</v>
+        <v>127049633</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>812039</v>
+        <v>811950</v>
       </c>
       <c r="R2" t="n">
-        <v>7389512</v>
+        <v>7389574</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049592</v>
+        <v>127049613</v>
       </c>
       <c r="B3" t="n">
-        <v>79638</v>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812072</v>
+        <v>812049</v>
       </c>
       <c r="R3" t="n">
-        <v>7389539</v>
+        <v>7389598</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049608</v>
+        <v>127049614</v>
       </c>
       <c r="B4" t="n">
-        <v>97339</v>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812055</v>
+        <v>812078</v>
       </c>
       <c r="R4" t="n">
-        <v>7389491</v>
+        <v>7389625</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049602</v>
+        <v>127049615</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,38 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>812043</v>
+        <v>811948</v>
       </c>
       <c r="R5" t="n">
-        <v>7389685</v>
+        <v>7389545</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1041,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049638</v>
+        <v>127271876</v>
       </c>
       <c r="B6" t="n">
-        <v>92628</v>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811921</v>
+        <v>812128</v>
       </c>
       <c r="R6" t="n">
-        <v>7389590</v>
+        <v>7390038</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1137,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1151,6 +1142,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1169,32 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049639</v>
+        <v>127388830</v>
       </c>
       <c r="B7" t="n">
-        <v>92628</v>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,13 +1196,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811937</v>
+        <v>812039</v>
       </c>
       <c r="R7" t="n">
-        <v>7389558</v>
+        <v>7389582</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1234,12 +1226,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1266,32 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049611</v>
+        <v>127049634</v>
       </c>
       <c r="B8" t="n">
-        <v>97339</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>812004</v>
+        <v>812073</v>
       </c>
       <c r="R8" t="n">
-        <v>7389528</v>
+        <v>7389533</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1363,10 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127049621</v>
+        <v>127049635</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>812153</v>
+        <v>812027</v>
       </c>
       <c r="R9" t="n">
-        <v>7389594</v>
+        <v>7389564</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1460,10 +1452,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127049595</v>
+        <v>127049636</v>
       </c>
       <c r="B10" t="n">
-        <v>79638</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811948</v>
+        <v>811936</v>
       </c>
       <c r="R10" t="n">
-        <v>7389545</v>
+        <v>7389670</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1557,32 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127049612</v>
+        <v>127049637</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>812021</v>
+        <v>811936</v>
       </c>
       <c r="R11" t="n">
-        <v>7389454</v>
+        <v>7389571</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1654,10 +1646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049620</v>
+        <v>127049638</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1657,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>812079</v>
+        <v>811921</v>
       </c>
       <c r="R12" t="n">
-        <v>7389510</v>
+        <v>7389590</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1751,10 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049628</v>
+        <v>127049639</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1754,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811980</v>
+        <v>811937</v>
       </c>
       <c r="R13" t="n">
-        <v>7389540</v>
+        <v>7389558</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1848,10 +1840,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049618</v>
+        <v>127049640</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1851,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>812047</v>
+        <v>811936</v>
       </c>
       <c r="R14" t="n">
-        <v>7389473</v>
+        <v>7389556</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1945,10 +1937,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049596</v>
+        <v>127049641</v>
       </c>
       <c r="B15" t="n">
-        <v>79638</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1948,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811955</v>
+        <v>811963</v>
       </c>
       <c r="R15" t="n">
-        <v>7389537</v>
+        <v>7389548</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2042,10 +2034,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127049623</v>
+        <v>127049642</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2053,21 +2045,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2077,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>812077</v>
+        <v>811969</v>
       </c>
       <c r="R16" t="n">
-        <v>7389513</v>
+        <v>7389545</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2139,14 +2131,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127049645</v>
+        <v>127049643</v>
       </c>
       <c r="B17" t="n">
-        <v>92628</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2174,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>812008</v>
+        <v>811987</v>
       </c>
       <c r="R17" t="n">
-        <v>7389456</v>
+        <v>7389527</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2236,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127049630</v>
+        <v>127049645</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2247,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2271,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>812021</v>
+        <v>812008</v>
       </c>
       <c r="R18" t="n">
-        <v>7389474</v>
+        <v>7389456</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2333,10 +2325,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127049631</v>
+        <v>127271906</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2336,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>812026</v>
+        <v>812166</v>
       </c>
       <c r="R19" t="n">
-        <v>7389461</v>
+        <v>7389625</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2398,12 +2390,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2430,10 +2422,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127049622</v>
+        <v>127271907</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2433,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>812088</v>
+        <v>812162</v>
       </c>
       <c r="R20" t="n">
-        <v>7389588</v>
+        <v>7389625</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2495,12 +2487,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2527,10 +2519,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127049601</v>
+        <v>127271908</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2538,38 +2530,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811940</v>
+        <v>812128</v>
       </c>
       <c r="R21" t="n">
-        <v>7389556</v>
+        <v>7389752</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2596,17 +2584,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan rinnande kåda.</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2633,10 +2616,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127049593</v>
+        <v>127271909</v>
       </c>
       <c r="B22" t="n">
-        <v>79638</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2644,21 +2627,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2668,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811934</v>
+        <v>812175</v>
       </c>
       <c r="R22" t="n">
-        <v>7389548</v>
+        <v>7389748</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2698,12 +2681,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2730,14 +2713,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127049637</v>
+        <v>127271910</v>
       </c>
       <c r="B23" t="n">
-        <v>92628</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2765,10 +2748,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811936</v>
+        <v>812192</v>
       </c>
       <c r="R23" t="n">
-        <v>7389571</v>
+        <v>7389757</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2795,12 +2778,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2827,14 +2810,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127049640</v>
+        <v>127271911</v>
       </c>
       <c r="B24" t="n">
-        <v>92628</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2862,10 +2845,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811936</v>
+        <v>812117</v>
       </c>
       <c r="R24" t="n">
-        <v>7389556</v>
+        <v>7389993</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2892,12 +2875,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2924,10 +2907,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127049613</v>
+        <v>127271912</v>
       </c>
       <c r="B25" t="n">
-        <v>80995</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2935,21 +2918,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2959,10 +2942,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>812049</v>
+        <v>811981</v>
       </c>
       <c r="R25" t="n">
-        <v>7389598</v>
+        <v>7389988</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -2989,12 +2972,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3021,10 +3004,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127049605</v>
+        <v>127271913</v>
       </c>
       <c r="B26" t="n">
-        <v>92656</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3032,21 +3015,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3056,10 +3039,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811911</v>
+        <v>811963</v>
       </c>
       <c r="R26" t="n">
-        <v>7389588</v>
+        <v>7390029</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3086,12 +3069,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3118,32 +3101,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127049609</v>
+        <v>127271914</v>
       </c>
       <c r="B27" t="n">
-        <v>97339</v>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3153,10 +3136,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811991</v>
+        <v>811875</v>
       </c>
       <c r="R27" t="n">
-        <v>7389623</v>
+        <v>7389980</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3183,12 +3166,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3215,10 +3198,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127049633</v>
+        <v>127271915</v>
       </c>
       <c r="B28" t="n">
-        <v>78687</v>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3226,21 +3209,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3250,10 +3233,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811950</v>
+        <v>811935</v>
       </c>
       <c r="R28" t="n">
-        <v>7389574</v>
+        <v>7389943</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3280,12 +3263,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3312,14 +3295,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127049642</v>
+        <v>127271916</v>
       </c>
       <c r="B29" t="n">
-        <v>92628</v>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3347,10 +3330,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811969</v>
+        <v>811958</v>
       </c>
       <c r="R29" t="n">
-        <v>7389545</v>
+        <v>7389946</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3377,12 +3360,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3409,14 +3392,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127049643</v>
+        <v>127271917</v>
       </c>
       <c r="B30" t="n">
-        <v>92628</v>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3444,10 +3427,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811987</v>
+        <v>812088</v>
       </c>
       <c r="R30" t="n">
-        <v>7389527</v>
+        <v>7389936</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3474,12 +3457,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3506,10 +3489,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127049594</v>
+        <v>127271918</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3517,21 +3500,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3541,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811945</v>
+        <v>812162</v>
       </c>
       <c r="R31" t="n">
-        <v>7389563</v>
+        <v>7389925</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3571,12 +3554,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3603,32 +3586,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127049610</v>
+        <v>127271919</v>
       </c>
       <c r="B32" t="n">
-        <v>97339</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3638,10 +3621,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811967</v>
+        <v>812158</v>
       </c>
       <c r="R32" t="n">
-        <v>7389626</v>
+        <v>7389883</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3668,12 +3651,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3700,32 +3683,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127049607</v>
+        <v>127271920</v>
       </c>
       <c r="B33" t="n">
-        <v>97339</v>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3735,10 +3718,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>812105</v>
+        <v>812127</v>
       </c>
       <c r="R33" t="n">
-        <v>7389559</v>
+        <v>7389853</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3765,12 +3748,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3797,14 +3780,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127049635</v>
+        <v>127271921</v>
       </c>
       <c r="B34" t="n">
-        <v>92628</v>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3832,10 +3815,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>812027</v>
+        <v>812092</v>
       </c>
       <c r="R34" t="n">
-        <v>7389564</v>
+        <v>7389721</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3862,12 +3845,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3894,10 +3877,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127049625</v>
+        <v>127271922</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3905,21 +3888,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3929,10 +3912,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811987</v>
+        <v>812120</v>
       </c>
       <c r="R35" t="n">
-        <v>7389722</v>
+        <v>7389691</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3959,12 +3942,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3991,10 +3974,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127049619</v>
+        <v>127271923</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4002,21 +3985,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4026,10 +4009,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>812060</v>
+        <v>811986</v>
       </c>
       <c r="R36" t="n">
-        <v>7389489</v>
+        <v>7389610</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4056,12 +4039,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4088,10 +4071,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127049624</v>
+        <v>127271924</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4099,21 +4082,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4123,10 +4106,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>812000</v>
+        <v>812019</v>
       </c>
       <c r="R37" t="n">
-        <v>7389736</v>
+        <v>7389582</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4153,12 +4136,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4185,32 +4168,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127049616</v>
+        <v>127049618</v>
       </c>
       <c r="B38" t="n">
-        <v>78778</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4220,10 +4203,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811934</v>
+        <v>812047</v>
       </c>
       <c r="R38" t="n">
-        <v>7389548</v>
+        <v>7389473</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4282,32 +4265,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127049648</v>
+        <v>127049619</v>
       </c>
       <c r="B39" t="n">
-        <v>78426</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4317,10 +4300,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811948</v>
+        <v>812060</v>
       </c>
       <c r="R39" t="n">
-        <v>7389545</v>
+        <v>7389489</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4361,7 +4344,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4380,49 +4362,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127049632</v>
+        <v>127049620</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>812117</v>
+        <v>812079</v>
       </c>
       <c r="R40" t="n">
-        <v>7389623</v>
+        <v>7389510</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4455,11 +4433,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4486,32 +4459,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127049591</v>
+        <v>127049621</v>
       </c>
       <c r="B41" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4521,10 +4494,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>812066</v>
+        <v>812153</v>
       </c>
       <c r="R41" t="n">
-        <v>7389504</v>
+        <v>7389594</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4583,32 +4556,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127049647</v>
+        <v>127049622</v>
       </c>
       <c r="B42" t="n">
-        <v>77998</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4618,10 +4591,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811948</v>
+        <v>812088</v>
       </c>
       <c r="R42" t="n">
-        <v>7389545</v>
+        <v>7389588</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4680,32 +4653,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127049634</v>
+        <v>127049623</v>
       </c>
       <c r="B43" t="n">
-        <v>92628</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4715,10 +4688,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>812073</v>
+        <v>812077</v>
       </c>
       <c r="R43" t="n">
-        <v>7389533</v>
+        <v>7389513</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4777,32 +4750,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127049615</v>
+        <v>127049624</v>
       </c>
       <c r="B44" t="n">
-        <v>80995</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4812,10 +4785,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811948</v>
+        <v>812000</v>
       </c>
       <c r="R44" t="n">
-        <v>7389545</v>
+        <v>7389736</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4874,32 +4847,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127049614</v>
+        <v>127049625</v>
       </c>
       <c r="B45" t="n">
-        <v>80995</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4909,10 +4882,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>812078</v>
+        <v>811987</v>
       </c>
       <c r="R45" t="n">
-        <v>7389625</v>
+        <v>7389722</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4971,32 +4944,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127049606</v>
+        <v>127049626</v>
       </c>
       <c r="B46" t="n">
-        <v>97339</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5006,10 +4979,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>812115</v>
+        <v>811984</v>
       </c>
       <c r="R46" t="n">
-        <v>7389567</v>
+        <v>7389705</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5068,14 +5041,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127049626</v>
+        <v>127049627</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5103,10 +5076,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811984</v>
+        <v>811924</v>
       </c>
       <c r="R47" t="n">
-        <v>7389705</v>
+        <v>7389661</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5165,32 +5138,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127049641</v>
+        <v>127049628</v>
       </c>
       <c r="B48" t="n">
-        <v>92628</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5200,10 +5173,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811963</v>
+        <v>811980</v>
       </c>
       <c r="R48" t="n">
-        <v>7389548</v>
+        <v>7389540</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5262,32 +5235,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127049600</v>
+        <v>127049629</v>
       </c>
       <c r="B49" t="n">
-        <v>79618</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5297,10 +5270,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811948</v>
+        <v>812039</v>
       </c>
       <c r="R49" t="n">
-        <v>7389545</v>
+        <v>7389512</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5341,7 +5314,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5360,32 +5332,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127049598</v>
+        <v>127049630</v>
       </c>
       <c r="B50" t="n">
-        <v>79618</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5395,10 +5367,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>812070</v>
+        <v>812021</v>
       </c>
       <c r="R50" t="n">
-        <v>7389509</v>
+        <v>7389474</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5439,7 +5411,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5458,32 +5429,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127049599</v>
+        <v>127049631</v>
       </c>
       <c r="B51" t="n">
-        <v>79618</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5493,10 +5464,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811934</v>
+        <v>812026</v>
       </c>
       <c r="R51" t="n">
-        <v>7389548</v>
+        <v>7389461</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5537,7 +5508,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5556,32 +5526,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127271845</v>
+        <v>127271878</v>
       </c>
       <c r="B52" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5591,10 +5561,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811999</v>
+        <v>812112</v>
       </c>
       <c r="R52" t="n">
-        <v>7389631</v>
+        <v>7389762</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5653,49 +5623,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127271854</v>
+        <v>127271879</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811858</v>
+        <v>812228</v>
       </c>
       <c r="R53" t="n">
-        <v>7390099</v>
+        <v>7389839</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5728,11 +5694,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5759,32 +5720,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127271920</v>
+        <v>127271880</v>
       </c>
       <c r="B54" t="n">
-        <v>92640</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5794,10 +5755,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>812127</v>
+        <v>812207</v>
       </c>
       <c r="R54" t="n">
-        <v>7389853</v>
+        <v>7389858</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5856,14 +5817,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127271889</v>
+        <v>127271881</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -5891,10 +5852,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811973</v>
+        <v>812133</v>
       </c>
       <c r="R55" t="n">
-        <v>7389939</v>
+        <v>7389830</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5953,32 +5914,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127271910</v>
+        <v>127271882</v>
       </c>
       <c r="B56" t="n">
-        <v>92640</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5988,10 +5949,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>812192</v>
+        <v>812120</v>
       </c>
       <c r="R56" t="n">
-        <v>7389757</v>
+        <v>7389917</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6050,32 +6011,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127271923</v>
+        <v>127271883</v>
       </c>
       <c r="B57" t="n">
-        <v>92640</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6085,10 +6046,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811986</v>
+        <v>812004</v>
       </c>
       <c r="R57" t="n">
-        <v>7389610</v>
+        <v>7389960</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6147,32 +6108,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127271925</v>
+        <v>127271884</v>
       </c>
       <c r="B58" t="n">
-        <v>78435</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6182,10 +6143,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>812066</v>
+        <v>811977</v>
       </c>
       <c r="R58" t="n">
-        <v>7389760</v>
+        <v>7389985</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6244,32 +6205,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127271847</v>
+        <v>127271885</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6279,10 +6240,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>812034</v>
+        <v>811960</v>
       </c>
       <c r="R59" t="n">
-        <v>7389561</v>
+        <v>7390029</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6341,49 +6302,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127271855</v>
+        <v>127271886</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811859</v>
+        <v>811852</v>
       </c>
       <c r="R60" t="n">
-        <v>7390026</v>
+        <v>7390093</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6416,11 +6373,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6447,32 +6399,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127271875</v>
+        <v>127271887</v>
       </c>
       <c r="B61" t="n">
-        <v>58042</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6482,10 +6434,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>812093</v>
+        <v>811866</v>
       </c>
       <c r="R61" t="n">
-        <v>7389656</v>
+        <v>7390052</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6544,32 +6496,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127271911</v>
+        <v>127271888</v>
       </c>
       <c r="B62" t="n">
-        <v>92640</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6579,10 +6531,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>812117</v>
+        <v>811957</v>
       </c>
       <c r="R62" t="n">
-        <v>7389993</v>
+        <v>7389943</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6641,14 +6593,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127271883</v>
+        <v>127271889</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6676,10 +6628,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>812004</v>
+        <v>811973</v>
       </c>
       <c r="R63" t="n">
-        <v>7389960</v>
+        <v>7389939</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6738,14 +6690,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127271888</v>
+        <v>127271890</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6773,10 +6725,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811957</v>
+        <v>812121</v>
       </c>
       <c r="R64" t="n">
-        <v>7389943</v>
+        <v>7389928</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6835,49 +6787,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127271858</v>
+        <v>127271891</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>812068</v>
+        <v>812077</v>
       </c>
       <c r="R65" t="n">
-        <v>7389929</v>
+        <v>7389800</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6910,11 +6858,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6941,32 +6884,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127271841</v>
+        <v>127271892</v>
       </c>
       <c r="B66" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6976,10 +6919,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>812139</v>
+        <v>812106</v>
       </c>
       <c r="R66" t="n">
-        <v>7389967</v>
+        <v>7389684</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7038,32 +6981,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127271842</v>
+        <v>127271893</v>
       </c>
       <c r="B67" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7073,10 +7016,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>812161</v>
+        <v>812066</v>
       </c>
       <c r="R67" t="n">
-        <v>7389878</v>
+        <v>7389634</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7135,14 +7078,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127271886</v>
+        <v>127271894</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7170,10 +7113,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811852</v>
+        <v>811982</v>
       </c>
       <c r="R68" t="n">
-        <v>7390093</v>
+        <v>7389609</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7232,14 +7175,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127271881</v>
+        <v>127271895</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7267,10 +7210,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>812133</v>
+        <v>812002</v>
       </c>
       <c r="R69" t="n">
-        <v>7389830</v>
+        <v>7389603</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7329,10 +7272,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127271876</v>
+        <v>127049648</v>
       </c>
       <c r="B70" t="n">
-        <v>81004</v>
+        <v>78730</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7340,21 +7283,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7364,10 +7307,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>812128</v>
+        <v>811948</v>
       </c>
       <c r="R70" t="n">
-        <v>7390038</v>
+        <v>7389545</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7394,12 +7337,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7427,32 +7370,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127271912</v>
+        <v>127271925</v>
       </c>
       <c r="B71" t="n">
-        <v>92640</v>
+        <v>78730</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7462,10 +7405,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811981</v>
+        <v>812066</v>
       </c>
       <c r="R71" t="n">
-        <v>7389988</v>
+        <v>7389760</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7524,32 +7467,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127271921</v>
+        <v>127049616</v>
       </c>
       <c r="B72" t="n">
-        <v>92640</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7559,10 +7502,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>812092</v>
+        <v>811934</v>
       </c>
       <c r="R72" t="n">
-        <v>7389721</v>
+        <v>7389548</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7589,12 +7532,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7621,32 +7564,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127271909</v>
+        <v>127049591</v>
       </c>
       <c r="B73" t="n">
-        <v>92640</v>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7656,10 +7599,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>812175</v>
+        <v>812066</v>
       </c>
       <c r="R73" t="n">
-        <v>7389748</v>
+        <v>7389504</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7686,12 +7629,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7718,10 +7661,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127271852</v>
+        <v>127049592</v>
       </c>
       <c r="B74" t="n">
-        <v>57672</v>
+        <v>79946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7729,38 +7672,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>812054</v>
+        <v>812072</v>
       </c>
       <c r="R74" t="n">
-        <v>7390009</v>
+        <v>7389539</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7787,17 +7726,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7824,32 +7758,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127271924</v>
+        <v>127049593</v>
       </c>
       <c r="B75" t="n">
-        <v>92640</v>
+        <v>79946</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7859,10 +7793,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>812019</v>
+        <v>811934</v>
       </c>
       <c r="R75" t="n">
-        <v>7389582</v>
+        <v>7389548</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7889,12 +7823,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7921,10 +7855,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127271880</v>
+        <v>127049594</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7932,21 +7866,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7956,10 +7890,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>812207</v>
+        <v>811945</v>
       </c>
       <c r="R76" t="n">
-        <v>7389858</v>
+        <v>7389563</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7986,12 +7920,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8018,32 +7952,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127271917</v>
+        <v>127049595</v>
       </c>
       <c r="B77" t="n">
-        <v>92640</v>
+        <v>79946</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8053,10 +7987,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>812088</v>
+        <v>811948</v>
       </c>
       <c r="R77" t="n">
-        <v>7389936</v>
+        <v>7389545</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8083,12 +8017,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8115,32 +8049,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127271908</v>
+        <v>127049596</v>
       </c>
       <c r="B78" t="n">
-        <v>92640</v>
+        <v>79946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8150,10 +8084,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>812128</v>
+        <v>811955</v>
       </c>
       <c r="R78" t="n">
-        <v>7389752</v>
+        <v>7389537</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8180,12 +8114,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8212,10 +8146,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127271877</v>
+        <v>127271836</v>
       </c>
       <c r="B79" t="n">
-        <v>91368</v>
+        <v>79946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8223,21 +8157,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8247,10 +8181,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>812195</v>
+        <v>811958</v>
       </c>
       <c r="R79" t="n">
-        <v>7389776</v>
+        <v>7389950</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8309,10 +8243,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127271851</v>
+        <v>127271838</v>
       </c>
       <c r="B80" t="n">
-        <v>57672</v>
+        <v>79946</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8320,38 +8254,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>812117</v>
+        <v>811971</v>
       </c>
       <c r="R80" t="n">
-        <v>7389911</v>
+        <v>7389931</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8384,11 +8314,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8415,10 +8340,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127271865</v>
+        <v>127271840</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>79946</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8426,38 +8351,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>812024</v>
+        <v>812127</v>
       </c>
       <c r="R81" t="n">
-        <v>7389558</v>
+        <v>7389936</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8490,11 +8411,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8521,10 +8437,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127271895</v>
+        <v>127271841</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8532,21 +8448,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8556,10 +8472,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>812002</v>
+        <v>812139</v>
       </c>
       <c r="R82" t="n">
-        <v>7389603</v>
+        <v>7389967</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8618,10 +8534,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127271878</v>
+        <v>127271842</v>
       </c>
       <c r="B83" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8629,21 +8545,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8653,10 +8569,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>812112</v>
+        <v>812161</v>
       </c>
       <c r="R83" t="n">
-        <v>7389762</v>
+        <v>7389878</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8715,10 +8631,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127271882</v>
+        <v>127271843</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8726,21 +8642,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8750,10 +8666,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>812120</v>
+        <v>812074</v>
       </c>
       <c r="R84" t="n">
-        <v>7389917</v>
+        <v>7389829</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8812,10 +8728,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127271843</v>
+        <v>127271844</v>
       </c>
       <c r="B85" t="n">
-        <v>79647</v>
+        <v>79946</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8847,10 +8763,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>812074</v>
+        <v>812114</v>
       </c>
       <c r="R85" t="n">
-        <v>7389829</v>
+        <v>7389680</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8909,10 +8825,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127271890</v>
+        <v>127271845</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>79946</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,21 +8836,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8944,10 +8860,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>812121</v>
+        <v>811999</v>
       </c>
       <c r="R86" t="n">
-        <v>7389928</v>
+        <v>7389631</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9006,10 +8922,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127271838</v>
+        <v>127271846</v>
       </c>
       <c r="B87" t="n">
-        <v>79647</v>
+        <v>79946</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9041,10 +8957,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811971</v>
+        <v>811819</v>
       </c>
       <c r="R87" t="n">
-        <v>7389931</v>
+        <v>7390080</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9103,10 +9019,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127271872</v>
+        <v>127271847</v>
       </c>
       <c r="B88" t="n">
-        <v>57669</v>
+        <v>79946</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9114,21 +9030,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9138,10 +9054,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811880</v>
+        <v>812034</v>
       </c>
       <c r="R88" t="n">
-        <v>7390107</v>
+        <v>7389561</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9174,11 +9090,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9205,10 +9116,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127271891</v>
+        <v>127049647</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>78334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9216,21 +9127,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9240,10 +9151,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>812077</v>
+        <v>811948</v>
       </c>
       <c r="R89" t="n">
-        <v>7389800</v>
+        <v>7389545</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9270,12 +9181,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9302,32 +9213,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127271836</v>
+        <v>127271872</v>
       </c>
       <c r="B90" t="n">
-        <v>79647</v>
+        <v>57950</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9337,10 +9248,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811958</v>
+        <v>811880</v>
       </c>
       <c r="R90" t="n">
-        <v>7389950</v>
+        <v>7390107</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9373,6 +9284,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre hack på gamma l tallåga.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9399,10 +9315,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127271894</v>
+        <v>127049601</v>
       </c>
       <c r="B91" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9410,34 +9326,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811982</v>
+        <v>811940</v>
       </c>
       <c r="R91" t="n">
-        <v>7389609</v>
+        <v>7389556</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9464,12 +9384,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan rinnande kåda.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9496,10 +9421,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127271849</v>
+        <v>127049602</v>
       </c>
       <c r="B92" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9525,16 +9450,20 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>812114</v>
+        <v>812043</v>
       </c>
       <c r="R92" t="n">
-        <v>7389969</v>
+        <v>7389685</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9561,17 +9490,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9598,10 +9527,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127271897</v>
+        <v>127049632</v>
       </c>
       <c r="B93" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9626,21 +9555,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>812122</v>
+        <v>812117</v>
       </c>
       <c r="R93" t="n">
-        <v>7389709</v>
+        <v>7389623</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9667,17 +9596,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Observerad och filmad under födosök.</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9704,10 +9633,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127271840</v>
+        <v>127271849</v>
       </c>
       <c r="B94" t="n">
-        <v>79647</v>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,21 +9644,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9739,10 +9668,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>812127</v>
+        <v>812114</v>
       </c>
       <c r="R94" t="n">
-        <v>7389936</v>
+        <v>7389969</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9775,6 +9704,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack på tall som är markerad som hänsyn av markägaren inför avverkning.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9801,10 +9735,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127271868</v>
+        <v>127271850</v>
       </c>
       <c r="B95" t="n">
-        <v>57832</v>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,34 +9746,38 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>812092</v>
+        <v>812124</v>
       </c>
       <c r="R95" t="n">
-        <v>7389656</v>
+        <v>7389758</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9872,6 +9810,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Mellersta området</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9898,10 +9841,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127271856</v>
+        <v>127271851</v>
       </c>
       <c r="B96" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9937,10 +9880,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811876</v>
+        <v>812117</v>
       </c>
       <c r="R96" t="n">
-        <v>7389968</v>
+        <v>7389911</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9977,7 +9920,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Äldre ringhack utan kåda. På äldre tall.</t>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10004,10 +9947,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127271857</v>
+        <v>127271852</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10033,16 +9976,20 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>812050</v>
+        <v>812054</v>
       </c>
       <c r="R97" t="n">
-        <v>7389925</v>
+        <v>7390009</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10075,6 +10022,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10101,45 +10053,49 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127271915</v>
+        <v>127271853</v>
       </c>
       <c r="B98" t="n">
-        <v>92640</v>
+        <v>57953</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811935</v>
+        <v>811970</v>
       </c>
       <c r="R98" t="n">
-        <v>7389943</v>
+        <v>7390085</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10172,6 +10128,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10198,27 +10159,27 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127271874</v>
+        <v>127271854</v>
       </c>
       <c r="B99" t="n">
-        <v>57776</v>
+        <v>57953</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10227,16 +10188,20 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>812168</v>
+        <v>811858</v>
       </c>
       <c r="R99" t="n">
-        <v>7389829</v>
+        <v>7390099</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10269,6 +10234,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10295,45 +10265,49 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127271907</v>
+        <v>127271855</v>
       </c>
       <c r="B100" t="n">
-        <v>92640</v>
+        <v>57953</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>812162</v>
+        <v>811859</v>
       </c>
       <c r="R100" t="n">
-        <v>7389625</v>
+        <v>7390026</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10366,6 +10340,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På tall.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10392,45 +10371,49 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127271916</v>
+        <v>127271856</v>
       </c>
       <c r="B101" t="n">
-        <v>92640</v>
+        <v>57953</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811958</v>
+        <v>811876</v>
       </c>
       <c r="R101" t="n">
-        <v>7389946</v>
+        <v>7389968</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10463,6 +10446,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre ringhack utan kåda. På äldre tall.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10489,10 +10477,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127271893</v>
+        <v>127271857</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10500,21 +10488,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10524,10 +10512,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>812066</v>
+        <v>812050</v>
       </c>
       <c r="R102" t="n">
-        <v>7389634</v>
+        <v>7389925</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10586,10 +10574,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127271884</v>
+        <v>127271858</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10597,34 +10585,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811977</v>
+        <v>812068</v>
       </c>
       <c r="R103" t="n">
-        <v>7389985</v>
+        <v>7389929</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10657,6 +10649,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack. På tall.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10683,10 +10680,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127271864</v>
+        <v>127271860</v>
       </c>
       <c r="B104" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10722,10 +10719,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>812087</v>
+        <v>812080</v>
       </c>
       <c r="R104" t="n">
-        <v>7389653</v>
+        <v>7389823</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10762,7 +10759,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Färskare ringhack på tall.</t>
+          <t>Äldre ringhack utan kåda på tall.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10789,45 +10786,49 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127271913</v>
+        <v>127271861</v>
       </c>
       <c r="B105" t="n">
-        <v>92640</v>
+        <v>57953</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811963</v>
+        <v>812106</v>
       </c>
       <c r="R105" t="n">
-        <v>7390029</v>
+        <v>7389819</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10860,6 +10861,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10886,45 +10892,49 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127271906</v>
+        <v>127271862</v>
       </c>
       <c r="B106" t="n">
-        <v>92640</v>
+        <v>57953</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>812166</v>
+        <v>812079</v>
       </c>
       <c r="R106" t="n">
-        <v>7389625</v>
+        <v>7389800</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10957,6 +10967,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10983,10 +10998,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127271892</v>
+        <v>127271864</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10994,34 +11009,38 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>812106</v>
+        <v>812087</v>
       </c>
       <c r="R107" t="n">
-        <v>7389684</v>
+        <v>7389653</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11054,6 +11073,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Färskare ringhack på tall.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11080,10 +11104,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127271879</v>
+        <v>127271865</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11091,34 +11115,38 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>812228</v>
+        <v>812024</v>
       </c>
       <c r="R108" t="n">
-        <v>7389839</v>
+        <v>7389558</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11151,6 +11179,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Avbarkade klena granar där tretåiga hackspetten har födosökt under gångna vintern, 2024-2025.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11177,10 +11210,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127271844</v>
+        <v>127271897</v>
       </c>
       <c r="B109" t="n">
-        <v>79647</v>
+        <v>57953</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11188,34 +11221,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>812114</v>
+        <v>812122</v>
       </c>
       <c r="R109" t="n">
-        <v>7389680</v>
+        <v>7389709</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11248,6 +11285,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Observerad och filmad under födosök.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11274,49 +11316,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127271853</v>
+        <v>127271866</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>57141</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811970</v>
+        <v>811935</v>
       </c>
       <c r="R110" t="n">
-        <v>7390085</v>
+        <v>7389957</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11349,11 +11387,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Äldre ringhack med vissa spår av kåda på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11380,10 +11413,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127271922</v>
+        <v>127049612</v>
       </c>
       <c r="B111" t="n">
-        <v>92640</v>
+        <v>58327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11391,21 +11424,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11415,10 +11448,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>812120</v>
+        <v>812021</v>
       </c>
       <c r="R111" t="n">
-        <v>7389691</v>
+        <v>7389454</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11445,12 +11478,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11477,32 +11510,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127271885</v>
+        <v>127271875</v>
       </c>
       <c r="B112" t="n">
-        <v>79029</v>
+        <v>58327</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11512,10 +11545,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811960</v>
+        <v>812093</v>
       </c>
       <c r="R112" t="n">
-        <v>7390029</v>
+        <v>7389656</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11574,10 +11607,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127271860</v>
+        <v>127049603</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>58114</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11585,38 +11618,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>812080</v>
+        <v>812059</v>
       </c>
       <c r="R113" t="n">
-        <v>7389823</v>
+        <v>7389467</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11643,17 +11672,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack utan kåda på tall.</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11680,10 +11704,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127271887</v>
+        <v>127271868</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>58114</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11691,21 +11715,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11715,10 +11739,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811866</v>
+        <v>812092</v>
       </c>
       <c r="R114" t="n">
-        <v>7390052</v>
+        <v>7389656</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11777,32 +11801,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127271866</v>
+        <v>127271874</v>
       </c>
       <c r="B115" t="n">
-        <v>57092</v>
+        <v>58057</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11812,10 +11836,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811935</v>
+        <v>812168</v>
       </c>
       <c r="R115" t="n">
-        <v>7389957</v>
+        <v>7389829</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11874,10 +11898,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127271919</v>
+        <v>127049606</v>
       </c>
       <c r="B116" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11885,21 +11909,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11909,10 +11933,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>812158</v>
+        <v>812115</v>
       </c>
       <c r="R116" t="n">
-        <v>7389883</v>
+        <v>7389567</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11939,12 +11963,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11971,10 +11995,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127271914</v>
+        <v>127049607</v>
       </c>
       <c r="B117" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11982,21 +12006,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12006,10 +12030,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811875</v>
+        <v>812105</v>
       </c>
       <c r="R117" t="n">
-        <v>7389980</v>
+        <v>7389559</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12036,12 +12060,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12068,49 +12092,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127271862</v>
+        <v>127049608</v>
       </c>
       <c r="B118" t="n">
-        <v>57672</v>
+        <v>97989</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>812079</v>
+        <v>812055</v>
       </c>
       <c r="R118" t="n">
-        <v>7389800</v>
+        <v>7389491</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12137,17 +12157,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack på tall med kåda kvar på stammen men inte helt färskt.</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12174,10 +12189,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127271918</v>
+        <v>127049609</v>
       </c>
       <c r="B119" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12185,21 +12200,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12209,10 +12224,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>812162</v>
+        <v>811991</v>
       </c>
       <c r="R119" t="n">
-        <v>7389925</v>
+        <v>7389623</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12239,12 +12254,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12271,49 +12286,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127271861</v>
+        <v>127049610</v>
       </c>
       <c r="B120" t="n">
-        <v>57672</v>
+        <v>97989</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>812106</v>
+        <v>811967</v>
       </c>
       <c r="R120" t="n">
-        <v>7389819</v>
+        <v>7389626</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12340,17 +12351,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12377,49 +12383,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127271850</v>
+        <v>127049611</v>
       </c>
       <c r="B121" t="n">
-        <v>57672</v>
+        <v>97989</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skaite, Lu lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>812124</v>
+        <v>812004</v>
       </c>
       <c r="R121" t="n">
-        <v>7389758</v>
+        <v>7389528</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12446,17 +12448,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Mellersta området</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12483,32 +12480,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127388830</v>
+        <v>127049598</v>
       </c>
       <c r="B122" t="n">
-        <v>91513</v>
+        <v>79917</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12518,13 +12515,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>812039</v>
+        <v>812070</v>
       </c>
       <c r="R122" t="n">
-        <v>7389582</v>
+        <v>7389509</v>
       </c>
       <c r="S122" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12548,12 +12545,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12562,6 +12559,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -12577,6 +12575,396 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>127049599</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Skaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>811934</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7389548</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>127049600</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Skaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>811948</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7389545</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127049604</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Skaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>811953</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7389640</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>127271869</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Skaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>811842</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7390090</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31283-2025 artfynd.xlsx
+++ b/artfynd/A 31283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AZ126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049613</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049615</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271876</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127388830</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049634</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049635</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049636</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049637</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049638</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049639</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049640</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049641</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049642</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049643</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049645</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271906</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2516,6 +2611,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271907</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2613,6 +2713,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271908</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2710,6 +2815,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271909</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2807,6 +2917,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271910</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2904,6 +3019,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271911</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3001,6 +3121,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271912</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3098,6 +3223,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271913</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3195,6 +3325,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271914</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3292,6 +3427,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271915</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3389,6 +3529,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271916</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3486,6 +3631,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271917</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3583,6 +3733,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271918</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3680,6 +3835,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271919</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3777,6 +3937,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271920</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3874,6 +4039,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271921</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3971,6 +4141,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271922</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4068,6 +4243,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271923</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4165,6 +4345,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271924</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4262,6 +4447,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049618</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4359,6 +4549,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049619</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4456,6 +4651,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049620</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4553,6 +4753,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049621</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4650,6 +4855,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049622</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4747,6 +4957,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049623</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4844,6 +5059,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049624</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4941,6 +5161,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049625</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5038,6 +5263,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049626</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5135,6 +5365,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049627</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5232,6 +5467,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049628</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5329,6 +5569,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049629</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5426,6 +5671,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049630</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5523,6 +5773,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049631</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5620,6 +5875,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271878</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5717,6 +5977,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271879</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5814,6 +6079,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271880</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5911,6 +6181,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271881</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6008,6 +6283,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271882</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6105,6 +6385,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271883</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6202,6 +6487,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271884</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6299,6 +6589,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271885</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6396,6 +6691,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271886</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6493,6 +6793,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271887</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6590,6 +6895,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271888</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6687,6 +6997,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271889</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6784,6 +7099,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271890</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6881,6 +7201,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271891</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6978,6 +7303,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271892</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7075,6 +7405,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271893</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7172,6 +7507,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271894</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7269,6 +7609,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271895</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7367,6 +7712,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049648</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7464,6 +7814,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271925</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7561,6 +7916,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049616</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7658,6 +8018,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049591</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7755,6 +8120,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049592</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7852,6 +8222,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049593</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7949,6 +8324,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049594</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8046,6 +8426,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049595</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8143,6 +8528,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049596</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8240,6 +8630,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271836</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8337,6 +8732,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271838</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8434,6 +8834,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271840</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8531,6 +8936,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271841</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8628,6 +9038,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271842</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8725,6 +9140,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271843</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8822,6 +9242,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271844</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8919,6 +9344,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271845</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9016,6 +9446,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271846</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9113,6 +9548,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271847</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9210,6 +9650,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049647</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9312,6 +9757,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271872</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9418,6 +9868,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049601</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9524,6 +9979,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049602</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9630,6 +10090,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049632</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9732,6 +10197,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271849</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9838,6 +10308,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271850</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9944,6 +10419,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271851</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10050,6 +10530,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271852</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10156,6 +10641,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271853</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10262,6 +10752,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271854</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10368,6 +10863,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271855</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10474,6 +10974,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271856</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10571,6 +11076,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271857</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10677,6 +11187,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271858</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10783,6 +11298,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271860</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10889,6 +11409,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271861</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10995,6 +11520,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271862</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11101,6 +11631,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271864</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11207,6 +11742,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271865</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11313,6 +11853,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271897</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11410,6 +11955,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271866</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11507,6 +12057,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049612</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11604,6 +12159,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271875</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11701,6 +12261,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049603</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11798,6 +12363,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271868</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11895,6 +12465,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271874</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11992,6 +12567,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049606</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12089,6 +12669,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049607</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12186,6 +12771,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049608</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12283,6 +12873,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049609</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12380,6 +12975,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049610</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12477,6 +13077,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049611</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12575,6 +13180,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049598</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12673,6 +13283,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049599</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12771,6 +13386,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049600</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12868,6 +13488,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049604</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12965,8 +13590,140 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127271869</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>